--- a/GearSage-client/rate/excel/metal_lure_detail.xlsx
+++ b/GearSage-client/rate/excel/metal_lure_detail.xlsx
@@ -32,7 +32,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">
@@ -441,11 +445,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>LFD10014</v>
+      </c>
+      <c r="B2" t="str">
+        <v>LF1000</v>
       </c>
       <c r="C2" t="str">
         <v>R30</v>
@@ -482,11 +486,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
+      <c r="A3" t="str">
+        <v>LFD10015</v>
+      </c>
+      <c r="B3" t="str">
+        <v>LF1000</v>
       </c>
       <c r="C3" t="str">
         <v>R35</v>
@@ -523,11 +527,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
+      <c r="A4" t="str">
+        <v>LFD10016</v>
+      </c>
+      <c r="B4" t="str">
+        <v>LF1000</v>
       </c>
       <c r="C4" t="str">
         <v>R40</v>
@@ -564,11 +568,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
+      <c r="A5" t="str">
+        <v>LFD10017</v>
+      </c>
+      <c r="B5" t="str">
+        <v>LF1000</v>
       </c>
       <c r="C5" t="str">
         <v>R45</v>
@@ -605,11 +609,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
+      <c r="A6" t="str">
+        <v>LFD10018</v>
+      </c>
+      <c r="B6" t="str">
+        <v>LF1000</v>
       </c>
       <c r="C6" t="str">
         <v>R50</v>
@@ -646,11 +650,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
+      <c r="A7" t="str">
+        <v>LFD10019</v>
+      </c>
+      <c r="B7" t="str">
+        <v>LF1001</v>
       </c>
       <c r="C7" t="str">
         <v>青虾VIB</v>
@@ -687,11 +691,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>2</v>
+      <c r="A8" t="str">
+        <v>LFD10020</v>
+      </c>
+      <c r="B8" t="str">
+        <v>LF1001</v>
       </c>
       <c r="C8" t="str">
         <v>青虾VIB</v>
@@ -728,11 +732,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
+      <c r="A9" t="str">
+        <v>LFD10021</v>
+      </c>
+      <c r="B9" t="str">
+        <v>LF1001</v>
       </c>
       <c r="C9" t="str">
         <v>青虾VIB</v>
@@ -769,11 +773,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>8</v>
+      <c r="A10" t="str">
+        <v>LFD10022</v>
+      </c>
+      <c r="B10" t="str">
+        <v>LF1007</v>
       </c>
       <c r="C10" t="str">
         <v>SR40</v>
@@ -810,11 +814,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>8</v>
+      <c r="A11" t="str">
+        <v>LFD10023</v>
+      </c>
+      <c r="B11" t="str">
+        <v>LF1007</v>
       </c>
       <c r="C11" t="str">
         <v>SR45</v>
@@ -851,11 +855,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>8</v>
+      <c r="A12" t="str">
+        <v>LFD10024</v>
+      </c>
+      <c r="B12" t="str">
+        <v>LF1007</v>
       </c>
       <c r="C12" t="str">
         <v>SR50</v>
@@ -892,11 +896,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13">
-        <v>8</v>
+      <c r="A13" t="str">
+        <v>LFD10025</v>
+      </c>
+      <c r="B13" t="str">
+        <v>LF1007</v>
       </c>
       <c r="C13" t="str">
         <v>SR55</v>
@@ -969,6 +973,9 @@
       <c r="L14" t="str">
         <v>626004</v>
       </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -1007,6 +1014,9 @@
       <c r="L15" t="str">
         <v>626011</v>
       </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -1045,6 +1055,9 @@
       <c r="L16" t="str">
         <v>626028</v>
       </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -1083,6 +1096,9 @@
       <c r="L17" t="str">
         <v>626035</v>
       </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -1121,6 +1137,9 @@
       <c r="L18" t="str">
         <v>626042</v>
       </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -1159,6 +1178,9 @@
       <c r="L19" t="str">
         <v>626059</v>
       </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -1197,6 +1219,9 @@
       <c r="L20" t="str">
         <v>626066</v>
       </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -1235,6 +1260,9 @@
       <c r="L21" t="str">
         <v>626073</v>
       </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -1273,6 +1301,9 @@
       <c r="L22" t="str">
         <v>626080</v>
       </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -1311,6 +1342,9 @@
       <c r="L23" t="str">
         <v>626097</v>
       </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -1349,6 +1383,9 @@
       <c r="L24" t="str">
         <v>626103</v>
       </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -1387,6 +1424,9 @@
       <c r="L25" t="str">
         <v>626110</v>
       </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -1425,6 +1465,9 @@
       <c r="L26" t="str">
         <v>626127</v>
       </c>
+      <c r="M26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -1463,6 +1506,9 @@
       <c r="L27" t="str">
         <v>626134</v>
       </c>
+      <c r="M27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -1501,6 +1547,9 @@
       <c r="L28" t="str">
         <v>626141</v>
       </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -1539,6 +1588,9 @@
       <c r="L29" t="str">
         <v>626158</v>
       </c>
+      <c r="M29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -1577,6 +1629,9 @@
       <c r="L30" t="str">
         <v>626271</v>
       </c>
+      <c r="M30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -1615,6 +1670,9 @@
       <c r="L31" t="str">
         <v>626288</v>
       </c>
+      <c r="M31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -1653,6 +1711,9 @@
       <c r="L32" t="str">
         <v>626295</v>
       </c>
+      <c r="M32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -1691,6 +1752,9 @@
       <c r="L33" t="str">
         <v>626301</v>
       </c>
+      <c r="M33" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -1729,6 +1793,9 @@
       <c r="L34" t="str">
         <v>626318</v>
       </c>
+      <c r="M34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -1767,6 +1834,9 @@
       <c r="L35" t="str">
         <v>626325</v>
       </c>
+      <c r="M35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -1805,6 +1875,9 @@
       <c r="L36" t="str">
         <v>626332</v>
       </c>
+      <c r="M36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -1843,6 +1916,9 @@
       <c r="L37" t="str">
         <v>626349</v>
       </c>
+      <c r="M37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -1881,6 +1957,9 @@
       <c r="L38" t="str">
         <v>626394</v>
       </c>
+      <c r="M38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -1919,6 +1998,9 @@
       <c r="L39" t="str">
         <v>626417</v>
       </c>
+      <c r="M39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -1957,6 +2039,9 @@
       <c r="L40" t="str">
         <v>626424</v>
       </c>
+      <c r="M40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -1995,6 +2080,9 @@
       <c r="L41" t="str">
         <v>626431</v>
       </c>
+      <c r="M41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -2033,6 +2121,9 @@
       <c r="L42" t="str">
         <v>626448</v>
       </c>
+      <c r="M42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -2071,6 +2162,9 @@
       <c r="L43" t="str">
         <v>626455</v>
       </c>
+      <c r="M43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -2109,6 +2203,9 @@
       <c r="L44" t="str">
         <v>626462</v>
       </c>
+      <c r="M44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -2147,6 +2244,9 @@
       <c r="L45" t="str">
         <v>626479</v>
       </c>
+      <c r="M45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -2185,6 +2285,9 @@
       <c r="L46" t="str">
         <v>626486</v>
       </c>
+      <c r="M46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -2223,6 +2326,9 @@
       <c r="L47" t="str">
         <v>626493</v>
       </c>
+      <c r="M47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -2261,6 +2367,9 @@
       <c r="L48" t="str">
         <v>626509</v>
       </c>
+      <c r="M48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -2299,6 +2408,9 @@
       <c r="L49" t="str">
         <v>626516</v>
       </c>
+      <c r="M49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -2337,6 +2449,9 @@
       <c r="L50" t="str">
         <v>626523</v>
       </c>
+      <c r="M50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -2375,6 +2490,9 @@
       <c r="L51" t="str">
         <v>626530</v>
       </c>
+      <c r="M51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -2413,6 +2531,9 @@
       <c r="L52" t="str">
         <v>626547</v>
       </c>
+      <c r="M52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -2451,6 +2572,9 @@
       <c r="L53" t="str">
         <v>626554</v>
       </c>
+      <c r="M53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -2489,6 +2613,9 @@
       <c r="L54" t="str">
         <v>626561</v>
       </c>
+      <c r="M54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -2527,6 +2654,9 @@
       <c r="L55" t="str">
         <v>626578</v>
       </c>
+      <c r="M55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -2565,6 +2695,9 @@
       <c r="L56" t="str">
         <v>626585</v>
       </c>
+      <c r="M56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -2603,6 +2736,9 @@
       <c r="L57" t="str">
         <v>626592</v>
       </c>
+      <c r="M57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -2641,6 +2777,9 @@
       <c r="L58" t="str">
         <v>626608</v>
       </c>
+      <c r="M58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -2679,6 +2818,9 @@
       <c r="L59" t="str">
         <v>626615</v>
       </c>
+      <c r="M59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -2717,6 +2859,9 @@
       <c r="L60" t="str">
         <v>626622</v>
       </c>
+      <c r="M60" t="str">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -2755,6 +2900,9 @@
       <c r="L61" t="str">
         <v>626639</v>
       </c>
+      <c r="M61" t="str">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -2793,6 +2941,9 @@
       <c r="L62" t="str">
         <v>626646</v>
       </c>
+      <c r="M62" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -2831,6 +2982,9 @@
       <c r="L63" t="str">
         <v>626653</v>
       </c>
+      <c r="M63" t="str">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -2869,6 +3023,9 @@
       <c r="L64" t="str">
         <v>626660</v>
       </c>
+      <c r="M64" t="str">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -2907,6 +3064,9 @@
       <c r="L65" t="str">
         <v>626677</v>
       </c>
+      <c r="M65" t="str">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -2945,6 +3105,9 @@
       <c r="L66" t="str">
         <v>626684</v>
       </c>
+      <c r="M66" t="str">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -2983,6 +3146,9 @@
       <c r="L67" t="str">
         <v>626691</v>
       </c>
+      <c r="M67" t="str">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -3021,6 +3187,9 @@
       <c r="L68" t="str">
         <v>626707</v>
       </c>
+      <c r="M68" t="str">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
@@ -3059,6 +3228,9 @@
       <c r="L69" t="str">
         <v>626714</v>
       </c>
+      <c r="M69" t="str">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
@@ -3097,6 +3269,9 @@
       <c r="L70" t="str">
         <v>626721</v>
       </c>
+      <c r="M70" t="str">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -3135,6 +3310,9 @@
       <c r="L71" t="str">
         <v>626738</v>
       </c>
+      <c r="M71" t="str">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -3173,6 +3351,9 @@
       <c r="L72" t="str">
         <v>626745</v>
       </c>
+      <c r="M72" t="str">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -3211,6 +3392,9 @@
       <c r="L73" t="str">
         <v>626752</v>
       </c>
+      <c r="M73" t="str">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
@@ -3249,6 +3433,9 @@
       <c r="L74" t="str">
         <v>626769</v>
       </c>
+      <c r="M74" t="str">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
@@ -3287,6 +3474,9 @@
       <c r="L75" t="str">
         <v>626776</v>
       </c>
+      <c r="M75" t="str">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -3325,6 +3515,9 @@
       <c r="L76" t="str">
         <v>626783</v>
       </c>
+      <c r="M76" t="str">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -3363,6 +3556,9 @@
       <c r="L77" t="str">
         <v>626790</v>
       </c>
+      <c r="M77" t="str">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -3401,6 +3597,9 @@
       <c r="L78" t="str">
         <v>626806</v>
       </c>
+      <c r="M78" t="str">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -3439,6 +3638,9 @@
       <c r="L79" t="str">
         <v>626813</v>
       </c>
+      <c r="M79" t="str">
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -3477,6 +3679,9 @@
       <c r="L80" t="str">
         <v>626820</v>
       </c>
+      <c r="M80" t="str">
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -3515,6 +3720,9 @@
       <c r="L81" t="str">
         <v>626837</v>
       </c>
+      <c r="M81" t="str">
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
@@ -3553,6 +3761,9 @@
       <c r="L82" t="str">
         <v>626844</v>
       </c>
+      <c r="M82" t="str">
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -3591,6 +3802,9 @@
       <c r="L83" t="str">
         <v>626851</v>
       </c>
+      <c r="M83" t="str">
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -3629,6 +3843,9 @@
       <c r="L84" t="str">
         <v>627001</v>
       </c>
+      <c r="M84" t="str">
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -3667,6 +3884,9 @@
       <c r="L85" t="str">
         <v>627018</v>
       </c>
+      <c r="M85" t="str">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -3705,6 +3925,9 @@
       <c r="L86" t="str">
         <v>627025</v>
       </c>
+      <c r="M86" t="str">
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
@@ -3743,6 +3966,9 @@
       <c r="L87" t="str">
         <v>627032</v>
       </c>
+      <c r="M87" t="str">
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
@@ -3781,6 +4007,9 @@
       <c r="L88" t="str">
         <v>627049</v>
       </c>
+      <c r="M88" t="str">
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
@@ -3819,6 +4048,9 @@
       <c r="L89" t="str">
         <v>627056</v>
       </c>
+      <c r="M89" t="str">
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
@@ -3857,6 +4089,9 @@
       <c r="L90" t="str">
         <v>627063</v>
       </c>
+      <c r="M90" t="str">
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
@@ -3895,6 +4130,9 @@
       <c r="L91" t="str">
         <v>627070</v>
       </c>
+      <c r="M91" t="str">
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
@@ -3933,6 +4171,9 @@
       <c r="L92" t="str">
         <v>627087</v>
       </c>
+      <c r="M92" t="str">
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -3971,6 +4212,9 @@
       <c r="L93" t="str">
         <v>627094</v>
       </c>
+      <c r="M93" t="str">
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -4009,6 +4253,9 @@
       <c r="L94" t="str">
         <v>656384</v>
       </c>
+      <c r="M94" t="str">
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -4047,6 +4294,9 @@
       <c r="L95" t="str">
         <v>656391</v>
       </c>
+      <c r="M95" t="str">
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
@@ -4085,6 +4335,9 @@
       <c r="L96" t="str">
         <v>656407</v>
       </c>
+      <c r="M96" t="str">
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
@@ -4123,6 +4376,9 @@
       <c r="L97" t="str">
         <v>656414</v>
       </c>
+      <c r="M97" t="str">
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
@@ -4161,6 +4417,9 @@
       <c r="L98" t="str">
         <v>104939</v>
       </c>
+      <c r="M98" t="str">
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -4199,6 +4458,9 @@
       <c r="L99" t="str">
         <v>104946</v>
       </c>
+      <c r="M99" t="str">
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
@@ -4237,6 +4499,9 @@
       <c r="L100" t="str">
         <v>104953</v>
       </c>
+      <c r="M100" t="str">
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
@@ -4275,6 +4540,9 @@
       <c r="L101" t="str">
         <v>656421</v>
       </c>
+      <c r="M101" t="str">
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -4313,6 +4581,9 @@
       <c r="L102" t="str">
         <v>656438</v>
       </c>
+      <c r="M102" t="str">
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
@@ -4351,6 +4622,9 @@
       <c r="L103" t="str">
         <v>656445</v>
       </c>
+      <c r="M103" t="str">
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
@@ -4389,6 +4663,9 @@
       <c r="L104" t="str">
         <v>656452</v>
       </c>
+      <c r="M104" t="str">
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -4427,6 +4704,9 @@
       <c r="L105" t="str">
         <v>104960</v>
       </c>
+      <c r="M105" t="str">
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -4465,6 +4745,9 @@
       <c r="L106" t="str">
         <v>104977</v>
       </c>
+      <c r="M106" t="str">
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -4503,6 +4786,9 @@
       <c r="L107" t="str">
         <v>104984</v>
       </c>
+      <c r="M107" t="str">
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -4541,6 +4827,9 @@
       <c r="L108" t="str">
         <v>656513</v>
       </c>
+      <c r="M108" t="str">
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
@@ -4579,6 +4868,9 @@
       <c r="L109" t="str">
         <v>656520</v>
       </c>
+      <c r="M109" t="str">
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
@@ -4617,6 +4909,9 @@
       <c r="L110" t="str">
         <v>656537</v>
       </c>
+      <c r="M110" t="str">
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
@@ -4655,6 +4950,9 @@
       <c r="L111" t="str">
         <v>656544</v>
       </c>
+      <c r="M111" t="str">
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
@@ -4693,6 +4991,9 @@
       <c r="L112" t="str">
         <v>104991</v>
       </c>
+      <c r="M112" t="str">
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
@@ -4731,6 +5032,9 @@
       <c r="L113" t="str">
         <v>105004</v>
       </c>
+      <c r="M113" t="str">
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -4769,6 +5073,9 @@
       <c r="L114" t="str">
         <v>105011</v>
       </c>
+      <c r="M114" t="str">
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
@@ -4807,6 +5114,9 @@
       <c r="L115" t="str">
         <v>656551</v>
       </c>
+      <c r="M115" t="str">
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
@@ -4845,6 +5155,9 @@
       <c r="L116" t="str">
         <v>656568</v>
       </c>
+      <c r="M116" t="str">
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
@@ -4883,6 +5196,9 @@
       <c r="L117" t="str">
         <v>656575</v>
       </c>
+      <c r="M117" t="str">
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
@@ -4921,6 +5237,9 @@
       <c r="L118" t="str">
         <v>656582</v>
       </c>
+      <c r="M118" t="str">
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
@@ -4959,6 +5278,9 @@
       <c r="L119" t="str">
         <v>105028</v>
       </c>
+      <c r="M119" t="str">
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
@@ -4997,6 +5319,9 @@
       <c r="L120" t="str">
         <v>105035</v>
       </c>
+      <c r="M120" t="str">
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
@@ -5035,6 +5360,9 @@
       <c r="L121" t="str">
         <v>105042</v>
       </c>
+      <c r="M121" t="str">
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
@@ -5073,6 +5401,9 @@
       <c r="L122" t="str">
         <v>713773</v>
       </c>
+      <c r="M122" t="str">
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -5111,6 +5442,9 @@
       <c r="L123" t="str">
         <v>713780</v>
       </c>
+      <c r="M123" t="str">
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -5149,6 +5483,9 @@
       <c r="L124" t="str">
         <v>713797</v>
       </c>
+      <c r="M124" t="str">
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -5187,6 +5524,9 @@
       <c r="L125" t="str">
         <v>713803</v>
       </c>
+      <c r="M125" t="str">
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -5225,6 +5565,9 @@
       <c r="L126" t="str">
         <v>713810</v>
       </c>
+      <c r="M126" t="str">
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
@@ -5263,6 +5606,9 @@
       <c r="L127" t="str">
         <v>713827</v>
       </c>
+      <c r="M127" t="str">
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
@@ -5301,6 +5647,9 @@
       <c r="L128" t="str">
         <v>713834</v>
       </c>
+      <c r="M128" t="str">
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
@@ -5339,6 +5688,9 @@
       <c r="L129" t="str">
         <v>713841</v>
       </c>
+      <c r="M129" t="str">
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
@@ -5377,6 +5729,9 @@
       <c r="L130" t="str">
         <v>713858</v>
       </c>
+      <c r="M130" t="str">
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
@@ -5415,6 +5770,9 @@
       <c r="L131" t="str">
         <v>713865</v>
       </c>
+      <c r="M131" t="str">
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -5453,6 +5811,9 @@
       <c r="L132" t="str">
         <v>436696</v>
       </c>
+      <c r="M132" t="str">
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -5491,6 +5852,9 @@
       <c r="L133" t="str">
         <v>436702</v>
       </c>
+      <c r="M133" t="str">
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -5529,6 +5893,9 @@
       <c r="L134" t="str">
         <v>436719</v>
       </c>
+      <c r="M134" t="str">
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -5567,6 +5934,9 @@
       <c r="L135" t="str">
         <v>436726</v>
       </c>
+      <c r="M135" t="str">
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
@@ -5605,6 +5975,9 @@
       <c r="L136" t="str">
         <v>436733</v>
       </c>
+      <c r="M136" t="str">
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
@@ -5643,6 +6016,9 @@
       <c r="L137" t="str">
         <v>436740</v>
       </c>
+      <c r="M137" t="str">
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
@@ -5681,6 +6057,9 @@
       <c r="L138" t="str">
         <v>436757</v>
       </c>
+      <c r="M138" t="str">
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
@@ -5719,6 +6098,9 @@
       <c r="L139" t="str">
         <v>436764</v>
       </c>
+      <c r="M139" t="str">
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
@@ -5757,6 +6139,9 @@
       <c r="L140" t="str">
         <v>436771</v>
       </c>
+      <c r="M140" t="str">
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
@@ -5795,6 +6180,9 @@
       <c r="L141" t="str">
         <v>436788</v>
       </c>
+      <c r="M141" t="str">
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
@@ -5833,6 +6221,9 @@
       <c r="L142" t="str">
         <v>714053</v>
       </c>
+      <c r="M142" t="str">
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
@@ -5871,6 +6262,9 @@
       <c r="L143" t="str">
         <v>714060</v>
       </c>
+      <c r="M143" t="str">
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
@@ -5909,6 +6303,9 @@
       <c r="L144" t="str">
         <v>714077</v>
       </c>
+      <c r="M144" t="str">
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
@@ -5947,6 +6344,9 @@
       <c r="L145" t="str">
         <v>714084</v>
       </c>
+      <c r="M145" t="str">
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
@@ -5985,6 +6385,9 @@
       <c r="L146" t="str">
         <v>714091</v>
       </c>
+      <c r="M146" t="str">
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
@@ -6023,6 +6426,9 @@
       <c r="L147" t="str">
         <v>714107</v>
       </c>
+      <c r="M147" t="str">
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
@@ -6061,6 +6467,9 @@
       <c r="L148" t="str">
         <v>714114</v>
       </c>
+      <c r="M148" t="str">
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
@@ -6099,6 +6508,9 @@
       <c r="L149" t="str">
         <v>714121</v>
       </c>
+      <c r="M149" t="str">
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
@@ -6137,6 +6549,9 @@
       <c r="L150" t="str">
         <v>714138</v>
       </c>
+      <c r="M150" t="str">
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
@@ -6175,6 +6590,9 @@
       <c r="L151" t="str">
         <v>714145</v>
       </c>
+      <c r="M151" t="str">
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
@@ -6213,6 +6631,9 @@
       <c r="L152" t="str">
         <v>436795</v>
       </c>
+      <c r="M152" t="str">
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
@@ -6251,6 +6672,9 @@
       <c r="L153" t="str">
         <v>436801</v>
       </c>
+      <c r="M153" t="str">
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
@@ -6289,6 +6713,9 @@
       <c r="L154" t="str">
         <v>436818</v>
       </c>
+      <c r="M154" t="str">
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
@@ -6327,6 +6754,9 @@
       <c r="L155" t="str">
         <v>436825</v>
       </c>
+      <c r="M155" t="str">
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
@@ -6365,6 +6795,9 @@
       <c r="L156" t="str">
         <v>436832</v>
       </c>
+      <c r="M156" t="str">
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
@@ -6403,6 +6836,9 @@
       <c r="L157" t="str">
         <v>436849</v>
       </c>
+      <c r="M157" t="str">
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
@@ -6441,6 +6877,9 @@
       <c r="L158" t="str">
         <v>436856</v>
       </c>
+      <c r="M158" t="str">
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
@@ -6479,6 +6918,9 @@
       <c r="L159" t="str">
         <v>436863</v>
       </c>
+      <c r="M159" t="str">
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
@@ -6517,6 +6959,9 @@
       <c r="L160" t="str">
         <v>436870</v>
       </c>
+      <c r="M160" t="str">
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
@@ -6555,6 +7000,9 @@
       <c r="L161" t="str">
         <v>436887</v>
       </c>
+      <c r="M161" t="str">
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
@@ -6593,6 +7041,9 @@
       <c r="L162" t="str">
         <v>105158</v>
       </c>
+      <c r="M162" t="str">
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
@@ -6631,6 +7082,9 @@
       <c r="L163" t="str">
         <v>105165</v>
       </c>
+      <c r="M163" t="str">
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
@@ -6669,6 +7123,9 @@
       <c r="L164" t="str">
         <v>105172</v>
       </c>
+      <c r="M164" t="str">
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
@@ -6707,6 +7164,9 @@
       <c r="L165" t="str">
         <v>624543</v>
       </c>
+      <c r="M165" t="str">
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
@@ -6745,6 +7205,9 @@
       <c r="L166" t="str">
         <v>624550</v>
       </c>
+      <c r="M166" t="str">
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
@@ -6783,6 +7246,9 @@
       <c r="L167" t="str">
         <v>624567</v>
       </c>
+      <c r="M167" t="str">
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
@@ -6821,6 +7287,9 @@
       <c r="L168" t="str">
         <v>624604</v>
       </c>
+      <c r="M168" t="str">
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
@@ -6859,6 +7328,9 @@
       <c r="L169" t="str">
         <v>105219</v>
       </c>
+      <c r="M169" t="str">
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
@@ -6897,6 +7369,9 @@
       <c r="L170" t="str">
         <v>105226</v>
       </c>
+      <c r="M170" t="str">
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
@@ -6935,6 +7410,9 @@
       <c r="L171" t="str">
         <v>105233</v>
       </c>
+      <c r="M171" t="str">
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
@@ -6973,6 +7451,9 @@
       <c r="L172" t="str">
         <v>624727</v>
       </c>
+      <c r="M172" t="str">
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
@@ -7011,6 +7492,9 @@
       <c r="L173" t="str">
         <v>624734</v>
       </c>
+      <c r="M173" t="str">
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
@@ -7049,6 +7533,9 @@
       <c r="L174" t="str">
         <v>624741</v>
       </c>
+      <c r="M174" t="str">
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
@@ -7087,6 +7574,9 @@
       <c r="L175" t="str">
         <v>624765</v>
       </c>
+      <c r="M175" t="str">
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
@@ -7125,6 +7615,9 @@
       <c r="L176" t="str">
         <v>105240</v>
       </c>
+      <c r="M176" t="str">
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
@@ -7163,6 +7656,9 @@
       <c r="L177" t="str">
         <v>105257</v>
       </c>
+      <c r="M177" t="str">
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
@@ -7201,6 +7697,9 @@
       <c r="L178" t="str">
         <v>105264</v>
       </c>
+      <c r="M178" t="str">
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
@@ -7239,6 +7738,9 @@
       <c r="L179" t="str">
         <v>624772</v>
       </c>
+      <c r="M179" t="str">
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
@@ -7277,6 +7779,9 @@
       <c r="L180" t="str">
         <v>624789</v>
       </c>
+      <c r="M180" t="str">
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
@@ -7315,6 +7820,9 @@
       <c r="L181" t="str">
         <v>624796</v>
       </c>
+      <c r="M181" t="str">
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
@@ -7353,6 +7861,9 @@
       <c r="L182" t="str">
         <v>624802</v>
       </c>
+      <c r="M182" t="str">
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
@@ -7391,6 +7902,9 @@
       <c r="L183" t="str">
         <v>105332</v>
       </c>
+      <c r="M183" t="str">
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
@@ -7429,6 +7943,9 @@
       <c r="L184" t="str">
         <v>105349</v>
       </c>
+      <c r="M184" t="str">
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
@@ -7467,6 +7984,9 @@
       <c r="L185" t="str">
         <v>105356</v>
       </c>
+      <c r="M185" t="str">
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
@@ -7505,6 +8025,9 @@
       <c r="L186" t="str">
         <v>624901</v>
       </c>
+      <c r="M186" t="str">
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
@@ -7543,6 +8066,9 @@
       <c r="L187" t="str">
         <v>624918</v>
       </c>
+      <c r="M187" t="str">
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
@@ -7581,6 +8107,9 @@
       <c r="L188" t="str">
         <v>624925</v>
       </c>
+      <c r="M188" t="str">
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
@@ -7619,6 +8148,9 @@
       <c r="L189" t="str">
         <v>624932</v>
       </c>
+      <c r="M189" t="str">
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
@@ -7657,6 +8189,9 @@
       <c r="L190" t="str">
         <v>105363</v>
       </c>
+      <c r="M190" t="str">
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
@@ -7695,6 +8230,9 @@
       <c r="L191" t="str">
         <v>105370</v>
       </c>
+      <c r="M191" t="str">
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
@@ -7733,6 +8271,9 @@
       <c r="L192" t="str">
         <v>105387</v>
       </c>
+      <c r="M192" t="str">
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
@@ -7771,6 +8312,9 @@
       <c r="L193" t="str">
         <v>624949</v>
       </c>
+      <c r="M193" t="str">
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
@@ -7809,6 +8353,9 @@
       <c r="L194" t="str">
         <v>624956</v>
       </c>
+      <c r="M194" t="str">
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
@@ -7847,6 +8394,9 @@
       <c r="L195" t="str">
         <v>624963</v>
       </c>
+      <c r="M195" t="str">
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
@@ -7885,6 +8435,9 @@
       <c r="L196" t="str">
         <v>624970</v>
       </c>
+      <c r="M196" t="str">
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
@@ -7923,6 +8476,9 @@
       <c r="L197" t="str">
         <v>105394</v>
       </c>
+      <c r="M197" t="str">
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
@@ -7961,6 +8517,9 @@
       <c r="L198" t="str">
         <v>105400</v>
       </c>
+      <c r="M198" t="str">
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
@@ -7999,6 +8558,9 @@
       <c r="L199" t="str">
         <v>105417</v>
       </c>
+      <c r="M199" t="str">
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
@@ -8037,6 +8599,9 @@
       <c r="L200" t="str">
         <v>624987</v>
       </c>
+      <c r="M200" t="str">
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
@@ -8075,6 +8640,9 @@
       <c r="L201" t="str">
         <v>624994</v>
       </c>
+      <c r="M201" t="str">
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
@@ -8113,6 +8681,9 @@
       <c r="L202" t="str">
         <v>625007</v>
       </c>
+      <c r="M202" t="str">
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
@@ -8151,6 +8722,9 @@
       <c r="L203" t="str">
         <v>625014</v>
       </c>
+      <c r="M203" t="str">
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
@@ -8189,6 +8763,9 @@
       <c r="L204" t="str">
         <v>105424</v>
       </c>
+      <c r="M204" t="str">
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
@@ -8227,6 +8804,9 @@
       <c r="L205" t="str">
         <v>105431</v>
       </c>
+      <c r="M205" t="str">
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
@@ -8265,6 +8845,9 @@
       <c r="L206" t="str">
         <v>105448</v>
       </c>
+      <c r="M206" t="str">
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
@@ -8303,6 +8886,9 @@
       <c r="L207" t="str">
         <v>625021</v>
       </c>
+      <c r="M207" t="str">
+        <v/>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
@@ -8341,6 +8927,9 @@
       <c r="L208" t="str">
         <v>625038</v>
       </c>
+      <c r="M208" t="str">
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
@@ -8379,6 +8968,9 @@
       <c r="L209" t="str">
         <v>625045</v>
       </c>
+      <c r="M209" t="str">
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
@@ -8417,6 +9009,9 @@
       <c r="L210" t="str">
         <v>625052</v>
       </c>
+      <c r="M210" t="str">
+        <v/>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
@@ -8455,6 +9050,9 @@
       <c r="L211" t="str">
         <v>105455</v>
       </c>
+      <c r="M211" t="str">
+        <v/>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
@@ -8493,6 +9091,9 @@
       <c r="L212" t="str">
         <v>105462</v>
       </c>
+      <c r="M212" t="str">
+        <v/>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
@@ -8531,6 +9132,9 @@
       <c r="L213" t="str">
         <v>105479</v>
       </c>
+      <c r="M213" t="str">
+        <v/>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
@@ -8569,6 +9173,9 @@
       <c r="L214" t="str">
         <v>625069</v>
       </c>
+      <c r="M214" t="str">
+        <v/>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
@@ -8607,6 +9214,9 @@
       <c r="L215" t="str">
         <v>625076</v>
       </c>
+      <c r="M215" t="str">
+        <v/>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
@@ -8645,6 +9255,9 @@
       <c r="L216" t="str">
         <v>625083</v>
       </c>
+      <c r="M216" t="str">
+        <v/>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
@@ -8683,6 +9296,9 @@
       <c r="L217" t="str">
         <v>625090</v>
       </c>
+      <c r="M217" t="str">
+        <v/>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
@@ -8721,6 +9337,9 @@
       <c r="L218" t="str">
         <v>105486</v>
       </c>
+      <c r="M218" t="str">
+        <v/>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
@@ -8759,6 +9378,9 @@
       <c r="L219" t="str">
         <v>105493</v>
       </c>
+      <c r="M219" t="str">
+        <v/>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
@@ -8797,6 +9419,9 @@
       <c r="L220" t="str">
         <v>105509</v>
       </c>
+      <c r="M220" t="str">
+        <v/>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
@@ -8835,6 +9460,9 @@
       <c r="L221" t="str">
         <v>625106</v>
       </c>
+      <c r="M221" t="str">
+        <v/>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
@@ -8873,6 +9501,9 @@
       <c r="L222" t="str">
         <v>625113</v>
       </c>
+      <c r="M222" t="str">
+        <v/>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
@@ -8911,6 +9542,9 @@
       <c r="L223" t="str">
         <v>625120</v>
       </c>
+      <c r="M223" t="str">
+        <v/>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
@@ -8949,6 +9583,9 @@
       <c r="L224" t="str">
         <v>625137</v>
       </c>
+      <c r="M224" t="str">
+        <v/>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
@@ -8987,6 +9624,9 @@
       <c r="L225" t="str">
         <v>105516</v>
       </c>
+      <c r="M225" t="str">
+        <v/>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
@@ -9025,6 +9665,9 @@
       <c r="L226" t="str">
         <v>105523</v>
       </c>
+      <c r="M226" t="str">
+        <v/>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
@@ -9063,6 +9706,9 @@
       <c r="L227" t="str">
         <v>105530</v>
       </c>
+      <c r="M227" t="str">
+        <v/>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
@@ -9101,6 +9747,9 @@
       <c r="L228" t="str">
         <v>625144</v>
       </c>
+      <c r="M228" t="str">
+        <v/>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
@@ -9139,6 +9788,9 @@
       <c r="L229" t="str">
         <v>625151</v>
       </c>
+      <c r="M229" t="str">
+        <v/>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
@@ -9177,6 +9829,9 @@
       <c r="L230" t="str">
         <v>625168</v>
       </c>
+      <c r="M230" t="str">
+        <v/>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
@@ -9215,6 +9870,9 @@
       <c r="L231" t="str">
         <v>625175</v>
       </c>
+      <c r="M231" t="str">
+        <v/>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
@@ -9253,6 +9911,9 @@
       <c r="L232" t="str">
         <v>105578</v>
       </c>
+      <c r="M232" t="str">
+        <v/>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
@@ -9291,6 +9952,9 @@
       <c r="L233" t="str">
         <v>105585</v>
       </c>
+      <c r="M233" t="str">
+        <v/>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
@@ -9329,6 +9993,9 @@
       <c r="L234" t="str">
         <v>105592</v>
       </c>
+      <c r="M234" t="str">
+        <v/>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
@@ -9367,6 +10034,9 @@
       <c r="L235" t="str">
         <v>625229</v>
       </c>
+      <c r="M235" t="str">
+        <v/>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
@@ -9405,6 +10075,9 @@
       <c r="L236" t="str">
         <v>625236</v>
       </c>
+      <c r="M236" t="str">
+        <v/>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
@@ -9443,6 +10116,9 @@
       <c r="L237" t="str">
         <v>625243</v>
       </c>
+      <c r="M237" t="str">
+        <v/>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
@@ -9481,6 +10157,9 @@
       <c r="L238" t="str">
         <v>625250</v>
       </c>
+      <c r="M238" t="str">
+        <v/>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
@@ -9519,6 +10198,9 @@
       <c r="L239" t="str">
         <v>996084</v>
       </c>
+      <c r="M239" t="str">
+        <v/>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
@@ -9557,6 +10239,9 @@
       <c r="L240" t="str">
         <v>996107</v>
       </c>
+      <c r="M240" t="str">
+        <v/>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
@@ -9595,6 +10280,9 @@
       <c r="L241" t="str">
         <v>996114</v>
       </c>
+      <c r="M241" t="str">
+        <v/>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
@@ -9633,6 +10321,9 @@
       <c r="L242" t="str">
         <v>996138</v>
       </c>
+      <c r="M242" t="str">
+        <v/>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
@@ -9671,6 +10362,9 @@
       <c r="L243" t="str">
         <v>996145</v>
       </c>
+      <c r="M243" t="str">
+        <v/>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
@@ -9709,6 +10403,9 @@
       <c r="L244" t="str">
         <v>996152</v>
       </c>
+      <c r="M244" t="str">
+        <v/>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
@@ -9747,6 +10444,9 @@
       <c r="L245" t="str">
         <v>996169</v>
       </c>
+      <c r="M245" t="str">
+        <v/>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
@@ -9785,6 +10485,9 @@
       <c r="L246" t="str">
         <v>996176</v>
       </c>
+      <c r="M246" t="str">
+        <v/>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
@@ -9823,6 +10526,9 @@
       <c r="L247" t="str">
         <v>996206</v>
       </c>
+      <c r="M247" t="str">
+        <v/>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
@@ -9861,6 +10567,9 @@
       <c r="L248" t="str">
         <v>996213</v>
       </c>
+      <c r="M248" t="str">
+        <v/>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
@@ -9899,6 +10608,9 @@
       <c r="L249" t="str">
         <v>435798</v>
       </c>
+      <c r="M249" t="str">
+        <v/>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
@@ -9937,6 +10649,9 @@
       <c r="L250" t="str">
         <v>435804</v>
       </c>
+      <c r="M250" t="str">
+        <v/>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
@@ -9975,6 +10690,9 @@
       <c r="L251" t="str">
         <v>435811</v>
       </c>
+      <c r="M251" t="str">
+        <v/>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
@@ -10013,6 +10731,9 @@
       <c r="L252" t="str">
         <v>435828</v>
       </c>
+      <c r="M252" t="str">
+        <v/>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
@@ -10051,6 +10772,9 @@
       <c r="L253" t="str">
         <v>435835</v>
       </c>
+      <c r="M253" t="str">
+        <v/>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
@@ -10089,6 +10813,9 @@
       <c r="L254" t="str">
         <v>435842</v>
       </c>
+      <c r="M254" t="str">
+        <v/>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
@@ -10127,6 +10854,9 @@
       <c r="L255" t="str">
         <v>435859</v>
       </c>
+      <c r="M255" t="str">
+        <v/>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
@@ -10165,6 +10895,9 @@
       <c r="L256" t="str">
         <v>435866</v>
       </c>
+      <c r="M256" t="str">
+        <v/>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
@@ -10203,6 +10936,9 @@
       <c r="L257" t="str">
         <v>435873</v>
       </c>
+      <c r="M257" t="str">
+        <v/>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
@@ -10241,6 +10977,9 @@
       <c r="L258" t="str">
         <v>435880</v>
       </c>
+      <c r="M258" t="str">
+        <v/>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
@@ -10279,6 +11018,9 @@
       <c r="L259" t="str">
         <v>803962</v>
       </c>
+      <c r="M259" t="str">
+        <v/>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
@@ -10317,6 +11059,9 @@
       <c r="L260" t="str">
         <v>803986</v>
       </c>
+      <c r="M260" t="str">
+        <v/>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
@@ -10355,6 +11100,9 @@
       <c r="L261" t="str">
         <v>803993</v>
       </c>
+      <c r="M261" t="str">
+        <v/>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
@@ -10393,6 +11141,9 @@
       <c r="L262" t="str">
         <v>804013</v>
       </c>
+      <c r="M262" t="str">
+        <v/>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
@@ -10431,6 +11182,9 @@
       <c r="L263" t="str">
         <v>804020</v>
       </c>
+      <c r="M263" t="str">
+        <v/>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
@@ -10469,6 +11223,9 @@
       <c r="L264" t="str">
         <v>804037</v>
       </c>
+      <c r="M264" t="str">
+        <v/>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
@@ -10507,6 +11264,9 @@
       <c r="L265" t="str">
         <v>804044</v>
       </c>
+      <c r="M265" t="str">
+        <v/>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
@@ -10545,6 +11305,9 @@
       <c r="L266" t="str">
         <v>804051</v>
       </c>
+      <c r="M266" t="str">
+        <v/>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
@@ -10583,6 +11346,9 @@
       <c r="L267" t="str">
         <v>804082</v>
       </c>
+      <c r="M267" t="str">
+        <v/>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
@@ -10621,6 +11387,9 @@
       <c r="L268" t="str">
         <v>804099</v>
       </c>
+      <c r="M268" t="str">
+        <v/>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
@@ -10659,6 +11428,9 @@
       <c r="L269" t="str">
         <v>435897</v>
       </c>
+      <c r="M269" t="str">
+        <v/>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
@@ -10697,6 +11469,9 @@
       <c r="L270" t="str">
         <v>435903</v>
       </c>
+      <c r="M270" t="str">
+        <v/>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
@@ -10735,6 +11510,9 @@
       <c r="L271" t="str">
         <v>435910</v>
       </c>
+      <c r="M271" t="str">
+        <v/>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
@@ -10773,6 +11551,9 @@
       <c r="L272" t="str">
         <v>435927</v>
       </c>
+      <c r="M272" t="str">
+        <v/>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
@@ -10811,6 +11592,9 @@
       <c r="L273" t="str">
         <v>435934</v>
       </c>
+      <c r="M273" t="str">
+        <v/>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
@@ -10849,6 +11633,9 @@
       <c r="L274" t="str">
         <v>435941</v>
       </c>
+      <c r="M274" t="str">
+        <v/>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
@@ -10887,6 +11674,9 @@
       <c r="L275" t="str">
         <v>435958</v>
       </c>
+      <c r="M275" t="str">
+        <v/>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
@@ -10925,6 +11715,9 @@
       <c r="L276" t="str">
         <v>435965</v>
       </c>
+      <c r="M276" t="str">
+        <v/>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
@@ -10963,6 +11756,9 @@
       <c r="L277" t="str">
         <v>435972</v>
       </c>
+      <c r="M277" t="str">
+        <v/>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
@@ -11001,6 +11797,9 @@
       <c r="L278" t="str">
         <v>435989</v>
       </c>
+      <c r="M278" t="str">
+        <v/>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
@@ -11039,6 +11838,9 @@
       <c r="L279" t="str">
         <v>804204</v>
       </c>
+      <c r="M279" t="str">
+        <v/>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
@@ -11077,6 +11879,9 @@
       <c r="L280" t="str">
         <v>804228</v>
       </c>
+      <c r="M280" t="str">
+        <v/>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
@@ -11115,6 +11920,9 @@
       <c r="L281" t="str">
         <v>804235</v>
       </c>
+      <c r="M281" t="str">
+        <v/>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
@@ -11153,6 +11961,9 @@
       <c r="L282" t="str">
         <v>804259</v>
       </c>
+      <c r="M282" t="str">
+        <v/>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
@@ -11191,6 +12002,9 @@
       <c r="L283" t="str">
         <v>804266</v>
       </c>
+      <c r="M283" t="str">
+        <v/>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
@@ -11229,6 +12043,9 @@
       <c r="L284" t="str">
         <v>804273</v>
       </c>
+      <c r="M284" t="str">
+        <v/>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
@@ -11267,6 +12084,9 @@
       <c r="L285" t="str">
         <v>804280</v>
       </c>
+      <c r="M285" t="str">
+        <v/>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
@@ -11305,6 +12125,9 @@
       <c r="L286" t="str">
         <v>804297</v>
       </c>
+      <c r="M286" t="str">
+        <v/>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
@@ -11343,6 +12166,9 @@
       <c r="L287" t="str">
         <v>804327</v>
       </c>
+      <c r="M287" t="str">
+        <v/>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
@@ -11381,6 +12207,9 @@
       <c r="L288" t="str">
         <v>804334</v>
       </c>
+      <c r="M288" t="str">
+        <v/>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
@@ -11419,6 +12248,9 @@
       <c r="L289" t="str">
         <v>435996</v>
       </c>
+      <c r="M289" t="str">
+        <v/>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
@@ -11457,6 +12289,9 @@
       <c r="L290" t="str">
         <v>436009</v>
       </c>
+      <c r="M290" t="str">
+        <v/>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
@@ -11495,6 +12330,9 @@
       <c r="L291" t="str">
         <v>436016</v>
       </c>
+      <c r="M291" t="str">
+        <v/>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
@@ -11533,6 +12371,9 @@
       <c r="L292" t="str">
         <v>436023</v>
       </c>
+      <c r="M292" t="str">
+        <v/>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
@@ -11571,6 +12412,9 @@
       <c r="L293" t="str">
         <v>436030</v>
       </c>
+      <c r="M293" t="str">
+        <v/>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
@@ -11609,6 +12453,9 @@
       <c r="L294" t="str">
         <v>436047</v>
       </c>
+      <c r="M294" t="str">
+        <v/>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
@@ -11647,6 +12494,9 @@
       <c r="L295" t="str">
         <v>436054</v>
       </c>
+      <c r="M295" t="str">
+        <v/>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
@@ -11685,6 +12535,9 @@
       <c r="L296" t="str">
         <v>436061</v>
       </c>
+      <c r="M296" t="str">
+        <v/>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
@@ -11723,6 +12576,9 @@
       <c r="L297" t="str">
         <v>436078</v>
       </c>
+      <c r="M297" t="str">
+        <v/>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
@@ -11761,6 +12617,9 @@
       <c r="L298" t="str">
         <v>436085</v>
       </c>
+      <c r="M298" t="str">
+        <v/>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
@@ -11799,6 +12658,9 @@
       <c r="L299" t="str">
         <v>982001</v>
       </c>
+      <c r="M299" t="str">
+        <v/>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
@@ -11837,6 +12699,9 @@
       <c r="L300" t="str">
         <v>982025</v>
       </c>
+      <c r="M300" t="str">
+        <v/>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
@@ -11875,6 +12740,9 @@
       <c r="L301" t="str">
         <v>982032</v>
       </c>
+      <c r="M301" t="str">
+        <v/>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
@@ -11913,6 +12781,9 @@
       <c r="L302" t="str">
         <v>982056</v>
       </c>
+      <c r="M302" t="str">
+        <v/>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
@@ -11951,6 +12822,9 @@
       <c r="L303" t="str">
         <v>982063</v>
       </c>
+      <c r="M303" t="str">
+        <v/>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
@@ -11989,6 +12863,9 @@
       <c r="L304" t="str">
         <v>982070</v>
       </c>
+      <c r="M304" t="str">
+        <v/>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
@@ -12027,6 +12904,9 @@
       <c r="L305" t="str">
         <v>982087</v>
       </c>
+      <c r="M305" t="str">
+        <v/>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
@@ -12065,6 +12945,9 @@
       <c r="L306" t="str">
         <v>982094</v>
       </c>
+      <c r="M306" t="str">
+        <v/>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
@@ -12103,6 +12986,9 @@
       <c r="L307" t="str">
         <v>982124</v>
       </c>
+      <c r="M307" t="str">
+        <v/>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
@@ -12141,6 +13027,9 @@
       <c r="L308" t="str">
         <v>982131</v>
       </c>
+      <c r="M308" t="str">
+        <v/>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
@@ -12179,6 +13068,9 @@
       <c r="L309" t="str">
         <v>436092</v>
       </c>
+      <c r="M309" t="str">
+        <v/>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
@@ -12217,6 +13109,9 @@
       <c r="L310" t="str">
         <v>436108</v>
       </c>
+      <c r="M310" t="str">
+        <v/>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
@@ -12255,6 +13150,9 @@
       <c r="L311" t="str">
         <v>436115</v>
       </c>
+      <c r="M311" t="str">
+        <v/>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
@@ -12293,6 +13191,9 @@
       <c r="L312" t="str">
         <v>436122</v>
       </c>
+      <c r="M312" t="str">
+        <v/>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
@@ -12331,6 +13232,9 @@
       <c r="L313" t="str">
         <v>436139</v>
       </c>
+      <c r="M313" t="str">
+        <v/>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
@@ -12369,6 +13273,9 @@
       <c r="L314" t="str">
         <v>436146</v>
       </c>
+      <c r="M314" t="str">
+        <v/>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
@@ -12407,6 +13314,9 @@
       <c r="L315" t="str">
         <v>436153</v>
       </c>
+      <c r="M315" t="str">
+        <v/>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
@@ -12445,6 +13355,9 @@
       <c r="L316" t="str">
         <v>436160</v>
       </c>
+      <c r="M316" t="str">
+        <v/>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
@@ -12483,6 +13396,9 @@
       <c r="L317" t="str">
         <v>436177</v>
       </c>
+      <c r="M317" t="str">
+        <v/>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
@@ -12521,6 +13437,9 @@
       <c r="L318" t="str">
         <v>436184</v>
       </c>
+      <c r="M318" t="str">
+        <v/>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
@@ -12559,6 +13478,9 @@
       <c r="L319" t="str">
         <v>768391</v>
       </c>
+      <c r="M319" t="str">
+        <v/>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
@@ -12597,6 +13519,9 @@
       <c r="L320" t="str">
         <v>768407</v>
       </c>
+      <c r="M320" t="str">
+        <v/>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
@@ -12635,6 +13560,9 @@
       <c r="L321" t="str">
         <v>768414</v>
       </c>
+      <c r="M321" t="str">
+        <v/>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
@@ -12673,6 +13601,9 @@
       <c r="L322" t="str">
         <v>768421</v>
       </c>
+      <c r="M322" t="str">
+        <v/>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
@@ -12711,6 +13642,9 @@
       <c r="L323" t="str">
         <v>768438</v>
       </c>
+      <c r="M323" t="str">
+        <v/>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
@@ -12749,6 +13683,9 @@
       <c r="L324" t="str">
         <v>768445</v>
       </c>
+      <c r="M324" t="str">
+        <v/>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
@@ -12787,6 +13724,9 @@
       <c r="L325" t="str">
         <v>768452</v>
       </c>
+      <c r="M325" t="str">
+        <v/>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
@@ -12825,6 +13765,9 @@
       <c r="L326" t="str">
         <v>768469</v>
       </c>
+      <c r="M326" t="str">
+        <v/>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
@@ -12863,6 +13806,9 @@
       <c r="L327" t="str">
         <v>768476</v>
       </c>
+      <c r="M327" t="str">
+        <v/>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
@@ -12901,6 +13847,9 @@
       <c r="L328" t="str">
         <v>768483</v>
       </c>
+      <c r="M328" t="str">
+        <v/>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
@@ -12939,6 +13888,9 @@
       <c r="L329" t="str">
         <v>436498</v>
       </c>
+      <c r="M329" t="str">
+        <v/>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
@@ -12977,6 +13929,9 @@
       <c r="L330" t="str">
         <v>436504</v>
       </c>
+      <c r="M330" t="str">
+        <v/>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
@@ -13015,6 +13970,9 @@
       <c r="L331" t="str">
         <v>436511</v>
       </c>
+      <c r="M331" t="str">
+        <v/>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
@@ -13053,6 +14011,9 @@
       <c r="L332" t="str">
         <v>436528</v>
       </c>
+      <c r="M332" t="str">
+        <v/>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
@@ -13091,6 +14052,9 @@
       <c r="L333" t="str">
         <v>436535</v>
       </c>
+      <c r="M333" t="str">
+        <v/>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
@@ -13129,6 +14093,9 @@
       <c r="L334" t="str">
         <v>436542</v>
       </c>
+      <c r="M334" t="str">
+        <v/>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
@@ -13167,6 +14134,9 @@
       <c r="L335" t="str">
         <v>436559</v>
       </c>
+      <c r="M335" t="str">
+        <v/>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
@@ -13205,6 +14175,9 @@
       <c r="L336" t="str">
         <v>436566</v>
       </c>
+      <c r="M336" t="str">
+        <v/>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
@@ -13243,6 +14216,9 @@
       <c r="L337" t="str">
         <v>436573</v>
       </c>
+      <c r="M337" t="str">
+        <v/>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
@@ -13281,6 +14257,9 @@
       <c r="L338" t="str">
         <v>436580</v>
       </c>
+      <c r="M338" t="str">
+        <v/>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
@@ -13319,6 +14298,9 @@
       <c r="L339" t="str">
         <v>768650</v>
       </c>
+      <c r="M339" t="str">
+        <v/>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
@@ -13357,6 +14339,9 @@
       <c r="L340" t="str">
         <v>768667</v>
       </c>
+      <c r="M340" t="str">
+        <v/>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
@@ -13395,6 +14380,9 @@
       <c r="L341" t="str">
         <v>768674</v>
       </c>
+      <c r="M341" t="str">
+        <v/>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
@@ -13433,6 +14421,9 @@
       <c r="L342" t="str">
         <v>768681</v>
       </c>
+      <c r="M342" t="str">
+        <v/>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
@@ -13471,6 +14462,9 @@
       <c r="L343" t="str">
         <v>768698</v>
       </c>
+      <c r="M343" t="str">
+        <v/>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
@@ -13509,6 +14503,9 @@
       <c r="L344" t="str">
         <v>768704</v>
       </c>
+      <c r="M344" t="str">
+        <v/>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
@@ -13547,6 +14544,9 @@
       <c r="L345" t="str">
         <v>768711</v>
       </c>
+      <c r="M345" t="str">
+        <v/>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
@@ -13585,6 +14585,9 @@
       <c r="L346" t="str">
         <v>768728</v>
       </c>
+      <c r="M346" t="str">
+        <v/>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
@@ -13623,6 +14626,9 @@
       <c r="L347" t="str">
         <v>768735</v>
       </c>
+      <c r="M347" t="str">
+        <v/>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
@@ -13661,6 +14667,9 @@
       <c r="L348" t="str">
         <v>768742</v>
       </c>
+      <c r="M348" t="str">
+        <v/>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
@@ -13699,6 +14708,9 @@
       <c r="L349" t="str">
         <v>436597</v>
       </c>
+      <c r="M349" t="str">
+        <v/>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
@@ -13737,6 +14749,9 @@
       <c r="L350" t="str">
         <v>436603</v>
       </c>
+      <c r="M350" t="str">
+        <v/>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
@@ -13775,6 +14790,9 @@
       <c r="L351" t="str">
         <v>436610</v>
       </c>
+      <c r="M351" t="str">
+        <v/>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
@@ -13813,6 +14831,9 @@
       <c r="L352" t="str">
         <v>436627</v>
       </c>
+      <c r="M352" t="str">
+        <v/>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
@@ -13851,6 +14872,9 @@
       <c r="L353" t="str">
         <v>436634</v>
       </c>
+      <c r="M353" t="str">
+        <v/>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
@@ -13889,6 +14913,9 @@
       <c r="L354" t="str">
         <v>436641</v>
       </c>
+      <c r="M354" t="str">
+        <v/>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
@@ -13927,6 +14954,9 @@
       <c r="L355" t="str">
         <v>436658</v>
       </c>
+      <c r="M355" t="str">
+        <v/>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
@@ -13965,6 +14995,9 @@
       <c r="L356" t="str">
         <v>436665</v>
       </c>
+      <c r="M356" t="str">
+        <v/>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
@@ -14003,6 +15036,9 @@
       <c r="L357" t="str">
         <v>436672</v>
       </c>
+      <c r="M357" t="str">
+        <v/>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
@@ -14041,6 +15077,9 @@
       <c r="L358" t="str">
         <v>436689</v>
       </c>
+      <c r="M358" t="str">
+        <v/>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
@@ -14079,6 +15118,9 @@
       <c r="L359" t="str">
         <v>972194</v>
       </c>
+      <c r="M359" t="str">
+        <v/>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
@@ -14117,6 +15159,9 @@
       <c r="L360" t="str">
         <v>972217</v>
       </c>
+      <c r="M360" t="str">
+        <v/>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
@@ -14155,6 +15200,9 @@
       <c r="L361" t="str">
         <v>972224</v>
       </c>
+      <c r="M361" t="str">
+        <v/>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
@@ -14193,6 +15241,9 @@
       <c r="L362" t="str">
         <v>972248</v>
       </c>
+      <c r="M362" t="str">
+        <v/>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
@@ -14231,6 +15282,9 @@
       <c r="L363" t="str">
         <v>972255</v>
       </c>
+      <c r="M363" t="str">
+        <v/>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
@@ -14269,6 +15323,9 @@
       <c r="L364" t="str">
         <v>972262</v>
       </c>
+      <c r="M364" t="str">
+        <v/>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
@@ -14307,6 +15364,9 @@
       <c r="L365" t="str">
         <v>972279</v>
       </c>
+      <c r="M365" t="str">
+        <v/>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
@@ -14345,6 +15405,9 @@
       <c r="L366" t="str">
         <v>972286</v>
       </c>
+      <c r="M366" t="str">
+        <v/>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
@@ -14383,6 +15446,9 @@
       <c r="L367" t="str">
         <v>972316</v>
       </c>
+      <c r="M367" t="str">
+        <v/>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
@@ -14421,6 +15487,9 @@
       <c r="L368" t="str">
         <v>972323</v>
       </c>
+      <c r="M368" t="str">
+        <v/>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
@@ -14459,6 +15528,9 @@
       <c r="L369" t="str">
         <v>436191</v>
       </c>
+      <c r="M369" t="str">
+        <v/>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
@@ -14497,6 +15569,9 @@
       <c r="L370" t="str">
         <v>436207</v>
       </c>
+      <c r="M370" t="str">
+        <v/>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
@@ -14535,6 +15610,9 @@
       <c r="L371" t="str">
         <v>436214</v>
       </c>
+      <c r="M371" t="str">
+        <v/>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
@@ -14573,6 +15651,9 @@
       <c r="L372" t="str">
         <v>436221</v>
       </c>
+      <c r="M372" t="str">
+        <v/>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
@@ -14611,6 +15692,9 @@
       <c r="L373" t="str">
         <v>436238</v>
       </c>
+      <c r="M373" t="str">
+        <v/>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
@@ -14649,6 +15733,9 @@
       <c r="L374" t="str">
         <v>436245</v>
       </c>
+      <c r="M374" t="str">
+        <v/>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
@@ -14687,6 +15774,9 @@
       <c r="L375" t="str">
         <v>436252</v>
       </c>
+      <c r="M375" t="str">
+        <v/>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
@@ -14725,6 +15815,9 @@
       <c r="L376" t="str">
         <v>436269</v>
       </c>
+      <c r="M376" t="str">
+        <v/>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
@@ -14763,6 +15856,9 @@
       <c r="L377" t="str">
         <v>436276</v>
       </c>
+      <c r="M377" t="str">
+        <v/>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
@@ -14801,6 +15897,9 @@
       <c r="L378" t="str">
         <v>436283</v>
       </c>
+      <c r="M378" t="str">
+        <v/>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
@@ -14839,6 +15938,9 @@
       <c r="L379" t="str">
         <v>972422</v>
       </c>
+      <c r="M379" t="str">
+        <v/>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
@@ -14877,6 +15979,9 @@
       <c r="L380" t="str">
         <v>972446</v>
       </c>
+      <c r="M380" t="str">
+        <v/>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
@@ -14915,6 +16020,9 @@
       <c r="L381" t="str">
         <v>972453</v>
       </c>
+      <c r="M381" t="str">
+        <v/>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
@@ -14953,6 +16061,9 @@
       <c r="L382" t="str">
         <v>972477</v>
       </c>
+      <c r="M382" t="str">
+        <v/>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
@@ -14991,6 +16102,9 @@
       <c r="L383" t="str">
         <v>972484</v>
       </c>
+      <c r="M383" t="str">
+        <v/>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
@@ -15029,6 +16143,9 @@
       <c r="L384" t="str">
         <v>972491</v>
       </c>
+      <c r="M384" t="str">
+        <v/>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
@@ -15067,6 +16184,9 @@
       <c r="L385" t="str">
         <v>972507</v>
       </c>
+      <c r="M385" t="str">
+        <v/>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
@@ -15105,6 +16225,9 @@
       <c r="L386" t="str">
         <v>972514</v>
       </c>
+      <c r="M386" t="str">
+        <v/>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
@@ -15143,6 +16266,9 @@
       <c r="L387" t="str">
         <v>972545</v>
       </c>
+      <c r="M387" t="str">
+        <v/>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
@@ -15181,6 +16307,9 @@
       <c r="L388" t="str">
         <v>972552</v>
       </c>
+      <c r="M388" t="str">
+        <v/>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
@@ -15219,6 +16348,9 @@
       <c r="L389" t="str">
         <v>436290</v>
       </c>
+      <c r="M389" t="str">
+        <v/>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
@@ -15257,6 +16389,9 @@
       <c r="L390" t="str">
         <v>436306</v>
       </c>
+      <c r="M390" t="str">
+        <v/>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
@@ -15295,6 +16430,9 @@
       <c r="L391" t="str">
         <v>436313</v>
       </c>
+      <c r="M391" t="str">
+        <v/>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
@@ -15333,6 +16471,9 @@
       <c r="L392" t="str">
         <v>436320</v>
       </c>
+      <c r="M392" t="str">
+        <v/>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
@@ -15371,6 +16512,9 @@
       <c r="L393" t="str">
         <v>436337</v>
       </c>
+      <c r="M393" t="str">
+        <v/>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
@@ -15409,6 +16553,9 @@
       <c r="L394" t="str">
         <v>436344</v>
       </c>
+      <c r="M394" t="str">
+        <v/>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
@@ -15447,6 +16594,9 @@
       <c r="L395" t="str">
         <v>436351</v>
       </c>
+      <c r="M395" t="str">
+        <v/>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
@@ -15485,6 +16635,9 @@
       <c r="L396" t="str">
         <v>436368</v>
       </c>
+      <c r="M396" t="str">
+        <v/>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
@@ -15523,6 +16676,9 @@
       <c r="L397" t="str">
         <v>436375</v>
       </c>
+      <c r="M397" t="str">
+        <v/>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
@@ -15561,6 +16717,9 @@
       <c r="L398" t="str">
         <v>436382</v>
       </c>
+      <c r="M398" t="str">
+        <v/>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
@@ -15599,6 +16758,9 @@
       <c r="L399" t="str">
         <v>972651</v>
       </c>
+      <c r="M399" t="str">
+        <v/>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
@@ -15637,6 +16799,9 @@
       <c r="L400" t="str">
         <v>972675</v>
       </c>
+      <c r="M400" t="str">
+        <v/>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
@@ -15675,6 +16840,9 @@
       <c r="L401" t="str">
         <v>972682</v>
       </c>
+      <c r="M401" t="str">
+        <v/>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
@@ -15713,6 +16881,9 @@
       <c r="L402" t="str">
         <v>972705</v>
       </c>
+      <c r="M402" t="str">
+        <v/>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
@@ -15751,6 +16922,9 @@
       <c r="L403" t="str">
         <v>972712</v>
       </c>
+      <c r="M403" t="str">
+        <v/>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
@@ -15789,6 +16963,9 @@
       <c r="L404" t="str">
         <v>972729</v>
       </c>
+      <c r="M404" t="str">
+        <v/>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
@@ -15827,6 +17004,9 @@
       <c r="L405" t="str">
         <v>972736</v>
       </c>
+      <c r="M405" t="str">
+        <v/>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
@@ -15865,6 +17045,9 @@
       <c r="L406" t="str">
         <v>972743</v>
       </c>
+      <c r="M406" t="str">
+        <v/>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
@@ -15903,6 +17086,9 @@
       <c r="L407" t="str">
         <v>972774</v>
       </c>
+      <c r="M407" t="str">
+        <v/>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
@@ -15941,6 +17127,9 @@
       <c r="L408" t="str">
         <v>972781</v>
       </c>
+      <c r="M408" t="str">
+        <v/>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
@@ -15979,6 +17168,9 @@
       <c r="L409" t="str">
         <v>436399</v>
       </c>
+      <c r="M409" t="str">
+        <v/>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
@@ -16017,6 +17209,9 @@
       <c r="L410" t="str">
         <v>436405</v>
       </c>
+      <c r="M410" t="str">
+        <v/>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
@@ -16055,6 +17250,9 @@
       <c r="L411" t="str">
         <v>436412</v>
       </c>
+      <c r="M411" t="str">
+        <v/>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
@@ -16093,6 +17291,9 @@
       <c r="L412" t="str">
         <v>436429</v>
       </c>
+      <c r="M412" t="str">
+        <v/>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
@@ -16131,6 +17332,9 @@
       <c r="L413" t="str">
         <v>436436</v>
       </c>
+      <c r="M413" t="str">
+        <v/>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
@@ -16169,6 +17373,9 @@
       <c r="L414" t="str">
         <v>436443</v>
       </c>
+      <c r="M414" t="str">
+        <v/>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
@@ -16207,6 +17414,9 @@
       <c r="L415" t="str">
         <v>436450</v>
       </c>
+      <c r="M415" t="str">
+        <v/>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
@@ -16245,6 +17455,9 @@
       <c r="L416" t="str">
         <v>436467</v>
       </c>
+      <c r="M416" t="str">
+        <v/>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
@@ -16283,6 +17496,9 @@
       <c r="L417" t="str">
         <v>436474</v>
       </c>
+      <c r="M417" t="str">
+        <v/>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
@@ -16321,6 +17537,9 @@
       <c r="L418" t="str">
         <v>436481</v>
       </c>
+      <c r="M418" t="str">
+        <v/>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
@@ -16359,6 +17578,9 @@
       <c r="L419" t="str">
         <v>105189</v>
       </c>
+      <c r="M419" t="str">
+        <v/>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
@@ -16397,6 +17619,9 @@
       <c r="L420" t="str">
         <v>105196</v>
       </c>
+      <c r="M420" t="str">
+        <v/>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
@@ -16435,6 +17660,9 @@
       <c r="L421" t="str">
         <v>105202</v>
       </c>
+      <c r="M421" t="str">
+        <v/>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
@@ -16473,6 +17701,9 @@
       <c r="L422" t="str">
         <v>624611</v>
       </c>
+      <c r="M422" t="str">
+        <v/>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
@@ -16511,6 +17742,9 @@
       <c r="L423" t="str">
         <v>624628</v>
       </c>
+      <c r="M423" t="str">
+        <v/>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
@@ -16549,6 +17783,9 @@
       <c r="L424" t="str">
         <v>624635</v>
       </c>
+      <c r="M424" t="str">
+        <v/>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
@@ -16587,6 +17824,9 @@
       <c r="L425" t="str">
         <v>624642</v>
       </c>
+      <c r="M425" t="str">
+        <v/>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
@@ -16625,6 +17865,9 @@
       <c r="L426" t="str">
         <v>105271</v>
       </c>
+      <c r="M426" t="str">
+        <v/>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
@@ -16663,6 +17906,9 @@
       <c r="L427" t="str">
         <v>105288</v>
       </c>
+      <c r="M427" t="str">
+        <v/>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
@@ -16701,6 +17947,9 @@
       <c r="L428" t="str">
         <v>105295</v>
       </c>
+      <c r="M428" t="str">
+        <v/>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
@@ -16739,6 +17988,9 @@
       <c r="L429" t="str">
         <v>624819</v>
       </c>
+      <c r="M429" t="str">
+        <v/>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
@@ -16777,6 +18029,9 @@
       <c r="L430" t="str">
         <v>624826</v>
       </c>
+      <c r="M430" t="str">
+        <v/>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
@@ -16815,6 +18070,9 @@
       <c r="L431" t="str">
         <v>624833</v>
       </c>
+      <c r="M431" t="str">
+        <v/>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
@@ -16853,6 +18111,9 @@
       <c r="L432" t="str">
         <v>624840</v>
       </c>
+      <c r="M432" t="str">
+        <v/>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
@@ -16891,6 +18152,9 @@
       <c r="L433" t="str">
         <v>105301</v>
       </c>
+      <c r="M433" t="str">
+        <v/>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
@@ -16929,6 +18193,9 @@
       <c r="L434" t="str">
         <v>105318</v>
       </c>
+      <c r="M434" t="str">
+        <v/>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
@@ -16967,6 +18234,9 @@
       <c r="L435" t="str">
         <v>105325</v>
       </c>
+      <c r="M435" t="str">
+        <v/>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
@@ -17005,6 +18275,9 @@
       <c r="L436" t="str">
         <v>624857</v>
       </c>
+      <c r="M436" t="str">
+        <v/>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
@@ -17043,6 +18316,9 @@
       <c r="L437" t="str">
         <v>624864</v>
       </c>
+      <c r="M437" t="str">
+        <v/>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
@@ -17081,6 +18357,9 @@
       <c r="L438" t="str">
         <v>624871</v>
       </c>
+      <c r="M438" t="str">
+        <v/>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
@@ -17119,6 +18398,9 @@
       <c r="L439" t="str">
         <v>624888</v>
       </c>
+      <c r="M439" t="str">
+        <v/>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
@@ -17157,6 +18439,9 @@
       <c r="L440" t="str">
         <v>105547</v>
       </c>
+      <c r="M440" t="str">
+        <v/>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
@@ -17195,6 +18480,9 @@
       <c r="L441" t="str">
         <v>105554</v>
       </c>
+      <c r="M441" t="str">
+        <v/>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
@@ -17233,6 +18521,9 @@
       <c r="L442" t="str">
         <v>105561</v>
       </c>
+      <c r="M442" t="str">
+        <v/>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
@@ -17271,6 +18562,9 @@
       <c r="L443" t="str">
         <v>625182</v>
       </c>
+      <c r="M443" t="str">
+        <v/>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
@@ -17309,6 +18603,9 @@
       <c r="L444" t="str">
         <v>625199</v>
       </c>
+      <c r="M444" t="str">
+        <v/>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
@@ -17347,6 +18644,9 @@
       <c r="L445" t="str">
         <v>625205</v>
       </c>
+      <c r="M445" t="str">
+        <v/>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
@@ -17385,6 +18685,9 @@
       <c r="L446" t="str">
         <v>625212</v>
       </c>
+      <c r="M446" t="str">
+        <v/>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
@@ -17423,6 +18726,9 @@
       <c r="L447" t="str">
         <v>105608</v>
       </c>
+      <c r="M447" t="str">
+        <v/>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
@@ -17461,6 +18767,9 @@
       <c r="L448" t="str">
         <v>105615</v>
       </c>
+      <c r="M448" t="str">
+        <v/>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
@@ -17499,6 +18808,9 @@
       <c r="L449" t="str">
         <v>105622</v>
       </c>
+      <c r="M449" t="str">
+        <v/>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
@@ -17537,6 +18849,9 @@
       <c r="L450" t="str">
         <v>625267</v>
       </c>
+      <c r="M450" t="str">
+        <v/>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
@@ -17575,6 +18890,9 @@
       <c r="L451" t="str">
         <v>625274</v>
       </c>
+      <c r="M451" t="str">
+        <v/>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
@@ -17613,6 +18931,9 @@
       <c r="L452" t="str">
         <v>625281</v>
       </c>
+      <c r="M452" t="str">
+        <v/>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
@@ -17651,6 +18972,9 @@
       <c r="L453" t="str">
         <v>625298</v>
       </c>
+      <c r="M453" t="str">
+        <v/>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
@@ -17689,6 +19013,9 @@
       <c r="L454" t="str">
         <v>627407</v>
       </c>
+      <c r="M454" t="str">
+        <v/>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
@@ -17727,6 +19054,9 @@
       <c r="L455" t="str">
         <v>627414</v>
       </c>
+      <c r="M455" t="str">
+        <v/>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
@@ -17765,6 +19095,9 @@
       <c r="L456" t="str">
         <v>627438</v>
       </c>
+      <c r="M456" t="str">
+        <v/>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
@@ -17803,6 +19136,9 @@
       <c r="L457" t="str">
         <v>627452</v>
       </c>
+      <c r="M457" t="str">
+        <v/>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
@@ -17841,6 +19177,9 @@
       <c r="L458" t="str">
         <v>627469</v>
       </c>
+      <c r="M458" t="str">
+        <v/>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
@@ -17879,6 +19218,9 @@
       <c r="L459" t="str">
         <v>627476</v>
       </c>
+      <c r="M459" t="str">
+        <v/>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
@@ -17917,6 +19259,9 @@
       <c r="L460" t="str">
         <v>627483</v>
       </c>
+      <c r="M460" t="str">
+        <v/>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
@@ -17955,6 +19300,9 @@
       <c r="L461" t="str">
         <v>627490</v>
       </c>
+      <c r="M461" t="str">
+        <v/>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
@@ -17993,6 +19341,9 @@
       <c r="L462" t="str">
         <v>627506</v>
       </c>
+      <c r="M462" t="str">
+        <v/>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
@@ -18031,6 +19382,9 @@
       <c r="L463" t="str">
         <v>627513</v>
       </c>
+      <c r="M463" t="str">
+        <v/>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
@@ -18069,6 +19423,9 @@
       <c r="L464" t="str">
         <v>627520</v>
       </c>
+      <c r="M464" t="str">
+        <v/>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
@@ -18107,6 +19464,9 @@
       <c r="L465" t="str">
         <v>627537</v>
       </c>
+      <c r="M465" t="str">
+        <v/>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
@@ -18145,6 +19505,9 @@
       <c r="L466" t="str">
         <v>627544</v>
       </c>
+      <c r="M466" t="str">
+        <v/>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
@@ -18183,6 +19546,9 @@
       <c r="L467" t="str">
         <v>627551</v>
       </c>
+      <c r="M467" t="str">
+        <v/>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
@@ -18221,6 +19587,9 @@
       <c r="L468" t="str">
         <v>627568</v>
       </c>
+      <c r="M468" t="str">
+        <v/>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
@@ -18259,6 +19628,9 @@
       <c r="L469" t="str">
         <v>627575</v>
       </c>
+      <c r="M469" t="str">
+        <v/>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
@@ -18297,6 +19669,9 @@
       <c r="L470" t="str">
         <v>627582</v>
       </c>
+      <c r="M470" t="str">
+        <v/>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
@@ -18335,6 +19710,9 @@
       <c r="L471" t="str">
         <v>627599</v>
       </c>
+      <c r="M471" t="str">
+        <v/>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
@@ -18373,6 +19751,9 @@
       <c r="L472" t="str">
         <v>629739</v>
       </c>
+      <c r="M472" t="str">
+        <v/>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
@@ -18411,6 +19792,9 @@
       <c r="L473" t="str">
         <v>629746</v>
       </c>
+      <c r="M473" t="str">
+        <v/>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
@@ -18449,6 +19833,9 @@
       <c r="L474" t="str">
         <v>629753</v>
       </c>
+      <c r="M474" t="str">
+        <v/>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
@@ -18487,6 +19874,9 @@
       <c r="L475" t="str">
         <v>629760</v>
       </c>
+      <c r="M475" t="str">
+        <v/>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
@@ -18525,6 +19915,9 @@
       <c r="L476" t="str">
         <v>629777</v>
       </c>
+      <c r="M476" t="str">
+        <v/>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
@@ -18563,6 +19956,9 @@
       <c r="L477" t="str">
         <v>629784</v>
       </c>
+      <c r="M477" t="str">
+        <v/>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
@@ -18601,6 +19997,9 @@
       <c r="L478" t="str">
         <v>629791</v>
       </c>
+      <c r="M478" t="str">
+        <v/>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
@@ -18639,6 +20038,9 @@
       <c r="L479" t="str">
         <v>629807</v>
       </c>
+      <c r="M479" t="str">
+        <v/>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
@@ -18677,6 +20079,9 @@
       <c r="L480" t="str">
         <v>629814</v>
       </c>
+      <c r="M480" t="str">
+        <v/>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
@@ -18715,6 +20120,9 @@
       <c r="L481" t="str">
         <v>629821</v>
       </c>
+      <c r="M481" t="str">
+        <v/>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
@@ -18753,6 +20161,9 @@
       <c r="L482" t="str">
         <v>629838</v>
       </c>
+      <c r="M482" t="str">
+        <v/>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
@@ -18791,6 +20202,9 @@
       <c r="L483" t="str">
         <v>629845</v>
       </c>
+      <c r="M483" t="str">
+        <v/>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
@@ -18829,6 +20243,9 @@
       <c r="L484" t="str">
         <v>629852</v>
       </c>
+      <c r="M484" t="str">
+        <v/>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
@@ -18867,6 +20284,9 @@
       <c r="L485" t="str">
         <v>629869</v>
       </c>
+      <c r="M485" t="str">
+        <v/>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
@@ -18905,6 +20325,9 @@
       <c r="L486" t="str">
         <v>629876</v>
       </c>
+      <c r="M486" t="str">
+        <v/>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
@@ -18943,6 +20366,9 @@
       <c r="L487" t="str">
         <v>629883</v>
       </c>
+      <c r="M487" t="str">
+        <v/>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
@@ -18981,6 +20407,9 @@
       <c r="L488" t="str">
         <v>629890</v>
       </c>
+      <c r="M488" t="str">
+        <v/>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
@@ -19019,6 +20448,9 @@
       <c r="L489" t="str">
         <v>629913</v>
       </c>
+      <c r="M489" t="str">
+        <v/>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
@@ -19057,6 +20489,9 @@
       <c r="L490" t="str">
         <v>592910</v>
       </c>
+      <c r="M490" t="str">
+        <v/>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
@@ -19095,6 +20530,9 @@
       <c r="L491" t="str">
         <v>592927</v>
       </c>
+      <c r="M491" t="str">
+        <v/>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
@@ -19133,6 +20571,9 @@
       <c r="L492" t="str">
         <v>592934</v>
       </c>
+      <c r="M492" t="str">
+        <v/>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
@@ -19171,6 +20612,9 @@
       <c r="L493" t="str">
         <v>592941</v>
       </c>
+      <c r="M493" t="str">
+        <v/>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
@@ -19209,6 +20653,9 @@
       <c r="L494" t="str">
         <v>592958</v>
       </c>
+      <c r="M494" t="str">
+        <v/>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
@@ -19247,6 +20694,9 @@
       <c r="L495" t="str">
         <v>547637</v>
       </c>
+      <c r="M495" t="str">
+        <v/>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
@@ -19285,6 +20735,9 @@
       <c r="L496" t="str">
         <v>547644</v>
       </c>
+      <c r="M496" t="str">
+        <v/>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
@@ -19323,6 +20776,9 @@
       <c r="L497" t="str">
         <v>547651</v>
       </c>
+      <c r="M497" t="str">
+        <v/>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
@@ -19361,6 +20817,9 @@
       <c r="L498" t="str">
         <v>547668</v>
       </c>
+      <c r="M498" t="str">
+        <v/>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
@@ -19399,6 +20858,9 @@
       <c r="L499" t="str">
         <v>547675</v>
       </c>
+      <c r="M499" t="str">
+        <v/>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
@@ -19437,6 +20899,9 @@
       <c r="L500" t="str">
         <v>547682</v>
       </c>
+      <c r="M500" t="str">
+        <v/>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
@@ -19475,6 +20940,9 @@
       <c r="L501" t="str">
         <v>547699</v>
       </c>
+      <c r="M501" t="str">
+        <v/>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
@@ -19513,6 +20981,9 @@
       <c r="L502" t="str">
         <v>547705</v>
       </c>
+      <c r="M502" t="str">
+        <v/>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
@@ -19551,6 +21022,9 @@
       <c r="L503" t="str">
         <v>547712</v>
       </c>
+      <c r="M503" t="str">
+        <v/>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
@@ -19589,6 +21063,9 @@
       <c r="L504" t="str">
         <v>547729</v>
       </c>
+      <c r="M504" t="str">
+        <v/>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
@@ -19627,6 +21104,9 @@
       <c r="L505" t="str">
         <v>547736</v>
       </c>
+      <c r="M505" t="str">
+        <v/>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
@@ -19665,6 +21145,9 @@
       <c r="L506" t="str">
         <v>547743</v>
       </c>
+      <c r="M506" t="str">
+        <v/>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
@@ -19703,6 +21186,9 @@
       <c r="L507" t="str">
         <v>547750</v>
       </c>
+      <c r="M507" t="str">
+        <v/>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
@@ -19741,6 +21227,9 @@
       <c r="L508" t="str">
         <v>547767</v>
       </c>
+      <c r="M508" t="str">
+        <v/>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
@@ -19779,6 +21268,9 @@
       <c r="L509" t="str">
         <v>547774</v>
       </c>
+      <c r="M509" t="str">
+        <v/>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
@@ -19817,6 +21309,9 @@
       <c r="L510" t="str">
         <v>547781</v>
       </c>
+      <c r="M510" t="str">
+        <v/>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
@@ -19855,6 +21350,9 @@
       <c r="L511" t="str">
         <v>547798</v>
       </c>
+      <c r="M511" t="str">
+        <v/>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
@@ -19893,6 +21391,9 @@
       <c r="L512" t="str">
         <v>547804</v>
       </c>
+      <c r="M512" t="str">
+        <v/>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
@@ -19931,6 +21432,9 @@
       <c r="L513" t="str">
         <v>547811</v>
       </c>
+      <c r="M513" t="str">
+        <v/>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
@@ -19969,6 +21473,9 @@
       <c r="L514" t="str">
         <v>547828</v>
       </c>
+      <c r="M514" t="str">
+        <v/>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
@@ -20007,6 +21514,9 @@
       <c r="L515" t="str">
         <v>592965</v>
       </c>
+      <c r="M515" t="str">
+        <v/>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
@@ -20045,6 +21555,9 @@
       <c r="L516" t="str">
         <v>592972</v>
       </c>
+      <c r="M516" t="str">
+        <v/>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
@@ -20083,6 +21596,9 @@
       <c r="L517" t="str">
         <v>592989</v>
       </c>
+      <c r="M517" t="str">
+        <v/>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
@@ -20121,6 +21637,9 @@
       <c r="L518" t="str">
         <v>592996</v>
       </c>
+      <c r="M518" t="str">
+        <v/>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
@@ -20159,6 +21678,9 @@
       <c r="L519" t="str">
         <v>593009</v>
       </c>
+      <c r="M519" t="str">
+        <v/>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
@@ -20197,6 +21719,9 @@
       <c r="L520" t="str">
         <v>547835</v>
       </c>
+      <c r="M520" t="str">
+        <v/>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
@@ -20235,6 +21760,9 @@
       <c r="L521" t="str">
         <v>547842</v>
       </c>
+      <c r="M521" t="str">
+        <v/>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
@@ -20273,6 +21801,9 @@
       <c r="L522" t="str">
         <v>547859</v>
       </c>
+      <c r="M522" t="str">
+        <v/>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
@@ -20311,6 +21842,9 @@
       <c r="L523" t="str">
         <v>547866</v>
       </c>
+      <c r="M523" t="str">
+        <v/>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
@@ -20349,6 +21883,9 @@
       <c r="L524" t="str">
         <v>547873</v>
       </c>
+      <c r="M524" t="str">
+        <v/>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
@@ -20387,6 +21924,9 @@
       <c r="L525" t="str">
         <v>547880</v>
       </c>
+      <c r="M525" t="str">
+        <v/>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
@@ -20425,6 +21965,9 @@
       <c r="L526" t="str">
         <v>547897</v>
       </c>
+      <c r="M526" t="str">
+        <v/>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
@@ -20463,6 +22006,9 @@
       <c r="L527" t="str">
         <v>547903</v>
       </c>
+      <c r="M527" t="str">
+        <v/>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
@@ -20501,6 +22047,9 @@
       <c r="L528" t="str">
         <v>547910</v>
       </c>
+      <c r="M528" t="str">
+        <v/>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
@@ -20539,6 +22088,9 @@
       <c r="L529" t="str">
         <v>547927</v>
       </c>
+      <c r="M529" t="str">
+        <v/>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
@@ -20577,6 +22129,9 @@
       <c r="L530" t="str">
         <v>547934</v>
       </c>
+      <c r="M530" t="str">
+        <v/>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
@@ -20615,6 +22170,9 @@
       <c r="L531" t="str">
         <v>547941</v>
       </c>
+      <c r="M531" t="str">
+        <v/>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
@@ -20653,6 +22211,9 @@
       <c r="L532" t="str">
         <v>547958</v>
       </c>
+      <c r="M532" t="str">
+        <v/>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
@@ -20691,6 +22252,9 @@
       <c r="L533" t="str">
         <v>547965</v>
       </c>
+      <c r="M533" t="str">
+        <v/>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
@@ -20729,6 +22293,9 @@
       <c r="L534" t="str">
         <v>547972</v>
       </c>
+      <c r="M534" t="str">
+        <v/>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
@@ -20767,6 +22334,9 @@
       <c r="L535" t="str">
         <v>547989</v>
       </c>
+      <c r="M535" t="str">
+        <v/>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
@@ -20805,6 +22375,9 @@
       <c r="L536" t="str">
         <v>547996</v>
       </c>
+      <c r="M536" t="str">
+        <v/>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
@@ -20843,6 +22416,9 @@
       <c r="L537" t="str">
         <v>548009</v>
       </c>
+      <c r="M537" t="str">
+        <v/>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
@@ -20881,6 +22457,9 @@
       <c r="L538" t="str">
         <v>548016</v>
       </c>
+      <c r="M538" t="str">
+        <v/>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
@@ -20919,6 +22498,9 @@
       <c r="L539" t="str">
         <v>548023</v>
       </c>
+      <c r="M539" t="str">
+        <v/>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
@@ -20957,6 +22539,9 @@
       <c r="L540" t="str">
         <v>593016</v>
       </c>
+      <c r="M540" t="str">
+        <v/>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
@@ -20995,6 +22580,9 @@
       <c r="L541" t="str">
         <v>593023</v>
       </c>
+      <c r="M541" t="str">
+        <v/>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
@@ -21033,6 +22621,9 @@
       <c r="L542" t="str">
         <v>593030</v>
       </c>
+      <c r="M542" t="str">
+        <v/>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
@@ -21071,6 +22662,9 @@
       <c r="L543" t="str">
         <v>593047</v>
       </c>
+      <c r="M543" t="str">
+        <v/>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
@@ -21109,6 +22703,9 @@
       <c r="L544" t="str">
         <v>593054</v>
       </c>
+      <c r="M544" t="str">
+        <v/>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
@@ -21147,6 +22744,9 @@
       <c r="L545" t="str">
         <v>548030</v>
       </c>
+      <c r="M545" t="str">
+        <v/>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
@@ -21185,6 +22785,9 @@
       <c r="L546" t="str">
         <v>548047</v>
       </c>
+      <c r="M546" t="str">
+        <v/>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
@@ -21223,6 +22826,9 @@
       <c r="L547" t="str">
         <v>548054</v>
       </c>
+      <c r="M547" t="str">
+        <v/>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
@@ -21261,6 +22867,9 @@
       <c r="L548" t="str">
         <v>548061</v>
       </c>
+      <c r="M548" t="str">
+        <v/>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
@@ -21299,6 +22908,9 @@
       <c r="L549" t="str">
         <v>548078</v>
       </c>
+      <c r="M549" t="str">
+        <v/>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
@@ -21337,6 +22949,9 @@
       <c r="L550" t="str">
         <v>548122</v>
       </c>
+      <c r="M550" t="str">
+        <v/>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
@@ -21375,6 +22990,9 @@
       <c r="L551" t="str">
         <v>548139</v>
       </c>
+      <c r="M551" t="str">
+        <v/>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
@@ -21413,6 +23031,9 @@
       <c r="L552" t="str">
         <v>548146</v>
       </c>
+      <c r="M552" t="str">
+        <v/>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
@@ -21451,6 +23072,9 @@
       <c r="L553" t="str">
         <v>548153</v>
       </c>
+      <c r="M553" t="str">
+        <v/>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
@@ -21489,6 +23113,9 @@
       <c r="L554" t="str">
         <v>548160</v>
       </c>
+      <c r="M554" t="str">
+        <v/>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
@@ -21527,6 +23154,9 @@
       <c r="L555" t="str">
         <v>548177</v>
       </c>
+      <c r="M555" t="str">
+        <v/>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
@@ -21565,6 +23195,9 @@
       <c r="L556" t="str">
         <v>548184</v>
       </c>
+      <c r="M556" t="str">
+        <v/>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
@@ -21603,6 +23236,9 @@
       <c r="L557" t="str">
         <v>548191</v>
       </c>
+      <c r="M557" t="str">
+        <v/>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
@@ -21641,6 +23277,9 @@
       <c r="L558" t="str">
         <v>548207</v>
       </c>
+      <c r="M558" t="str">
+        <v/>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
@@ -21679,6 +23318,9 @@
       <c r="L559" t="str">
         <v>548214</v>
       </c>
+      <c r="M559" t="str">
+        <v/>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
@@ -21717,6 +23359,9 @@
       <c r="L560" t="str">
         <v>548221</v>
       </c>
+      <c r="M560" t="str">
+        <v/>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
@@ -21755,6 +23400,9 @@
       <c r="L561" t="str">
         <v>548238</v>
       </c>
+      <c r="M561" t="str">
+        <v/>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
@@ -21793,6 +23441,9 @@
       <c r="L562" t="str">
         <v>548245</v>
       </c>
+      <c r="M562" t="str">
+        <v/>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
@@ -21831,6 +23482,9 @@
       <c r="L563" t="str">
         <v>548962</v>
       </c>
+      <c r="M563" t="str">
+        <v/>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
@@ -21869,6 +23523,9 @@
       <c r="L564" t="str">
         <v>548979</v>
       </c>
+      <c r="M564" t="str">
+        <v/>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
@@ -21907,6 +23564,9 @@
       <c r="L565" t="str">
         <v>593108</v>
       </c>
+      <c r="M565" t="str">
+        <v/>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
@@ -21945,6 +23605,9 @@
       <c r="L566" t="str">
         <v>593115</v>
       </c>
+      <c r="M566" t="str">
+        <v/>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
@@ -21983,6 +23646,9 @@
       <c r="L567" t="str">
         <v>593122</v>
       </c>
+      <c r="M567" t="str">
+        <v/>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
@@ -22021,6 +23687,9 @@
       <c r="L568" t="str">
         <v>593139</v>
       </c>
+      <c r="M568" t="str">
+        <v/>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
@@ -22059,6 +23728,9 @@
       <c r="L569" t="str">
         <v>593146</v>
       </c>
+      <c r="M569" t="str">
+        <v/>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
@@ -22097,6 +23769,9 @@
       <c r="L570" t="str">
         <v>548986</v>
       </c>
+      <c r="M570" t="str">
+        <v/>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
@@ -22135,6 +23810,9 @@
       <c r="L571" t="str">
         <v>548993</v>
       </c>
+      <c r="M571" t="str">
+        <v/>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
@@ -22173,6 +23851,9 @@
       <c r="L572" t="str">
         <v>549006</v>
       </c>
+      <c r="M572" t="str">
+        <v/>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
@@ -22211,6 +23892,9 @@
       <c r="L573" t="str">
         <v>549013</v>
       </c>
+      <c r="M573" t="str">
+        <v/>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
@@ -22249,6 +23933,9 @@
       <c r="L574" t="str">
         <v>549020</v>
       </c>
+      <c r="M574" t="str">
+        <v/>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
@@ -22287,6 +23974,9 @@
       <c r="L575" t="str">
         <v>549037</v>
       </c>
+      <c r="M575" t="str">
+        <v/>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
@@ -22325,6 +24015,9 @@
       <c r="L576" t="str">
         <v>549044</v>
       </c>
+      <c r="M576" t="str">
+        <v/>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
@@ -22363,6 +24056,9 @@
       <c r="L577" t="str">
         <v>549051</v>
       </c>
+      <c r="M577" t="str">
+        <v/>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
@@ -22401,6 +24097,9 @@
       <c r="L578" t="str">
         <v>549068</v>
       </c>
+      <c r="M578" t="str">
+        <v/>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
@@ -22439,6 +24138,9 @@
       <c r="L579" t="str">
         <v>549075</v>
       </c>
+      <c r="M579" t="str">
+        <v/>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
@@ -22477,6 +24179,9 @@
       <c r="L580" t="str">
         <v>549082</v>
       </c>
+      <c r="M580" t="str">
+        <v/>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
@@ -22515,6 +24220,9 @@
       <c r="L581" t="str">
         <v>549099</v>
       </c>
+      <c r="M581" t="str">
+        <v/>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
@@ -22553,6 +24261,9 @@
       <c r="L582" t="str">
         <v>549105</v>
       </c>
+      <c r="M582" t="str">
+        <v/>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
@@ -22591,6 +24302,9 @@
       <c r="L583" t="str">
         <v>549112</v>
       </c>
+      <c r="M583" t="str">
+        <v/>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
@@ -22629,6 +24343,9 @@
       <c r="L584" t="str">
         <v>549129</v>
       </c>
+      <c r="M584" t="str">
+        <v/>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
@@ -22667,6 +24384,9 @@
       <c r="L585" t="str">
         <v>549136</v>
       </c>
+      <c r="M585" t="str">
+        <v/>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
@@ -22705,6 +24425,9 @@
       <c r="L586" t="str">
         <v>549143</v>
       </c>
+      <c r="M586" t="str">
+        <v/>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
@@ -22743,6 +24466,9 @@
       <c r="L587" t="str">
         <v>549150</v>
       </c>
+      <c r="M587" t="str">
+        <v/>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
@@ -22781,6 +24507,9 @@
       <c r="L588" t="str">
         <v>549167</v>
       </c>
+      <c r="M588" t="str">
+        <v/>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
@@ -22819,6 +24548,9 @@
       <c r="L589" t="str">
         <v>549174</v>
       </c>
+      <c r="M589" t="str">
+        <v/>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
@@ -22857,6 +24589,9 @@
       <c r="L590" t="str">
         <v>440303</v>
       </c>
+      <c r="M590" t="str">
+        <v/>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
@@ -22895,6 +24630,9 @@
       <c r="L591" t="str">
         <v>440310</v>
       </c>
+      <c r="M591" t="str">
+        <v/>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
@@ -22933,6 +24671,9 @@
       <c r="L592" t="str">
         <v>440327</v>
       </c>
+      <c r="M592" t="str">
+        <v/>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
@@ -22971,6 +24712,9 @@
       <c r="L593" t="str">
         <v>440334</v>
       </c>
+      <c r="M593" t="str">
+        <v/>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
@@ -23009,6 +24753,9 @@
       <c r="L594" t="str">
         <v>440341</v>
       </c>
+      <c r="M594" t="str">
+        <v/>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
@@ -23047,6 +24794,9 @@
       <c r="L595" t="str">
         <v>440358</v>
       </c>
+      <c r="M595" t="str">
+        <v/>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
@@ -23085,6 +24835,9 @@
       <c r="L596" t="str">
         <v>440365</v>
       </c>
+      <c r="M596" t="str">
+        <v/>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
@@ -23123,6 +24876,9 @@
       <c r="L597" t="str">
         <v>440372</v>
       </c>
+      <c r="M597" t="str">
+        <v/>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
@@ -23161,6 +24917,9 @@
       <c r="L598" t="str">
         <v>440389</v>
       </c>
+      <c r="M598" t="str">
+        <v/>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
@@ -23199,6 +24958,9 @@
       <c r="L599" t="str">
         <v>440396</v>
       </c>
+      <c r="M599" t="str">
+        <v/>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
@@ -23237,6 +24999,9 @@
       <c r="L600" t="str">
         <v>440402</v>
       </c>
+      <c r="M600" t="str">
+        <v/>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
@@ -23275,6 +25040,9 @@
       <c r="L601" t="str">
         <v>440419</v>
       </c>
+      <c r="M601" t="str">
+        <v/>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
@@ -23313,6 +25081,9 @@
       <c r="L602" t="str">
         <v>440426</v>
       </c>
+      <c r="M602" t="str">
+        <v/>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
@@ -23351,6 +25122,9 @@
       <c r="L603" t="str">
         <v>440433</v>
       </c>
+      <c r="M603" t="str">
+        <v/>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
@@ -23389,6 +25163,9 @@
       <c r="L604" t="str">
         <v>440440</v>
       </c>
+      <c r="M604" t="str">
+        <v/>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
@@ -23427,6 +25204,9 @@
       <c r="L605" t="str">
         <v>440457</v>
       </c>
+      <c r="M605" t="str">
+        <v/>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
@@ -23465,6 +25245,9 @@
       <c r="L606" t="str">
         <v>440464</v>
       </c>
+      <c r="M606" t="str">
+        <v/>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
@@ -23503,6 +25286,9 @@
       <c r="L607" t="str">
         <v>440471</v>
       </c>
+      <c r="M607" t="str">
+        <v/>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
@@ -23541,6 +25327,9 @@
       <c r="L608" t="str">
         <v>440488</v>
       </c>
+      <c r="M608" t="str">
+        <v/>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
@@ -23579,6 +25368,9 @@
       <c r="L609" t="str">
         <v>440495</v>
       </c>
+      <c r="M609" t="str">
+        <v/>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
@@ -23617,6 +25409,9 @@
       <c r="L610" t="str">
         <v>440501</v>
       </c>
+      <c r="M610" t="str">
+        <v/>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
@@ -23655,6 +25450,9 @@
       <c r="L611" t="str">
         <v>440518</v>
       </c>
+      <c r="M611" t="str">
+        <v/>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
@@ -23693,6 +25491,9 @@
       <c r="L612" t="str">
         <v>440525</v>
       </c>
+      <c r="M612" t="str">
+        <v/>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
@@ -23731,6 +25532,9 @@
       <c r="L613" t="str">
         <v>440532</v>
       </c>
+      <c r="M613" t="str">
+        <v/>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
@@ -23769,6 +25573,9 @@
       <c r="L614" t="str">
         <v>440549</v>
       </c>
+      <c r="M614" t="str">
+        <v/>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
@@ -23807,6 +25614,9 @@
       <c r="L615" t="str">
         <v>440556</v>
       </c>
+      <c r="M615" t="str">
+        <v/>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
@@ -23845,6 +25655,9 @@
       <c r="L616" t="str">
         <v>440563</v>
       </c>
+      <c r="M616" t="str">
+        <v/>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
@@ -23883,6 +25696,9 @@
       <c r="L617" t="str">
         <v>440570</v>
       </c>
+      <c r="M617" t="str">
+        <v/>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
@@ -23921,6 +25737,9 @@
       <c r="L618" t="str">
         <v>440587</v>
       </c>
+      <c r="M618" t="str">
+        <v/>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
@@ -23959,6 +25778,9 @@
       <c r="L619" t="str">
         <v>440594</v>
       </c>
+      <c r="M619" t="str">
+        <v/>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
@@ -23997,6 +25819,9 @@
       <c r="L620" t="str">
         <v>440600</v>
       </c>
+      <c r="M620" t="str">
+        <v/>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
@@ -24035,6 +25860,9 @@
       <c r="L621" t="str">
         <v>440617</v>
       </c>
+      <c r="M621" t="str">
+        <v/>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
@@ -24073,6 +25901,9 @@
       <c r="L622" t="str">
         <v>440624</v>
       </c>
+      <c r="M622" t="str">
+        <v/>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
@@ -24111,6 +25942,9 @@
       <c r="L623" t="str">
         <v>440631</v>
       </c>
+      <c r="M623" t="str">
+        <v/>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
@@ -24149,6 +25983,9 @@
       <c r="L624" t="str">
         <v>440648</v>
       </c>
+      <c r="M624" t="str">
+        <v/>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
@@ -24187,6 +26024,9 @@
       <c r="L625" t="str">
         <v>440655</v>
       </c>
+      <c r="M625" t="str">
+        <v/>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
@@ -24225,6 +26065,9 @@
       <c r="L626" t="str">
         <v>440662</v>
       </c>
+      <c r="M626" t="str">
+        <v/>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
@@ -24263,6 +26106,9 @@
       <c r="L627" t="str">
         <v>440679</v>
       </c>
+      <c r="M627" t="str">
+        <v/>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
@@ -24301,6 +26147,9 @@
       <c r="L628" t="str">
         <v>440686</v>
       </c>
+      <c r="M628" t="str">
+        <v/>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
@@ -24339,6 +26188,9 @@
       <c r="L629" t="str">
         <v>440693</v>
       </c>
+      <c r="M629" t="str">
+        <v/>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
@@ -24377,6 +26229,9 @@
       <c r="L630" t="str">
         <v>440709</v>
       </c>
+      <c r="M630" t="str">
+        <v/>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
@@ -24415,6 +26270,9 @@
       <c r="L631" t="str">
         <v>440716</v>
       </c>
+      <c r="M631" t="str">
+        <v/>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
@@ -24453,6 +26311,9 @@
       <c r="L632" t="str">
         <v>440723</v>
       </c>
+      <c r="M632" t="str">
+        <v/>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
@@ -24491,6 +26352,9 @@
       <c r="L633" t="str">
         <v>440730</v>
       </c>
+      <c r="M633" t="str">
+        <v/>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
@@ -24529,6 +26393,9 @@
       <c r="L634" t="str">
         <v>440747</v>
       </c>
+      <c r="M634" t="str">
+        <v/>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
@@ -24567,6 +26434,9 @@
       <c r="L635" t="str">
         <v>440754</v>
       </c>
+      <c r="M635" t="str">
+        <v/>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
@@ -24605,6 +26475,9 @@
       <c r="L636" t="str">
         <v>440761</v>
       </c>
+      <c r="M636" t="str">
+        <v/>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
@@ -24643,6 +26516,9 @@
       <c r="L637" t="str">
         <v>440778</v>
       </c>
+      <c r="M637" t="str">
+        <v/>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
@@ -24681,6 +26557,9 @@
       <c r="L638" t="str">
         <v>440785</v>
       </c>
+      <c r="M638" t="str">
+        <v/>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
@@ -24719,6 +26598,9 @@
       <c r="L639" t="str">
         <v>440792</v>
       </c>
+      <c r="M639" t="str">
+        <v/>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
@@ -24757,6 +26639,9 @@
       <c r="L640" t="str">
         <v>440808</v>
       </c>
+      <c r="M640" t="str">
+        <v/>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
@@ -24795,6 +26680,9 @@
       <c r="L641" t="str">
         <v>440815</v>
       </c>
+      <c r="M641" t="str">
+        <v/>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
@@ -24833,6 +26721,9 @@
       <c r="L642" t="str">
         <v>440822</v>
       </c>
+      <c r="M642" t="str">
+        <v/>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
@@ -24871,6 +26762,9 @@
       <c r="L643" t="str">
         <v>440839</v>
       </c>
+      <c r="M643" t="str">
+        <v/>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
@@ -24909,6 +26803,9 @@
       <c r="L644" t="str">
         <v>440846</v>
       </c>
+      <c r="M644" t="str">
+        <v/>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
@@ -24947,6 +26844,9 @@
       <c r="L645" t="str">
         <v>440853</v>
       </c>
+      <c r="M645" t="str">
+        <v/>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
@@ -24985,6 +26885,9 @@
       <c r="L646" t="str">
         <v>440860</v>
       </c>
+      <c r="M646" t="str">
+        <v/>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
@@ -25023,6 +26926,9 @@
       <c r="L647" t="str">
         <v>440877</v>
       </c>
+      <c r="M647" t="str">
+        <v/>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
@@ -25061,6 +26967,9 @@
       <c r="L648" t="str">
         <v>440884</v>
       </c>
+      <c r="M648" t="str">
+        <v/>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
@@ -25099,6 +27008,9 @@
       <c r="L649" t="str">
         <v>440891</v>
       </c>
+      <c r="M649" t="str">
+        <v/>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
@@ -25137,6 +27049,9 @@
       <c r="L650" t="str">
         <v>440907</v>
       </c>
+      <c r="M650" t="str">
+        <v/>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
@@ -25175,6 +27090,9 @@
       <c r="L651" t="str">
         <v>440914</v>
       </c>
+      <c r="M651" t="str">
+        <v/>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
@@ -25213,6 +27131,9 @@
       <c r="L652" t="str">
         <v>440921</v>
       </c>
+      <c r="M652" t="str">
+        <v/>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
@@ -25251,6 +27172,9 @@
       <c r="L653" t="str">
         <v>440938</v>
       </c>
+      <c r="M653" t="str">
+        <v/>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
@@ -25289,6 +27213,9 @@
       <c r="L654" t="str">
         <v>440945</v>
       </c>
+      <c r="M654" t="str">
+        <v/>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
@@ -25327,6 +27254,9 @@
       <c r="L655" t="str">
         <v>440952</v>
       </c>
+      <c r="M655" t="str">
+        <v/>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
@@ -25365,6 +27295,9 @@
       <c r="L656" t="str">
         <v>440969</v>
       </c>
+      <c r="M656" t="str">
+        <v/>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
@@ -25403,6 +27336,9 @@
       <c r="L657" t="str">
         <v>440976</v>
       </c>
+      <c r="M657" t="str">
+        <v/>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
@@ -25441,6 +27377,9 @@
       <c r="L658" t="str">
         <v>440983</v>
       </c>
+      <c r="M658" t="str">
+        <v/>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
@@ -25479,6 +27418,9 @@
       <c r="L659" t="str">
         <v>440990</v>
       </c>
+      <c r="M659" t="str">
+        <v/>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
@@ -25517,6 +27459,9 @@
       <c r="L660" t="str">
         <v>441003</v>
       </c>
+      <c r="M660" t="str">
+        <v/>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
@@ -25555,6 +27500,9 @@
       <c r="L661" t="str">
         <v>441010</v>
       </c>
+      <c r="M661" t="str">
+        <v/>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
@@ -25593,6 +27541,9 @@
       <c r="L662" t="str">
         <v>441027</v>
       </c>
+      <c r="M662" t="str">
+        <v/>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
@@ -25631,6 +27582,9 @@
       <c r="L663" t="str">
         <v>441034</v>
       </c>
+      <c r="M663" t="str">
+        <v/>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
@@ -25669,6 +27623,9 @@
       <c r="L664" t="str">
         <v>441041</v>
       </c>
+      <c r="M664" t="str">
+        <v/>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
@@ -25707,6 +27664,9 @@
       <c r="L665" t="str">
         <v>441058</v>
       </c>
+      <c r="M665" t="str">
+        <v/>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
@@ -25745,6 +27705,9 @@
       <c r="L666" t="str">
         <v>441065</v>
       </c>
+      <c r="M666" t="str">
+        <v/>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
@@ -25783,6 +27746,9 @@
       <c r="L667" t="str">
         <v>441072</v>
       </c>
+      <c r="M667" t="str">
+        <v/>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
@@ -25821,6 +27787,9 @@
       <c r="L668" t="str">
         <v>441089</v>
       </c>
+      <c r="M668" t="str">
+        <v/>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
@@ -25859,6 +27828,9 @@
       <c r="L669" t="str">
         <v>441096</v>
       </c>
+      <c r="M669" t="str">
+        <v/>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
@@ -25897,6 +27869,9 @@
       <c r="L670" t="str">
         <v>441102</v>
       </c>
+      <c r="M670" t="str">
+        <v/>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
@@ -25935,6 +27910,9 @@
       <c r="L671" t="str">
         <v>441119</v>
       </c>
+      <c r="M671" t="str">
+        <v/>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
@@ -25973,6 +27951,9 @@
       <c r="L672" t="str">
         <v>441126</v>
       </c>
+      <c r="M672" t="str">
+        <v/>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
@@ -26011,6 +27992,9 @@
       <c r="L673" t="str">
         <v>441133</v>
       </c>
+      <c r="M673" t="str">
+        <v/>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
@@ -26049,6 +28033,9 @@
       <c r="L674" t="str">
         <v>441140</v>
       </c>
+      <c r="M674" t="str">
+        <v/>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
@@ -26087,6 +28074,9 @@
       <c r="L675" t="str">
         <v>441157</v>
       </c>
+      <c r="M675" t="str">
+        <v/>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
@@ -26125,6 +28115,9 @@
       <c r="L676" t="str">
         <v>441164</v>
       </c>
+      <c r="M676" t="str">
+        <v/>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
@@ -26163,6 +28156,9 @@
       <c r="L677" t="str">
         <v>441171</v>
       </c>
+      <c r="M677" t="str">
+        <v/>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
@@ -26201,6 +28197,9 @@
       <c r="L678" t="str">
         <v>441188</v>
       </c>
+      <c r="M678" t="str">
+        <v/>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
@@ -26239,6 +28238,9 @@
       <c r="L679" t="str">
         <v>441195</v>
       </c>
+      <c r="M679" t="str">
+        <v/>
+      </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
@@ -26277,6 +28279,9 @@
       <c r="L680" t="str">
         <v>441201</v>
       </c>
+      <c r="M680" t="str">
+        <v/>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
@@ -26315,6 +28320,9 @@
       <c r="L681" t="str">
         <v>441218</v>
       </c>
+      <c r="M681" t="str">
+        <v/>
+      </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
@@ -26353,6 +28361,9 @@
       <c r="L682" t="str">
         <v>441225</v>
       </c>
+      <c r="M682" t="str">
+        <v/>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
@@ -26391,6 +28402,9 @@
       <c r="L683" t="str">
         <v>441232</v>
       </c>
+      <c r="M683" t="str">
+        <v/>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
@@ -26429,6 +28443,9 @@
       <c r="L684" t="str">
         <v>441249</v>
       </c>
+      <c r="M684" t="str">
+        <v/>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
@@ -26467,6 +28484,9 @@
       <c r="L685" t="str">
         <v>441256</v>
       </c>
+      <c r="M685" t="str">
+        <v/>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
@@ -26505,6 +28525,9 @@
       <c r="L686" t="str">
         <v>441263</v>
       </c>
+      <c r="M686" t="str">
+        <v/>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
@@ -26543,6 +28566,9 @@
       <c r="L687" t="str">
         <v>441270</v>
       </c>
+      <c r="M687" t="str">
+        <v/>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
@@ -26581,6 +28607,9 @@
       <c r="L688" t="str">
         <v>441287</v>
       </c>
+      <c r="M688" t="str">
+        <v/>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
@@ -26619,6 +28648,9 @@
       <c r="L689" t="str">
         <v>441294</v>
       </c>
+      <c r="M689" t="str">
+        <v/>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
@@ -26657,6 +28689,9 @@
       <c r="L690" t="str">
         <v>800831</v>
       </c>
+      <c r="M690" t="str">
+        <v/>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
@@ -26695,6 +28730,9 @@
       <c r="L691" t="str">
         <v>783530</v>
       </c>
+      <c r="M691" t="str">
+        <v/>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
@@ -26733,6 +28771,9 @@
       <c r="L692" t="str">
         <v>783561</v>
       </c>
+      <c r="M692" t="str">
+        <v/>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
@@ -26771,6 +28812,9 @@
       <c r="L693" t="str">
         <v>783578</v>
       </c>
+      <c r="M693" t="str">
+        <v/>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
@@ -26809,6 +28853,9 @@
       <c r="L694" t="str">
         <v>783592</v>
       </c>
+      <c r="M694" t="str">
+        <v/>
+      </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
@@ -26847,6 +28894,9 @@
       <c r="L695" t="str">
         <v>800848</v>
       </c>
+      <c r="M695" t="str">
+        <v/>
+      </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
@@ -26885,6 +28935,9 @@
       <c r="L696" t="str">
         <v>800855</v>
       </c>
+      <c r="M696" t="str">
+        <v/>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
@@ -26923,6 +28976,9 @@
       <c r="L697" t="str">
         <v>800862</v>
       </c>
+      <c r="M697" t="str">
+        <v/>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
@@ -26961,6 +29017,9 @@
       <c r="L698" t="str">
         <v>800879</v>
       </c>
+      <c r="M698" t="str">
+        <v/>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
@@ -26999,6 +29058,9 @@
       <c r="L699" t="str">
         <v>783653</v>
       </c>
+      <c r="M699" t="str">
+        <v/>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
@@ -27037,6 +29099,9 @@
       <c r="L700" t="str">
         <v>783660</v>
       </c>
+      <c r="M700" t="str">
+        <v/>
+      </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
@@ -27075,6 +29140,9 @@
       <c r="L701" t="str">
         <v>783677</v>
       </c>
+      <c r="M701" t="str">
+        <v/>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
@@ -27113,6 +29181,9 @@
       <c r="L702" t="str">
         <v>547385</v>
       </c>
+      <c r="M702" t="str">
+        <v/>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
@@ -27151,6 +29222,9 @@
       <c r="L703" t="str">
         <v>547408</v>
       </c>
+      <c r="M703" t="str">
+        <v/>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
@@ -27189,6 +29263,9 @@
       <c r="L704" t="str">
         <v>547415</v>
       </c>
+      <c r="M704" t="str">
+        <v/>
+      </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
@@ -27227,6 +29304,9 @@
       <c r="L705" t="str">
         <v>547422</v>
       </c>
+      <c r="M705" t="str">
+        <v/>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
@@ -27265,6 +29345,9 @@
       <c r="L706" t="str">
         <v>800886</v>
       </c>
+      <c r="M706" t="str">
+        <v/>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="str">
@@ -27303,6 +29386,9 @@
       <c r="L707" t="str">
         <v>783738</v>
       </c>
+      <c r="M707" t="str">
+        <v/>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="str">
@@ -27341,6 +29427,9 @@
       <c r="L708" t="str">
         <v>783769</v>
       </c>
+      <c r="M708" t="str">
+        <v/>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="str">
@@ -27379,6 +29468,9 @@
       <c r="L709" t="str">
         <v>783776</v>
       </c>
+      <c r="M709" t="str">
+        <v/>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="str">
@@ -27417,6 +29509,9 @@
       <c r="L710" t="str">
         <v>783790</v>
       </c>
+      <c r="M710" t="str">
+        <v/>
+      </c>
     </row>
     <row r="711">
       <c r="A711" t="str">
@@ -27455,6 +29550,9 @@
       <c r="L711" t="str">
         <v>800923</v>
       </c>
+      <c r="M711" t="str">
+        <v/>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="str">
@@ -27493,6 +29591,9 @@
       <c r="L712" t="str">
         <v>800930</v>
       </c>
+      <c r="M712" t="str">
+        <v/>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="str">
@@ -27531,6 +29632,9 @@
       <c r="L713" t="str">
         <v>800947</v>
       </c>
+      <c r="M713" t="str">
+        <v/>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="str">
@@ -27569,6 +29673,9 @@
       <c r="L714" t="str">
         <v>800954</v>
       </c>
+      <c r="M714" t="str">
+        <v/>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="str">
@@ -27607,6 +29714,9 @@
       <c r="L715" t="str">
         <v>783851</v>
       </c>
+      <c r="M715" t="str">
+        <v/>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="str">
@@ -27645,6 +29755,9 @@
       <c r="L716" t="str">
         <v>783868</v>
       </c>
+      <c r="M716" t="str">
+        <v/>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="str">
@@ -27683,6 +29796,9 @@
       <c r="L717" t="str">
         <v>783875</v>
       </c>
+      <c r="M717" t="str">
+        <v/>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="str">
@@ -27721,6 +29837,9 @@
       <c r="L718" t="str">
         <v>547446</v>
       </c>
+      <c r="M718" t="str">
+        <v/>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="str">
@@ -27759,6 +29878,9 @@
       <c r="L719" t="str">
         <v>547460</v>
       </c>
+      <c r="M719" t="str">
+        <v/>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="str">
@@ -27797,6 +29919,9 @@
       <c r="L720" t="str">
         <v>547477</v>
       </c>
+      <c r="M720" t="str">
+        <v/>
+      </c>
     </row>
     <row r="721">
       <c r="A721" t="str">
@@ -27835,6 +29960,9 @@
       <c r="L721" t="str">
         <v>547484</v>
       </c>
+      <c r="M721" t="str">
+        <v/>
+      </c>
     </row>
     <row r="722">
       <c r="A722" t="str">
@@ -27873,6 +30001,9 @@
       <c r="L722" t="str">
         <v>800961</v>
       </c>
+      <c r="M722" t="str">
+        <v/>
+      </c>
     </row>
     <row r="723">
       <c r="A723" t="str">
@@ -27911,6 +30042,9 @@
       <c r="L723" t="str">
         <v>783936</v>
       </c>
+      <c r="M723" t="str">
+        <v/>
+      </c>
     </row>
     <row r="724">
       <c r="A724" t="str">
@@ -27949,6 +30083,9 @@
       <c r="L724" t="str">
         <v>783967</v>
       </c>
+      <c r="M724" t="str">
+        <v/>
+      </c>
     </row>
     <row r="725">
       <c r="A725" t="str">
@@ -27987,6 +30124,9 @@
       <c r="L725" t="str">
         <v>783974</v>
       </c>
+      <c r="M725" t="str">
+        <v/>
+      </c>
     </row>
     <row r="726">
       <c r="A726" t="str">
@@ -28025,6 +30165,9 @@
       <c r="L726" t="str">
         <v>783998</v>
       </c>
+      <c r="M726" t="str">
+        <v/>
+      </c>
     </row>
     <row r="727">
       <c r="A727" t="str">
@@ -28063,6 +30206,9 @@
       <c r="L727" t="str">
         <v>800978</v>
       </c>
+      <c r="M727" t="str">
+        <v/>
+      </c>
     </row>
     <row r="728">
       <c r="A728" t="str">
@@ -28101,6 +30247,9 @@
       <c r="L728" t="str">
         <v>800985</v>
       </c>
+      <c r="M728" t="str">
+        <v/>
+      </c>
     </row>
     <row r="729">
       <c r="A729" t="str">
@@ -28139,6 +30288,9 @@
       <c r="L729" t="str">
         <v>800992</v>
       </c>
+      <c r="M729" t="str">
+        <v/>
+      </c>
     </row>
     <row r="730">
       <c r="A730" t="str">
@@ -28177,6 +30329,9 @@
       <c r="L730" t="str">
         <v>801005</v>
       </c>
+      <c r="M730" t="str">
+        <v/>
+      </c>
     </row>
     <row r="731">
       <c r="A731" t="str">
@@ -28215,6 +30370,9 @@
       <c r="L731" t="str">
         <v>784056</v>
       </c>
+      <c r="M731" t="str">
+        <v/>
+      </c>
     </row>
     <row r="732">
       <c r="A732" t="str">
@@ -28253,6 +30411,9 @@
       <c r="L732" t="str">
         <v>784063</v>
       </c>
+      <c r="M732" t="str">
+        <v/>
+      </c>
     </row>
     <row r="733">
       <c r="A733" t="str">
@@ -28291,6 +30452,9 @@
       <c r="L733" t="str">
         <v>784070</v>
       </c>
+      <c r="M733" t="str">
+        <v/>
+      </c>
     </row>
     <row r="734">
       <c r="A734" t="str">
@@ -28329,6 +30493,9 @@
       <c r="L734" t="str">
         <v>547514</v>
       </c>
+      <c r="M734" t="str">
+        <v/>
+      </c>
     </row>
     <row r="735">
       <c r="A735" t="str">
@@ -28367,6 +30534,9 @@
       <c r="L735" t="str">
         <v>547538</v>
       </c>
+      <c r="M735" t="str">
+        <v/>
+      </c>
     </row>
     <row r="736">
       <c r="A736" t="str">
@@ -28405,6 +30575,9 @@
       <c r="L736" t="str">
         <v>547545</v>
       </c>
+      <c r="M736" t="str">
+        <v/>
+      </c>
     </row>
     <row r="737">
       <c r="A737" t="str">
@@ -28443,6 +30616,9 @@
       <c r="L737" t="str">
         <v>547552</v>
       </c>
+      <c r="M737" t="str">
+        <v/>
+      </c>
     </row>
     <row r="738">
       <c r="A738" t="str">
@@ -28481,6 +30657,9 @@
       <c r="L738" t="str">
         <v>801012</v>
       </c>
+      <c r="M738" t="str">
+        <v/>
+      </c>
     </row>
     <row r="739">
       <c r="A739" t="str">
@@ -28519,6 +30698,9 @@
       <c r="L739" t="str">
         <v>784131</v>
       </c>
+      <c r="M739" t="str">
+        <v/>
+      </c>
     </row>
     <row r="740">
       <c r="A740" t="str">
@@ -28557,6 +30739,9 @@
       <c r="L740" t="str">
         <v>784162</v>
       </c>
+      <c r="M740" t="str">
+        <v/>
+      </c>
     </row>
     <row r="741">
       <c r="A741" t="str">
@@ -28595,6 +30780,9 @@
       <c r="L741" t="str">
         <v>784179</v>
       </c>
+      <c r="M741" t="str">
+        <v/>
+      </c>
     </row>
     <row r="742">
       <c r="A742" t="str">
@@ -28633,6 +30821,9 @@
       <c r="L742" t="str">
         <v>784193</v>
       </c>
+      <c r="M742" t="str">
+        <v/>
+      </c>
     </row>
     <row r="743">
       <c r="A743" t="str">
@@ -28671,6 +30862,9 @@
       <c r="L743" t="str">
         <v>801029</v>
       </c>
+      <c r="M743" t="str">
+        <v/>
+      </c>
     </row>
     <row r="744">
       <c r="A744" t="str">
@@ -28709,6 +30903,9 @@
       <c r="L744" t="str">
         <v>801036</v>
       </c>
+      <c r="M744" t="str">
+        <v/>
+      </c>
     </row>
     <row r="745">
       <c r="A745" t="str">
@@ -28747,6 +30944,9 @@
       <c r="L745" t="str">
         <v>801043</v>
       </c>
+      <c r="M745" t="str">
+        <v/>
+      </c>
     </row>
     <row r="746">
       <c r="A746" t="str">
@@ -28785,6 +30985,9 @@
       <c r="L746" t="str">
         <v>801050</v>
       </c>
+      <c r="M746" t="str">
+        <v/>
+      </c>
     </row>
     <row r="747">
       <c r="A747" t="str">
@@ -28823,6 +31026,9 @@
       <c r="L747" t="str">
         <v>784254</v>
       </c>
+      <c r="M747" t="str">
+        <v/>
+      </c>
     </row>
     <row r="748">
       <c r="A748" t="str">
@@ -28861,6 +31067,9 @@
       <c r="L748" t="str">
         <v>784261</v>
       </c>
+      <c r="M748" t="str">
+        <v/>
+      </c>
     </row>
     <row r="749">
       <c r="A749" t="str">
@@ -28899,6 +31108,9 @@
       <c r="L749" t="str">
         <v>784278</v>
       </c>
+      <c r="M749" t="str">
+        <v/>
+      </c>
     </row>
     <row r="750">
       <c r="A750" t="str">
@@ -28937,6 +31149,9 @@
       <c r="L750" t="str">
         <v>547576</v>
       </c>
+      <c r="M750" t="str">
+        <v/>
+      </c>
     </row>
     <row r="751">
       <c r="A751" t="str">
@@ -28975,6 +31190,9 @@
       <c r="L751" t="str">
         <v>547590</v>
       </c>
+      <c r="M751" t="str">
+        <v/>
+      </c>
     </row>
     <row r="752">
       <c r="A752" t="str">
@@ -29013,6 +31231,9 @@
       <c r="L752" t="str">
         <v>547606</v>
       </c>
+      <c r="M752" t="str">
+        <v/>
+      </c>
     </row>
     <row r="753">
       <c r="A753" t="str">
@@ -29050,6 +31271,9 @@
       </c>
       <c r="L753" t="str">
         <v>547613</v>
+      </c>
+      <c r="M753" t="str">
+        <v/>
       </c>
     </row>
     <row r="754">

--- a/GearSage-client/rate/excel/metal_lure_detail.xlsx
+++ b/GearSage-client/rate/excel/metal_lure_detail.xlsx
@@ -32,11 +32,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">

--- a/GearSage-client/rate/excel/metal_lure_detail.xlsx
+++ b/GearSage-client/rate/excel/metal_lure_detail.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q1087"/>
+  <dimension ref="A1:M1087"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,18 +439,6 @@
       <c r="M1" t="str">
         <v>hook_size</v>
       </c>
-      <c r="N1" t="str">
-        <v>depth</v>
-      </c>
-      <c r="O1" t="str">
-        <v>action</v>
-      </c>
-      <c r="P1" t="str">
-        <v>subname</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>other.1</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -31488,18 +31476,6 @@
       <c r="M758" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N758" t="str">
-        <v/>
-      </c>
-      <c r="O758" t="str">
-        <v/>
-      </c>
-      <c r="P758" t="str">
-        <v/>
-      </c>
-      <c r="Q758" t="str">
-        <v/>
-      </c>
     </row>
     <row r="759">
       <c r="A759" t="str">
@@ -31541,18 +31517,6 @@
       <c r="M759" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N759" t="str">
-        <v/>
-      </c>
-      <c r="O759" t="str">
-        <v/>
-      </c>
-      <c r="P759" t="str">
-        <v/>
-      </c>
-      <c r="Q759" t="str">
-        <v/>
-      </c>
     </row>
     <row r="760">
       <c r="A760" t="str">
@@ -31594,18 +31558,6 @@
       <c r="M760" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N760" t="str">
-        <v/>
-      </c>
-      <c r="O760" t="str">
-        <v/>
-      </c>
-      <c r="P760" t="str">
-        <v/>
-      </c>
-      <c r="Q760" t="str">
-        <v/>
-      </c>
     </row>
     <row r="761">
       <c r="A761" t="str">
@@ -31647,18 +31599,6 @@
       <c r="M761" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N761" t="str">
-        <v/>
-      </c>
-      <c r="O761" t="str">
-        <v/>
-      </c>
-      <c r="P761" t="str">
-        <v/>
-      </c>
-      <c r="Q761" t="str">
-        <v/>
-      </c>
     </row>
     <row r="762">
       <c r="A762" t="str">
@@ -31700,18 +31640,6 @@
       <c r="M762" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N762" t="str">
-        <v/>
-      </c>
-      <c r="O762" t="str">
-        <v/>
-      </c>
-      <c r="P762" t="str">
-        <v/>
-      </c>
-      <c r="Q762" t="str">
-        <v/>
-      </c>
     </row>
     <row r="763">
       <c r="A763" t="str">
@@ -31753,18 +31681,6 @@
       <c r="M763" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N763" t="str">
-        <v/>
-      </c>
-      <c r="O763" t="str">
-        <v/>
-      </c>
-      <c r="P763" t="str">
-        <v/>
-      </c>
-      <c r="Q763" t="str">
-        <v/>
-      </c>
     </row>
     <row r="764">
       <c r="A764" t="str">
@@ -31806,18 +31722,6 @@
       <c r="M764" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N764" t="str">
-        <v/>
-      </c>
-      <c r="O764" t="str">
-        <v/>
-      </c>
-      <c r="P764" t="str">
-        <v/>
-      </c>
-      <c r="Q764" t="str">
-        <v/>
-      </c>
     </row>
     <row r="765">
       <c r="A765" t="str">
@@ -31859,18 +31763,6 @@
       <c r="M765" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N765" t="str">
-        <v/>
-      </c>
-      <c r="O765" t="str">
-        <v/>
-      </c>
-      <c r="P765" t="str">
-        <v/>
-      </c>
-      <c r="Q765" t="str">
-        <v/>
-      </c>
     </row>
     <row r="766">
       <c r="A766" t="str">
@@ -31912,18 +31804,6 @@
       <c r="M766" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N766" t="str">
-        <v/>
-      </c>
-      <c r="O766" t="str">
-        <v/>
-      </c>
-      <c r="P766" t="str">
-        <v/>
-      </c>
-      <c r="Q766" t="str">
-        <v/>
-      </c>
     </row>
     <row r="767">
       <c r="A767" t="str">
@@ -31965,18 +31845,6 @@
       <c r="M767" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N767" t="str">
-        <v/>
-      </c>
-      <c r="O767" t="str">
-        <v/>
-      </c>
-      <c r="P767" t="str">
-        <v/>
-      </c>
-      <c r="Q767" t="str">
-        <v/>
-      </c>
     </row>
     <row r="768">
       <c r="A768" t="str">
@@ -32018,18 +31886,6 @@
       <c r="M768" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N768" t="str">
-        <v/>
-      </c>
-      <c r="O768" t="str">
-        <v/>
-      </c>
-      <c r="P768" t="str">
-        <v/>
-      </c>
-      <c r="Q768" t="str">
-        <v/>
-      </c>
     </row>
     <row r="769">
       <c r="A769" t="str">
@@ -32071,18 +31927,6 @@
       <c r="M769" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N769" t="str">
-        <v/>
-      </c>
-      <c r="O769" t="str">
-        <v/>
-      </c>
-      <c r="P769" t="str">
-        <v/>
-      </c>
-      <c r="Q769" t="str">
-        <v/>
-      </c>
     </row>
     <row r="770">
       <c r="A770" t="str">
@@ -32124,18 +31968,6 @@
       <c r="M770" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N770" t="str">
-        <v/>
-      </c>
-      <c r="O770" t="str">
-        <v/>
-      </c>
-      <c r="P770" t="str">
-        <v/>
-      </c>
-      <c r="Q770" t="str">
-        <v/>
-      </c>
     </row>
     <row r="771">
       <c r="A771" t="str">
@@ -32177,18 +32009,6 @@
       <c r="M771" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N771" t="str">
-        <v/>
-      </c>
-      <c r="O771" t="str">
-        <v/>
-      </c>
-      <c r="P771" t="str">
-        <v/>
-      </c>
-      <c r="Q771" t="str">
-        <v/>
-      </c>
     </row>
     <row r="772">
       <c r="A772" t="str">
@@ -32230,18 +32050,6 @@
       <c r="M772" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N772" t="str">
-        <v/>
-      </c>
-      <c r="O772" t="str">
-        <v/>
-      </c>
-      <c r="P772" t="str">
-        <v/>
-      </c>
-      <c r="Q772" t="str">
-        <v/>
-      </c>
     </row>
     <row r="773">
       <c r="A773" t="str">
@@ -32283,18 +32091,6 @@
       <c r="M773" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N773" t="str">
-        <v/>
-      </c>
-      <c r="O773" t="str">
-        <v/>
-      </c>
-      <c r="P773" t="str">
-        <v/>
-      </c>
-      <c r="Q773" t="str">
-        <v/>
-      </c>
     </row>
     <row r="774">
       <c r="A774" t="str">
@@ -32336,18 +32132,6 @@
       <c r="M774" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N774" t="str">
-        <v/>
-      </c>
-      <c r="O774" t="str">
-        <v/>
-      </c>
-      <c r="P774" t="str">
-        <v/>
-      </c>
-      <c r="Q774" t="str">
-        <v/>
-      </c>
     </row>
     <row r="775">
       <c r="A775" t="str">
@@ -32389,18 +32173,6 @@
       <c r="M775" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N775" t="str">
-        <v/>
-      </c>
-      <c r="O775" t="str">
-        <v/>
-      </c>
-      <c r="P775" t="str">
-        <v/>
-      </c>
-      <c r="Q775" t="str">
-        <v/>
-      </c>
     </row>
     <row r="776">
       <c r="A776" t="str">
@@ -32442,18 +32214,6 @@
       <c r="M776" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N776" t="str">
-        <v/>
-      </c>
-      <c r="O776" t="str">
-        <v/>
-      </c>
-      <c r="P776" t="str">
-        <v/>
-      </c>
-      <c r="Q776" t="str">
-        <v/>
-      </c>
     </row>
     <row r="777">
       <c r="A777" t="str">
@@ -32495,18 +32255,6 @@
       <c r="M777" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N777" t="str">
-        <v/>
-      </c>
-      <c r="O777" t="str">
-        <v/>
-      </c>
-      <c r="P777" t="str">
-        <v/>
-      </c>
-      <c r="Q777" t="str">
-        <v/>
-      </c>
     </row>
     <row r="778">
       <c r="A778" t="str">
@@ -32548,18 +32296,6 @@
       <c r="M778" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N778" t="str">
-        <v/>
-      </c>
-      <c r="O778" t="str">
-        <v/>
-      </c>
-      <c r="P778" t="str">
-        <v/>
-      </c>
-      <c r="Q778" t="str">
-        <v/>
-      </c>
     </row>
     <row r="779">
       <c r="A779" t="str">
@@ -32601,18 +32337,6 @@
       <c r="M779" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N779" t="str">
-        <v/>
-      </c>
-      <c r="O779" t="str">
-        <v/>
-      </c>
-      <c r="P779" t="str">
-        <v/>
-      </c>
-      <c r="Q779" t="str">
-        <v/>
-      </c>
     </row>
     <row r="780">
       <c r="A780" t="str">
@@ -32654,18 +32378,6 @@
       <c r="M780" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N780" t="str">
-        <v/>
-      </c>
-      <c r="O780" t="str">
-        <v/>
-      </c>
-      <c r="P780" t="str">
-        <v/>
-      </c>
-      <c r="Q780" t="str">
-        <v/>
-      </c>
     </row>
     <row r="781">
       <c r="A781" t="str">
@@ -32707,18 +32419,6 @@
       <c r="M781" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N781" t="str">
-        <v/>
-      </c>
-      <c r="O781" t="str">
-        <v/>
-      </c>
-      <c r="P781" t="str">
-        <v/>
-      </c>
-      <c r="Q781" t="str">
-        <v/>
-      </c>
     </row>
     <row r="782">
       <c r="A782" t="str">
@@ -32760,18 +32460,6 @@
       <c r="M782" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N782" t="str">
-        <v/>
-      </c>
-      <c r="O782" t="str">
-        <v/>
-      </c>
-      <c r="P782" t="str">
-        <v/>
-      </c>
-      <c r="Q782" t="str">
-        <v/>
-      </c>
     </row>
     <row r="783">
       <c r="A783" t="str">
@@ -32813,18 +32501,6 @@
       <c r="M783" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N783" t="str">
-        <v/>
-      </c>
-      <c r="O783" t="str">
-        <v/>
-      </c>
-      <c r="P783" t="str">
-        <v/>
-      </c>
-      <c r="Q783" t="str">
-        <v/>
-      </c>
     </row>
     <row r="784">
       <c r="A784" t="str">
@@ -32866,18 +32542,6 @@
       <c r="M784" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N784" t="str">
-        <v/>
-      </c>
-      <c r="O784" t="str">
-        <v/>
-      </c>
-      <c r="P784" t="str">
-        <v/>
-      </c>
-      <c r="Q784" t="str">
-        <v/>
-      </c>
     </row>
     <row r="785">
       <c r="A785" t="str">
@@ -32919,18 +32583,6 @@
       <c r="M785" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N785" t="str">
-        <v/>
-      </c>
-      <c r="O785" t="str">
-        <v/>
-      </c>
-      <c r="P785" t="str">
-        <v/>
-      </c>
-      <c r="Q785" t="str">
-        <v/>
-      </c>
     </row>
     <row r="786">
       <c r="A786" t="str">
@@ -32972,18 +32624,6 @@
       <c r="M786" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N786" t="str">
-        <v/>
-      </c>
-      <c r="O786" t="str">
-        <v/>
-      </c>
-      <c r="P786" t="str">
-        <v/>
-      </c>
-      <c r="Q786" t="str">
-        <v/>
-      </c>
     </row>
     <row r="787">
       <c r="A787" t="str">
@@ -33025,18 +32665,6 @@
       <c r="M787" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N787" t="str">
-        <v/>
-      </c>
-      <c r="O787" t="str">
-        <v/>
-      </c>
-      <c r="P787" t="str">
-        <v/>
-      </c>
-      <c r="Q787" t="str">
-        <v/>
-      </c>
     </row>
     <row r="788">
       <c r="A788" t="str">
@@ -33078,18 +32706,6 @@
       <c r="M788" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N788" t="str">
-        <v/>
-      </c>
-      <c r="O788" t="str">
-        <v/>
-      </c>
-      <c r="P788" t="str">
-        <v/>
-      </c>
-      <c r="Q788" t="str">
-        <v/>
-      </c>
     </row>
     <row r="789">
       <c r="A789" t="str">
@@ -33131,18 +32747,6 @@
       <c r="M789" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N789" t="str">
-        <v/>
-      </c>
-      <c r="O789" t="str">
-        <v/>
-      </c>
-      <c r="P789" t="str">
-        <v/>
-      </c>
-      <c r="Q789" t="str">
-        <v/>
-      </c>
     </row>
     <row r="790">
       <c r="A790" t="str">
@@ -33184,18 +32788,6 @@
       <c r="M790" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N790" t="str">
-        <v/>
-      </c>
-      <c r="O790" t="str">
-        <v/>
-      </c>
-      <c r="P790" t="str">
-        <v/>
-      </c>
-      <c r="Q790" t="str">
-        <v/>
-      </c>
     </row>
     <row r="791">
       <c r="A791" t="str">
@@ -33237,18 +32829,6 @@
       <c r="M791" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N791" t="str">
-        <v/>
-      </c>
-      <c r="O791" t="str">
-        <v/>
-      </c>
-      <c r="P791" t="str">
-        <v/>
-      </c>
-      <c r="Q791" t="str">
-        <v/>
-      </c>
     </row>
     <row r="792">
       <c r="A792" t="str">
@@ -33290,18 +32870,6 @@
       <c r="M792" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N792" t="str">
-        <v/>
-      </c>
-      <c r="O792" t="str">
-        <v/>
-      </c>
-      <c r="P792" t="str">
-        <v/>
-      </c>
-      <c r="Q792" t="str">
-        <v/>
-      </c>
     </row>
     <row r="793">
       <c r="A793" t="str">
@@ -33343,18 +32911,6 @@
       <c r="M793" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N793" t="str">
-        <v/>
-      </c>
-      <c r="O793" t="str">
-        <v/>
-      </c>
-      <c r="P793" t="str">
-        <v/>
-      </c>
-      <c r="Q793" t="str">
-        <v/>
-      </c>
     </row>
     <row r="794">
       <c r="A794" t="str">
@@ -33396,18 +32952,6 @@
       <c r="M794" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N794" t="str">
-        <v/>
-      </c>
-      <c r="O794" t="str">
-        <v/>
-      </c>
-      <c r="P794" t="str">
-        <v/>
-      </c>
-      <c r="Q794" t="str">
-        <v/>
-      </c>
     </row>
     <row r="795">
       <c r="A795" t="str">
@@ -33449,18 +32993,6 @@
       <c r="M795" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N795" t="str">
-        <v/>
-      </c>
-      <c r="O795" t="str">
-        <v/>
-      </c>
-      <c r="P795" t="str">
-        <v/>
-      </c>
-      <c r="Q795" t="str">
-        <v/>
-      </c>
     </row>
     <row r="796">
       <c r="A796" t="str">
@@ -33502,18 +33034,6 @@
       <c r="M796" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N796" t="str">
-        <v/>
-      </c>
-      <c r="O796" t="str">
-        <v/>
-      </c>
-      <c r="P796" t="str">
-        <v/>
-      </c>
-      <c r="Q796" t="str">
-        <v/>
-      </c>
     </row>
     <row r="797">
       <c r="A797" t="str">
@@ -33555,18 +33075,6 @@
       <c r="M797" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N797" t="str">
-        <v/>
-      </c>
-      <c r="O797" t="str">
-        <v/>
-      </c>
-      <c r="P797" t="str">
-        <v/>
-      </c>
-      <c r="Q797" t="str">
-        <v/>
-      </c>
     </row>
     <row r="798">
       <c r="A798" t="str">
@@ -33608,18 +33116,6 @@
       <c r="M798" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N798" t="str">
-        <v/>
-      </c>
-      <c r="O798" t="str">
-        <v/>
-      </c>
-      <c r="P798" t="str">
-        <v/>
-      </c>
-      <c r="Q798" t="str">
-        <v/>
-      </c>
     </row>
     <row r="799">
       <c r="A799" t="str">
@@ -33661,18 +33157,6 @@
       <c r="M799" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N799" t="str">
-        <v/>
-      </c>
-      <c r="O799" t="str">
-        <v/>
-      </c>
-      <c r="P799" t="str">
-        <v/>
-      </c>
-      <c r="Q799" t="str">
-        <v/>
-      </c>
     </row>
     <row r="800">
       <c r="A800" t="str">
@@ -33714,18 +33198,6 @@
       <c r="M800" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N800" t="str">
-        <v/>
-      </c>
-      <c r="O800" t="str">
-        <v/>
-      </c>
-      <c r="P800" t="str">
-        <v/>
-      </c>
-      <c r="Q800" t="str">
-        <v/>
-      </c>
     </row>
     <row r="801">
       <c r="A801" t="str">
@@ -33767,18 +33239,6 @@
       <c r="M801" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N801" t="str">
-        <v/>
-      </c>
-      <c r="O801" t="str">
-        <v/>
-      </c>
-      <c r="P801" t="str">
-        <v/>
-      </c>
-      <c r="Q801" t="str">
-        <v/>
-      </c>
     </row>
     <row r="802">
       <c r="A802" t="str">
@@ -33820,18 +33280,6 @@
       <c r="M802" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N802" t="str">
-        <v/>
-      </c>
-      <c r="O802" t="str">
-        <v/>
-      </c>
-      <c r="P802" t="str">
-        <v/>
-      </c>
-      <c r="Q802" t="str">
-        <v/>
-      </c>
     </row>
     <row r="803">
       <c r="A803" t="str">
@@ -33873,18 +33321,6 @@
       <c r="M803" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N803" t="str">
-        <v/>
-      </c>
-      <c r="O803" t="str">
-        <v/>
-      </c>
-      <c r="P803" t="str">
-        <v/>
-      </c>
-      <c r="Q803" t="str">
-        <v/>
-      </c>
     </row>
     <row r="804">
       <c r="A804" t="str">
@@ -33926,18 +33362,6 @@
       <c r="M804" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N804" t="str">
-        <v/>
-      </c>
-      <c r="O804" t="str">
-        <v/>
-      </c>
-      <c r="P804" t="str">
-        <v/>
-      </c>
-      <c r="Q804" t="str">
-        <v/>
-      </c>
     </row>
     <row r="805">
       <c r="A805" t="str">
@@ -33979,18 +33403,6 @@
       <c r="M805" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N805" t="str">
-        <v/>
-      </c>
-      <c r="O805" t="str">
-        <v/>
-      </c>
-      <c r="P805" t="str">
-        <v/>
-      </c>
-      <c r="Q805" t="str">
-        <v/>
-      </c>
     </row>
     <row r="806">
       <c r="A806" t="str">
@@ -34032,18 +33444,6 @@
       <c r="M806" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N806" t="str">
-        <v/>
-      </c>
-      <c r="O806" t="str">
-        <v/>
-      </c>
-      <c r="P806" t="str">
-        <v/>
-      </c>
-      <c r="Q806" t="str">
-        <v/>
-      </c>
     </row>
     <row r="807">
       <c r="A807" t="str">
@@ -34085,18 +33485,6 @@
       <c r="M807" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N807" t="str">
-        <v/>
-      </c>
-      <c r="O807" t="str">
-        <v/>
-      </c>
-      <c r="P807" t="str">
-        <v/>
-      </c>
-      <c r="Q807" t="str">
-        <v/>
-      </c>
     </row>
     <row r="808">
       <c r="A808" t="str">
@@ -34138,18 +33526,6 @@
       <c r="M808" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N808" t="str">
-        <v/>
-      </c>
-      <c r="O808" t="str">
-        <v/>
-      </c>
-      <c r="P808" t="str">
-        <v/>
-      </c>
-      <c r="Q808" t="str">
-        <v/>
-      </c>
     </row>
     <row r="809">
       <c r="A809" t="str">
@@ -34191,18 +33567,6 @@
       <c r="M809" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N809" t="str">
-        <v/>
-      </c>
-      <c r="O809" t="str">
-        <v/>
-      </c>
-      <c r="P809" t="str">
-        <v/>
-      </c>
-      <c r="Q809" t="str">
-        <v/>
-      </c>
     </row>
     <row r="810">
       <c r="A810" t="str">
@@ -34244,18 +33608,6 @@
       <c r="M810" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N810" t="str">
-        <v/>
-      </c>
-      <c r="O810" t="str">
-        <v/>
-      </c>
-      <c r="P810" t="str">
-        <v/>
-      </c>
-      <c r="Q810" t="str">
-        <v/>
-      </c>
     </row>
     <row r="811">
       <c r="A811" t="str">
@@ -34297,18 +33649,6 @@
       <c r="M811" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N811" t="str">
-        <v/>
-      </c>
-      <c r="O811" t="str">
-        <v/>
-      </c>
-      <c r="P811" t="str">
-        <v/>
-      </c>
-      <c r="Q811" t="str">
-        <v/>
-      </c>
     </row>
     <row r="812">
       <c r="A812" t="str">
@@ -34350,18 +33690,6 @@
       <c r="M812" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N812" t="str">
-        <v/>
-      </c>
-      <c r="O812" t="str">
-        <v/>
-      </c>
-      <c r="P812" t="str">
-        <v/>
-      </c>
-      <c r="Q812" t="str">
-        <v/>
-      </c>
     </row>
     <row r="813">
       <c r="A813" t="str">
@@ -34403,18 +33731,6 @@
       <c r="M813" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N813" t="str">
-        <v/>
-      </c>
-      <c r="O813" t="str">
-        <v/>
-      </c>
-      <c r="P813" t="str">
-        <v/>
-      </c>
-      <c r="Q813" t="str">
-        <v/>
-      </c>
     </row>
     <row r="814">
       <c r="A814" t="str">
@@ -34456,18 +33772,6 @@
       <c r="M814" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N814" t="str">
-        <v/>
-      </c>
-      <c r="O814" t="str">
-        <v/>
-      </c>
-      <c r="P814" t="str">
-        <v/>
-      </c>
-      <c r="Q814" t="str">
-        <v/>
-      </c>
     </row>
     <row r="815">
       <c r="A815" t="str">
@@ -34509,18 +33813,6 @@
       <c r="M815" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N815" t="str">
-        <v/>
-      </c>
-      <c r="O815" t="str">
-        <v/>
-      </c>
-      <c r="P815" t="str">
-        <v/>
-      </c>
-      <c r="Q815" t="str">
-        <v/>
-      </c>
     </row>
     <row r="816">
       <c r="A816" t="str">
@@ -34562,18 +33854,6 @@
       <c r="M816" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N816" t="str">
-        <v/>
-      </c>
-      <c r="O816" t="str">
-        <v/>
-      </c>
-      <c r="P816" t="str">
-        <v/>
-      </c>
-      <c r="Q816" t="str">
-        <v/>
-      </c>
     </row>
     <row r="817">
       <c r="A817" t="str">
@@ -34615,18 +33895,6 @@
       <c r="M817" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N817" t="str">
-        <v/>
-      </c>
-      <c r="O817" t="str">
-        <v/>
-      </c>
-      <c r="P817" t="str">
-        <v/>
-      </c>
-      <c r="Q817" t="str">
-        <v/>
-      </c>
     </row>
     <row r="818">
       <c r="A818" t="str">
@@ -34668,18 +33936,6 @@
       <c r="M818" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N818" t="str">
-        <v/>
-      </c>
-      <c r="O818" t="str">
-        <v/>
-      </c>
-      <c r="P818" t="str">
-        <v/>
-      </c>
-      <c r="Q818" t="str">
-        <v/>
-      </c>
     </row>
     <row r="819">
       <c r="A819" t="str">
@@ -34721,18 +33977,6 @@
       <c r="M819" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N819" t="str">
-        <v/>
-      </c>
-      <c r="O819" t="str">
-        <v/>
-      </c>
-      <c r="P819" t="str">
-        <v/>
-      </c>
-      <c r="Q819" t="str">
-        <v/>
-      </c>
     </row>
     <row r="820">
       <c r="A820" t="str">
@@ -34774,18 +34018,6 @@
       <c r="M820" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N820" t="str">
-        <v/>
-      </c>
-      <c r="O820" t="str">
-        <v/>
-      </c>
-      <c r="P820" t="str">
-        <v/>
-      </c>
-      <c r="Q820" t="str">
-        <v/>
-      </c>
     </row>
     <row r="821">
       <c r="A821" t="str">
@@ -34827,18 +34059,6 @@
       <c r="M821" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N821" t="str">
-        <v/>
-      </c>
-      <c r="O821" t="str">
-        <v/>
-      </c>
-      <c r="P821" t="str">
-        <v/>
-      </c>
-      <c r="Q821" t="str">
-        <v/>
-      </c>
     </row>
     <row r="822">
       <c r="A822" t="str">
@@ -34880,18 +34100,6 @@
       <c r="M822" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N822" t="str">
-        <v/>
-      </c>
-      <c r="O822" t="str">
-        <v/>
-      </c>
-      <c r="P822" t="str">
-        <v/>
-      </c>
-      <c r="Q822" t="str">
-        <v/>
-      </c>
     </row>
     <row r="823">
       <c r="A823" t="str">
@@ -34933,18 +34141,6 @@
       <c r="M823" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N823" t="str">
-        <v/>
-      </c>
-      <c r="O823" t="str">
-        <v/>
-      </c>
-      <c r="P823" t="str">
-        <v/>
-      </c>
-      <c r="Q823" t="str">
-        <v/>
-      </c>
     </row>
     <row r="824">
       <c r="A824" t="str">
@@ -34986,18 +34182,6 @@
       <c r="M824" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N824" t="str">
-        <v/>
-      </c>
-      <c r="O824" t="str">
-        <v/>
-      </c>
-      <c r="P824" t="str">
-        <v/>
-      </c>
-      <c r="Q824" t="str">
-        <v/>
-      </c>
     </row>
     <row r="825">
       <c r="A825" t="str">
@@ -35039,18 +34223,6 @@
       <c r="M825" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N825" t="str">
-        <v/>
-      </c>
-      <c r="O825" t="str">
-        <v/>
-      </c>
-      <c r="P825" t="str">
-        <v/>
-      </c>
-      <c r="Q825" t="str">
-        <v/>
-      </c>
     </row>
     <row r="826">
       <c r="A826" t="str">
@@ -35092,18 +34264,6 @@
       <c r="M826" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N826" t="str">
-        <v/>
-      </c>
-      <c r="O826" t="str">
-        <v/>
-      </c>
-      <c r="P826" t="str">
-        <v/>
-      </c>
-      <c r="Q826" t="str">
-        <v/>
-      </c>
     </row>
     <row r="827">
       <c r="A827" t="str">
@@ -35145,18 +34305,6 @@
       <c r="M827" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N827" t="str">
-        <v/>
-      </c>
-      <c r="O827" t="str">
-        <v/>
-      </c>
-      <c r="P827" t="str">
-        <v/>
-      </c>
-      <c r="Q827" t="str">
-        <v/>
-      </c>
     </row>
     <row r="828">
       <c r="A828" t="str">
@@ -35198,18 +34346,6 @@
       <c r="M828" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N828" t="str">
-        <v/>
-      </c>
-      <c r="O828" t="str">
-        <v/>
-      </c>
-      <c r="P828" t="str">
-        <v/>
-      </c>
-      <c r="Q828" t="str">
-        <v/>
-      </c>
     </row>
     <row r="829">
       <c r="A829" t="str">
@@ -35251,18 +34387,6 @@
       <c r="M829" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N829" t="str">
-        <v/>
-      </c>
-      <c r="O829" t="str">
-        <v/>
-      </c>
-      <c r="P829" t="str">
-        <v/>
-      </c>
-      <c r="Q829" t="str">
-        <v/>
-      </c>
     </row>
     <row r="830">
       <c r="A830" t="str">
@@ -35304,18 +34428,6 @@
       <c r="M830" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N830" t="str">
-        <v/>
-      </c>
-      <c r="O830" t="str">
-        <v/>
-      </c>
-      <c r="P830" t="str">
-        <v/>
-      </c>
-      <c r="Q830" t="str">
-        <v/>
-      </c>
     </row>
     <row r="831">
       <c r="A831" t="str">
@@ -35357,18 +34469,6 @@
       <c r="M831" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N831" t="str">
-        <v/>
-      </c>
-      <c r="O831" t="str">
-        <v/>
-      </c>
-      <c r="P831" t="str">
-        <v/>
-      </c>
-      <c r="Q831" t="str">
-        <v/>
-      </c>
     </row>
     <row r="832">
       <c r="A832" t="str">
@@ -35410,18 +34510,6 @@
       <c r="M832" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N832" t="str">
-        <v/>
-      </c>
-      <c r="O832" t="str">
-        <v/>
-      </c>
-      <c r="P832" t="str">
-        <v/>
-      </c>
-      <c r="Q832" t="str">
-        <v/>
-      </c>
     </row>
     <row r="833">
       <c r="A833" t="str">
@@ -35463,18 +34551,6 @@
       <c r="M833" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N833" t="str">
-        <v/>
-      </c>
-      <c r="O833" t="str">
-        <v/>
-      </c>
-      <c r="P833" t="str">
-        <v/>
-      </c>
-      <c r="Q833" t="str">
-        <v/>
-      </c>
     </row>
     <row r="834">
       <c r="A834" t="str">
@@ -35516,18 +34592,6 @@
       <c r="M834" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N834" t="str">
-        <v/>
-      </c>
-      <c r="O834" t="str">
-        <v/>
-      </c>
-      <c r="P834" t="str">
-        <v/>
-      </c>
-      <c r="Q834" t="str">
-        <v/>
-      </c>
     </row>
     <row r="835">
       <c r="A835" t="str">
@@ -35569,18 +34633,6 @@
       <c r="M835" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N835" t="str">
-        <v/>
-      </c>
-      <c r="O835" t="str">
-        <v/>
-      </c>
-      <c r="P835" t="str">
-        <v/>
-      </c>
-      <c r="Q835" t="str">
-        <v/>
-      </c>
     </row>
     <row r="836">
       <c r="A836" t="str">
@@ -35622,18 +34674,6 @@
       <c r="M836" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N836" t="str">
-        <v/>
-      </c>
-      <c r="O836" t="str">
-        <v/>
-      </c>
-      <c r="P836" t="str">
-        <v/>
-      </c>
-      <c r="Q836" t="str">
-        <v/>
-      </c>
     </row>
     <row r="837">
       <c r="A837" t="str">
@@ -35675,18 +34715,6 @@
       <c r="M837" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N837" t="str">
-        <v/>
-      </c>
-      <c r="O837" t="str">
-        <v/>
-      </c>
-      <c r="P837" t="str">
-        <v/>
-      </c>
-      <c r="Q837" t="str">
-        <v/>
-      </c>
     </row>
     <row r="838">
       <c r="A838" t="str">
@@ -35728,18 +34756,6 @@
       <c r="M838" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N838" t="str">
-        <v/>
-      </c>
-      <c r="O838" t="str">
-        <v/>
-      </c>
-      <c r="P838" t="str">
-        <v/>
-      </c>
-      <c r="Q838" t="str">
-        <v/>
-      </c>
     </row>
     <row r="839">
       <c r="A839" t="str">
@@ -35781,18 +34797,6 @@
       <c r="M839" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N839" t="str">
-        <v/>
-      </c>
-      <c r="O839" t="str">
-        <v/>
-      </c>
-      <c r="P839" t="str">
-        <v/>
-      </c>
-      <c r="Q839" t="str">
-        <v/>
-      </c>
     </row>
     <row r="840">
       <c r="A840" t="str">
@@ -35834,18 +34838,6 @@
       <c r="M840" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N840" t="str">
-        <v/>
-      </c>
-      <c r="O840" t="str">
-        <v/>
-      </c>
-      <c r="P840" t="str">
-        <v/>
-      </c>
-      <c r="Q840" t="str">
-        <v/>
-      </c>
     </row>
     <row r="841">
       <c r="A841" t="str">
@@ -35887,18 +34879,6 @@
       <c r="M841" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N841" t="str">
-        <v/>
-      </c>
-      <c r="O841" t="str">
-        <v/>
-      </c>
-      <c r="P841" t="str">
-        <v/>
-      </c>
-      <c r="Q841" t="str">
-        <v/>
-      </c>
     </row>
     <row r="842">
       <c r="A842" t="str">
@@ -35940,18 +34920,6 @@
       <c r="M842" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N842" t="str">
-        <v/>
-      </c>
-      <c r="O842" t="str">
-        <v/>
-      </c>
-      <c r="P842" t="str">
-        <v/>
-      </c>
-      <c r="Q842" t="str">
-        <v/>
-      </c>
     </row>
     <row r="843">
       <c r="A843" t="str">
@@ -35993,18 +34961,6 @@
       <c r="M843" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N843" t="str">
-        <v/>
-      </c>
-      <c r="O843" t="str">
-        <v/>
-      </c>
-      <c r="P843" t="str">
-        <v/>
-      </c>
-      <c r="Q843" t="str">
-        <v/>
-      </c>
     </row>
     <row r="844">
       <c r="A844" t="str">
@@ -36046,18 +35002,6 @@
       <c r="M844" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N844" t="str">
-        <v/>
-      </c>
-      <c r="O844" t="str">
-        <v/>
-      </c>
-      <c r="P844" t="str">
-        <v/>
-      </c>
-      <c r="Q844" t="str">
-        <v/>
-      </c>
     </row>
     <row r="845">
       <c r="A845" t="str">
@@ -36099,18 +35043,6 @@
       <c r="M845" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N845" t="str">
-        <v/>
-      </c>
-      <c r="O845" t="str">
-        <v/>
-      </c>
-      <c r="P845" t="str">
-        <v/>
-      </c>
-      <c r="Q845" t="str">
-        <v/>
-      </c>
     </row>
     <row r="846">
       <c r="A846" t="str">
@@ -36152,18 +35084,6 @@
       <c r="M846" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N846" t="str">
-        <v/>
-      </c>
-      <c r="O846" t="str">
-        <v/>
-      </c>
-      <c r="P846" t="str">
-        <v/>
-      </c>
-      <c r="Q846" t="str">
-        <v/>
-      </c>
     </row>
     <row r="847">
       <c r="A847" t="str">
@@ -36205,18 +35125,6 @@
       <c r="M847" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N847" t="str">
-        <v/>
-      </c>
-      <c r="O847" t="str">
-        <v/>
-      </c>
-      <c r="P847" t="str">
-        <v/>
-      </c>
-      <c r="Q847" t="str">
-        <v/>
-      </c>
     </row>
     <row r="848">
       <c r="A848" t="str">
@@ -36258,18 +35166,6 @@
       <c r="M848" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N848" t="str">
-        <v/>
-      </c>
-      <c r="O848" t="str">
-        <v/>
-      </c>
-      <c r="P848" t="str">
-        <v/>
-      </c>
-      <c r="Q848" t="str">
-        <v/>
-      </c>
     </row>
     <row r="849">
       <c r="A849" t="str">
@@ -36311,18 +35207,6 @@
       <c r="M849" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N849" t="str">
-        <v/>
-      </c>
-      <c r="O849" t="str">
-        <v/>
-      </c>
-      <c r="P849" t="str">
-        <v/>
-      </c>
-      <c r="Q849" t="str">
-        <v/>
-      </c>
     </row>
     <row r="850">
       <c r="A850" t="str">
@@ -36364,18 +35248,6 @@
       <c r="M850" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N850" t="str">
-        <v/>
-      </c>
-      <c r="O850" t="str">
-        <v/>
-      </c>
-      <c r="P850" t="str">
-        <v/>
-      </c>
-      <c r="Q850" t="str">
-        <v/>
-      </c>
     </row>
     <row r="851">
       <c r="A851" t="str">
@@ -36417,18 +35289,6 @@
       <c r="M851" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N851" t="str">
-        <v/>
-      </c>
-      <c r="O851" t="str">
-        <v/>
-      </c>
-      <c r="P851" t="str">
-        <v/>
-      </c>
-      <c r="Q851" t="str">
-        <v/>
-      </c>
     </row>
     <row r="852">
       <c r="A852" t="str">
@@ -36470,18 +35330,6 @@
       <c r="M852" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N852" t="str">
-        <v/>
-      </c>
-      <c r="O852" t="str">
-        <v/>
-      </c>
-      <c r="P852" t="str">
-        <v/>
-      </c>
-      <c r="Q852" t="str">
-        <v/>
-      </c>
     </row>
     <row r="853">
       <c r="A853" t="str">
@@ -36523,18 +35371,6 @@
       <c r="M853" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N853" t="str">
-        <v/>
-      </c>
-      <c r="O853" t="str">
-        <v/>
-      </c>
-      <c r="P853" t="str">
-        <v/>
-      </c>
-      <c r="Q853" t="str">
-        <v/>
-      </c>
     </row>
     <row r="854">
       <c r="A854" t="str">
@@ -36576,18 +35412,6 @@
       <c r="M854" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N854" t="str">
-        <v/>
-      </c>
-      <c r="O854" t="str">
-        <v/>
-      </c>
-      <c r="P854" t="str">
-        <v/>
-      </c>
-      <c r="Q854" t="str">
-        <v/>
-      </c>
     </row>
     <row r="855">
       <c r="A855" t="str">
@@ -36629,18 +35453,6 @@
       <c r="M855" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N855" t="str">
-        <v/>
-      </c>
-      <c r="O855" t="str">
-        <v/>
-      </c>
-      <c r="P855" t="str">
-        <v/>
-      </c>
-      <c r="Q855" t="str">
-        <v/>
-      </c>
     </row>
     <row r="856">
       <c r="A856" t="str">
@@ -36682,18 +35494,6 @@
       <c r="M856" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N856" t="str">
-        <v/>
-      </c>
-      <c r="O856" t="str">
-        <v/>
-      </c>
-      <c r="P856" t="str">
-        <v/>
-      </c>
-      <c r="Q856" t="str">
-        <v/>
-      </c>
     </row>
     <row r="857">
       <c r="A857" t="str">
@@ -36735,18 +35535,6 @@
       <c r="M857" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N857" t="str">
-        <v/>
-      </c>
-      <c r="O857" t="str">
-        <v/>
-      </c>
-      <c r="P857" t="str">
-        <v/>
-      </c>
-      <c r="Q857" t="str">
-        <v/>
-      </c>
     </row>
     <row r="858">
       <c r="A858" t="str">
@@ -36788,18 +35576,6 @@
       <c r="M858" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N858" t="str">
-        <v/>
-      </c>
-      <c r="O858" t="str">
-        <v/>
-      </c>
-      <c r="P858" t="str">
-        <v/>
-      </c>
-      <c r="Q858" t="str">
-        <v/>
-      </c>
     </row>
     <row r="859">
       <c r="A859" t="str">
@@ -36841,18 +35617,6 @@
       <c r="M859" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N859" t="str">
-        <v/>
-      </c>
-      <c r="O859" t="str">
-        <v/>
-      </c>
-      <c r="P859" t="str">
-        <v/>
-      </c>
-      <c r="Q859" t="str">
-        <v/>
-      </c>
     </row>
     <row r="860">
       <c r="A860" t="str">
@@ -36894,18 +35658,6 @@
       <c r="M860" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N860" t="str">
-        <v/>
-      </c>
-      <c r="O860" t="str">
-        <v/>
-      </c>
-      <c r="P860" t="str">
-        <v/>
-      </c>
-      <c r="Q860" t="str">
-        <v/>
-      </c>
     </row>
     <row r="861">
       <c r="A861" t="str">
@@ -36947,18 +35699,6 @@
       <c r="M861" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N861" t="str">
-        <v/>
-      </c>
-      <c r="O861" t="str">
-        <v/>
-      </c>
-      <c r="P861" t="str">
-        <v/>
-      </c>
-      <c r="Q861" t="str">
-        <v/>
-      </c>
     </row>
     <row r="862">
       <c r="A862" t="str">
@@ -37000,18 +35740,6 @@
       <c r="M862" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N862" t="str">
-        <v/>
-      </c>
-      <c r="O862" t="str">
-        <v/>
-      </c>
-      <c r="P862" t="str">
-        <v/>
-      </c>
-      <c r="Q862" t="str">
-        <v/>
-      </c>
     </row>
     <row r="863">
       <c r="A863" t="str">
@@ -37053,18 +35781,6 @@
       <c r="M863" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N863" t="str">
-        <v/>
-      </c>
-      <c r="O863" t="str">
-        <v/>
-      </c>
-      <c r="P863" t="str">
-        <v/>
-      </c>
-      <c r="Q863" t="str">
-        <v/>
-      </c>
     </row>
     <row r="864">
       <c r="A864" t="str">
@@ -37106,18 +35822,6 @@
       <c r="M864" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N864" t="str">
-        <v/>
-      </c>
-      <c r="O864" t="str">
-        <v/>
-      </c>
-      <c r="P864" t="str">
-        <v/>
-      </c>
-      <c r="Q864" t="str">
-        <v/>
-      </c>
     </row>
     <row r="865">
       <c r="A865" t="str">
@@ -37159,18 +35863,6 @@
       <c r="M865" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N865" t="str">
-        <v/>
-      </c>
-      <c r="O865" t="str">
-        <v/>
-      </c>
-      <c r="P865" t="str">
-        <v/>
-      </c>
-      <c r="Q865" t="str">
-        <v/>
-      </c>
     </row>
     <row r="866">
       <c r="A866" t="str">
@@ -37212,18 +35904,6 @@
       <c r="M866" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N866" t="str">
-        <v/>
-      </c>
-      <c r="O866" t="str">
-        <v/>
-      </c>
-      <c r="P866" t="str">
-        <v/>
-      </c>
-      <c r="Q866" t="str">
-        <v/>
-      </c>
     </row>
     <row r="867">
       <c r="A867" t="str">
@@ -37265,18 +35945,6 @@
       <c r="M867" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N867" t="str">
-        <v/>
-      </c>
-      <c r="O867" t="str">
-        <v/>
-      </c>
-      <c r="P867" t="str">
-        <v/>
-      </c>
-      <c r="Q867" t="str">
-        <v/>
-      </c>
     </row>
     <row r="868">
       <c r="A868" t="str">
@@ -37318,18 +35986,6 @@
       <c r="M868" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N868" t="str">
-        <v/>
-      </c>
-      <c r="O868" t="str">
-        <v/>
-      </c>
-      <c r="P868" t="str">
-        <v/>
-      </c>
-      <c r="Q868" t="str">
-        <v/>
-      </c>
     </row>
     <row r="869">
       <c r="A869" t="str">
@@ -37371,18 +36027,6 @@
       <c r="M869" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N869" t="str">
-        <v/>
-      </c>
-      <c r="O869" t="str">
-        <v/>
-      </c>
-      <c r="P869" t="str">
-        <v/>
-      </c>
-      <c r="Q869" t="str">
-        <v/>
-      </c>
     </row>
     <row r="870">
       <c r="A870" t="str">
@@ -37424,18 +36068,6 @@
       <c r="M870" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N870" t="str">
-        <v/>
-      </c>
-      <c r="O870" t="str">
-        <v/>
-      </c>
-      <c r="P870" t="str">
-        <v/>
-      </c>
-      <c r="Q870" t="str">
-        <v/>
-      </c>
     </row>
     <row r="871">
       <c r="A871" t="str">
@@ -37477,18 +36109,6 @@
       <c r="M871" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N871" t="str">
-        <v/>
-      </c>
-      <c r="O871" t="str">
-        <v/>
-      </c>
-      <c r="P871" t="str">
-        <v/>
-      </c>
-      <c r="Q871" t="str">
-        <v/>
-      </c>
     </row>
     <row r="872">
       <c r="A872" t="str">
@@ -37530,18 +36150,6 @@
       <c r="M872" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N872" t="str">
-        <v/>
-      </c>
-      <c r="O872" t="str">
-        <v/>
-      </c>
-      <c r="P872" t="str">
-        <v/>
-      </c>
-      <c r="Q872" t="str">
-        <v/>
-      </c>
     </row>
     <row r="873">
       <c r="A873" t="str">
@@ -37583,18 +36191,6 @@
       <c r="M873" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N873" t="str">
-        <v/>
-      </c>
-      <c r="O873" t="str">
-        <v/>
-      </c>
-      <c r="P873" t="str">
-        <v/>
-      </c>
-      <c r="Q873" t="str">
-        <v/>
-      </c>
     </row>
     <row r="874">
       <c r="A874" t="str">
@@ -37636,18 +36232,6 @@
       <c r="M874" t="str">
         <v>ダブルフック#10</v>
       </c>
-      <c r="N874" t="str">
-        <v/>
-      </c>
-      <c r="O874" t="str">
-        <v/>
-      </c>
-      <c r="P874" t="str">
-        <v/>
-      </c>
-      <c r="Q874" t="str">
-        <v/>
-      </c>
     </row>
     <row r="875">
       <c r="A875" t="str">
@@ -37689,18 +36273,6 @@
       <c r="M875" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N875" t="str">
-        <v/>
-      </c>
-      <c r="O875" t="str">
-        <v/>
-      </c>
-      <c r="P875" t="str">
-        <v/>
-      </c>
-      <c r="Q875" t="str">
-        <v/>
-      </c>
     </row>
     <row r="876">
       <c r="A876" t="str">
@@ -37742,18 +36314,6 @@
       <c r="M876" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N876" t="str">
-        <v/>
-      </c>
-      <c r="O876" t="str">
-        <v/>
-      </c>
-      <c r="P876" t="str">
-        <v/>
-      </c>
-      <c r="Q876" t="str">
-        <v/>
-      </c>
     </row>
     <row r="877">
       <c r="A877" t="str">
@@ -37795,18 +36355,6 @@
       <c r="M877" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N877" t="str">
-        <v/>
-      </c>
-      <c r="O877" t="str">
-        <v/>
-      </c>
-      <c r="P877" t="str">
-        <v/>
-      </c>
-      <c r="Q877" t="str">
-        <v/>
-      </c>
     </row>
     <row r="878">
       <c r="A878" t="str">
@@ -37848,18 +36396,6 @@
       <c r="M878" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N878" t="str">
-        <v/>
-      </c>
-      <c r="O878" t="str">
-        <v/>
-      </c>
-      <c r="P878" t="str">
-        <v/>
-      </c>
-      <c r="Q878" t="str">
-        <v/>
-      </c>
     </row>
     <row r="879">
       <c r="A879" t="str">
@@ -37901,18 +36437,6 @@
       <c r="M879" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N879" t="str">
-        <v/>
-      </c>
-      <c r="O879" t="str">
-        <v/>
-      </c>
-      <c r="P879" t="str">
-        <v/>
-      </c>
-      <c r="Q879" t="str">
-        <v/>
-      </c>
     </row>
     <row r="880">
       <c r="A880" t="str">
@@ -37954,18 +36478,6 @@
       <c r="M880" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N880" t="str">
-        <v/>
-      </c>
-      <c r="O880" t="str">
-        <v/>
-      </c>
-      <c r="P880" t="str">
-        <v/>
-      </c>
-      <c r="Q880" t="str">
-        <v/>
-      </c>
     </row>
     <row r="881">
       <c r="A881" t="str">
@@ -38007,18 +36519,6 @@
       <c r="M881" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N881" t="str">
-        <v/>
-      </c>
-      <c r="O881" t="str">
-        <v/>
-      </c>
-      <c r="P881" t="str">
-        <v/>
-      </c>
-      <c r="Q881" t="str">
-        <v/>
-      </c>
     </row>
     <row r="882">
       <c r="A882" t="str">
@@ -38060,18 +36560,6 @@
       <c r="M882" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N882" t="str">
-        <v/>
-      </c>
-      <c r="O882" t="str">
-        <v/>
-      </c>
-      <c r="P882" t="str">
-        <v/>
-      </c>
-      <c r="Q882" t="str">
-        <v/>
-      </c>
     </row>
     <row r="883">
       <c r="A883" t="str">
@@ -38113,18 +36601,6 @@
       <c r="M883" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N883" t="str">
-        <v/>
-      </c>
-      <c r="O883" t="str">
-        <v/>
-      </c>
-      <c r="P883" t="str">
-        <v/>
-      </c>
-      <c r="Q883" t="str">
-        <v/>
-      </c>
     </row>
     <row r="884">
       <c r="A884" t="str">
@@ -38166,18 +36642,6 @@
       <c r="M884" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N884" t="str">
-        <v/>
-      </c>
-      <c r="O884" t="str">
-        <v/>
-      </c>
-      <c r="P884" t="str">
-        <v/>
-      </c>
-      <c r="Q884" t="str">
-        <v/>
-      </c>
     </row>
     <row r="885">
       <c r="A885" t="str">
@@ -38219,18 +36683,6 @@
       <c r="M885" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N885" t="str">
-        <v/>
-      </c>
-      <c r="O885" t="str">
-        <v/>
-      </c>
-      <c r="P885" t="str">
-        <v/>
-      </c>
-      <c r="Q885" t="str">
-        <v/>
-      </c>
     </row>
     <row r="886">
       <c r="A886" t="str">
@@ -38272,18 +36724,6 @@
       <c r="M886" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N886" t="str">
-        <v/>
-      </c>
-      <c r="O886" t="str">
-        <v/>
-      </c>
-      <c r="P886" t="str">
-        <v/>
-      </c>
-      <c r="Q886" t="str">
-        <v/>
-      </c>
     </row>
     <row r="887">
       <c r="A887" t="str">
@@ -38325,18 +36765,6 @@
       <c r="M887" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N887" t="str">
-        <v/>
-      </c>
-      <c r="O887" t="str">
-        <v/>
-      </c>
-      <c r="P887" t="str">
-        <v/>
-      </c>
-      <c r="Q887" t="str">
-        <v/>
-      </c>
     </row>
     <row r="888">
       <c r="A888" t="str">
@@ -38378,18 +36806,6 @@
       <c r="M888" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N888" t="str">
-        <v/>
-      </c>
-      <c r="O888" t="str">
-        <v/>
-      </c>
-      <c r="P888" t="str">
-        <v/>
-      </c>
-      <c r="Q888" t="str">
-        <v/>
-      </c>
     </row>
     <row r="889">
       <c r="A889" t="str">
@@ -38431,18 +36847,6 @@
       <c r="M889" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N889" t="str">
-        <v/>
-      </c>
-      <c r="O889" t="str">
-        <v/>
-      </c>
-      <c r="P889" t="str">
-        <v/>
-      </c>
-      <c r="Q889" t="str">
-        <v/>
-      </c>
     </row>
     <row r="890">
       <c r="A890" t="str">
@@ -38484,18 +36888,6 @@
       <c r="M890" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N890" t="str">
-        <v/>
-      </c>
-      <c r="O890" t="str">
-        <v/>
-      </c>
-      <c r="P890" t="str">
-        <v/>
-      </c>
-      <c r="Q890" t="str">
-        <v/>
-      </c>
     </row>
     <row r="891">
       <c r="A891" t="str">
@@ -38537,18 +36929,6 @@
       <c r="M891" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N891" t="str">
-        <v/>
-      </c>
-      <c r="O891" t="str">
-        <v/>
-      </c>
-      <c r="P891" t="str">
-        <v/>
-      </c>
-      <c r="Q891" t="str">
-        <v/>
-      </c>
     </row>
     <row r="892">
       <c r="A892" t="str">
@@ -38590,18 +36970,6 @@
       <c r="M892" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N892" t="str">
-        <v/>
-      </c>
-      <c r="O892" t="str">
-        <v/>
-      </c>
-      <c r="P892" t="str">
-        <v/>
-      </c>
-      <c r="Q892" t="str">
-        <v/>
-      </c>
     </row>
     <row r="893">
       <c r="A893" t="str">
@@ -38643,18 +37011,6 @@
       <c r="M893" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N893" t="str">
-        <v/>
-      </c>
-      <c r="O893" t="str">
-        <v/>
-      </c>
-      <c r="P893" t="str">
-        <v/>
-      </c>
-      <c r="Q893" t="str">
-        <v/>
-      </c>
     </row>
     <row r="894">
       <c r="A894" t="str">
@@ -38696,18 +37052,6 @@
       <c r="M894" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N894" t="str">
-        <v/>
-      </c>
-      <c r="O894" t="str">
-        <v/>
-      </c>
-      <c r="P894" t="str">
-        <v/>
-      </c>
-      <c r="Q894" t="str">
-        <v/>
-      </c>
     </row>
     <row r="895">
       <c r="A895" t="str">
@@ -38749,18 +37093,6 @@
       <c r="M895" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N895" t="str">
-        <v/>
-      </c>
-      <c r="O895" t="str">
-        <v/>
-      </c>
-      <c r="P895" t="str">
-        <v/>
-      </c>
-      <c r="Q895" t="str">
-        <v/>
-      </c>
     </row>
     <row r="896">
       <c r="A896" t="str">
@@ -38802,18 +37134,6 @@
       <c r="M896" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N896" t="str">
-        <v/>
-      </c>
-      <c r="O896" t="str">
-        <v/>
-      </c>
-      <c r="P896" t="str">
-        <v/>
-      </c>
-      <c r="Q896" t="str">
-        <v/>
-      </c>
     </row>
     <row r="897">
       <c r="A897" t="str">
@@ -38855,18 +37175,6 @@
       <c r="M897" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N897" t="str">
-        <v/>
-      </c>
-      <c r="O897" t="str">
-        <v/>
-      </c>
-      <c r="P897" t="str">
-        <v/>
-      </c>
-      <c r="Q897" t="str">
-        <v/>
-      </c>
     </row>
     <row r="898">
       <c r="A898" t="str">
@@ -38908,18 +37216,6 @@
       <c r="M898" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N898" t="str">
-        <v/>
-      </c>
-      <c r="O898" t="str">
-        <v/>
-      </c>
-      <c r="P898" t="str">
-        <v/>
-      </c>
-      <c r="Q898" t="str">
-        <v/>
-      </c>
     </row>
     <row r="899">
       <c r="A899" t="str">
@@ -38961,18 +37257,6 @@
       <c r="M899" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N899" t="str">
-        <v/>
-      </c>
-      <c r="O899" t="str">
-        <v/>
-      </c>
-      <c r="P899" t="str">
-        <v/>
-      </c>
-      <c r="Q899" t="str">
-        <v/>
-      </c>
     </row>
     <row r="900">
       <c r="A900" t="str">
@@ -39014,18 +37298,6 @@
       <c r="M900" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N900" t="str">
-        <v/>
-      </c>
-      <c r="O900" t="str">
-        <v/>
-      </c>
-      <c r="P900" t="str">
-        <v/>
-      </c>
-      <c r="Q900" t="str">
-        <v/>
-      </c>
     </row>
     <row r="901">
       <c r="A901" t="str">
@@ -39067,18 +37339,6 @@
       <c r="M901" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N901" t="str">
-        <v/>
-      </c>
-      <c r="O901" t="str">
-        <v/>
-      </c>
-      <c r="P901" t="str">
-        <v/>
-      </c>
-      <c r="Q901" t="str">
-        <v/>
-      </c>
     </row>
     <row r="902">
       <c r="A902" t="str">
@@ -39120,18 +37380,6 @@
       <c r="M902" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N902" t="str">
-        <v/>
-      </c>
-      <c r="O902" t="str">
-        <v/>
-      </c>
-      <c r="P902" t="str">
-        <v/>
-      </c>
-      <c r="Q902" t="str">
-        <v/>
-      </c>
     </row>
     <row r="903">
       <c r="A903" t="str">
@@ -39173,18 +37421,6 @@
       <c r="M903" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N903" t="str">
-        <v/>
-      </c>
-      <c r="O903" t="str">
-        <v/>
-      </c>
-      <c r="P903" t="str">
-        <v/>
-      </c>
-      <c r="Q903" t="str">
-        <v/>
-      </c>
     </row>
     <row r="904">
       <c r="A904" t="str">
@@ -39226,18 +37462,6 @@
       <c r="M904" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N904" t="str">
-        <v/>
-      </c>
-      <c r="O904" t="str">
-        <v/>
-      </c>
-      <c r="P904" t="str">
-        <v/>
-      </c>
-      <c r="Q904" t="str">
-        <v/>
-      </c>
     </row>
     <row r="905">
       <c r="A905" t="str">
@@ -39279,18 +37503,6 @@
       <c r="M905" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N905" t="str">
-        <v/>
-      </c>
-      <c r="O905" t="str">
-        <v/>
-      </c>
-      <c r="P905" t="str">
-        <v/>
-      </c>
-      <c r="Q905" t="str">
-        <v/>
-      </c>
     </row>
     <row r="906">
       <c r="A906" t="str">
@@ -39332,18 +37544,6 @@
       <c r="M906" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N906" t="str">
-        <v/>
-      </c>
-      <c r="O906" t="str">
-        <v/>
-      </c>
-      <c r="P906" t="str">
-        <v/>
-      </c>
-      <c r="Q906" t="str">
-        <v/>
-      </c>
     </row>
     <row r="907">
       <c r="A907" t="str">
@@ -39385,18 +37585,6 @@
       <c r="M907" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N907" t="str">
-        <v/>
-      </c>
-      <c r="O907" t="str">
-        <v/>
-      </c>
-      <c r="P907" t="str">
-        <v/>
-      </c>
-      <c r="Q907" t="str">
-        <v/>
-      </c>
     </row>
     <row r="908">
       <c r="A908" t="str">
@@ -39438,18 +37626,6 @@
       <c r="M908" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N908" t="str">
-        <v/>
-      </c>
-      <c r="O908" t="str">
-        <v/>
-      </c>
-      <c r="P908" t="str">
-        <v/>
-      </c>
-      <c r="Q908" t="str">
-        <v/>
-      </c>
     </row>
     <row r="909">
       <c r="A909" t="str">
@@ -39491,18 +37667,6 @@
       <c r="M909" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N909" t="str">
-        <v/>
-      </c>
-      <c r="O909" t="str">
-        <v/>
-      </c>
-      <c r="P909" t="str">
-        <v/>
-      </c>
-      <c r="Q909" t="str">
-        <v/>
-      </c>
     </row>
     <row r="910">
       <c r="A910" t="str">
@@ -39544,18 +37708,6 @@
       <c r="M910" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N910" t="str">
-        <v/>
-      </c>
-      <c r="O910" t="str">
-        <v/>
-      </c>
-      <c r="P910" t="str">
-        <v/>
-      </c>
-      <c r="Q910" t="str">
-        <v/>
-      </c>
     </row>
     <row r="911">
       <c r="A911" t="str">
@@ -39597,18 +37749,6 @@
       <c r="M911" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N911" t="str">
-        <v/>
-      </c>
-      <c r="O911" t="str">
-        <v/>
-      </c>
-      <c r="P911" t="str">
-        <v/>
-      </c>
-      <c r="Q911" t="str">
-        <v/>
-      </c>
     </row>
     <row r="912">
       <c r="A912" t="str">
@@ -39650,18 +37790,6 @@
       <c r="M912" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N912" t="str">
-        <v/>
-      </c>
-      <c r="O912" t="str">
-        <v/>
-      </c>
-      <c r="P912" t="str">
-        <v/>
-      </c>
-      <c r="Q912" t="str">
-        <v/>
-      </c>
     </row>
     <row r="913">
       <c r="A913" t="str">
@@ -39703,18 +37831,6 @@
       <c r="M913" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N913" t="str">
-        <v/>
-      </c>
-      <c r="O913" t="str">
-        <v/>
-      </c>
-      <c r="P913" t="str">
-        <v/>
-      </c>
-      <c r="Q913" t="str">
-        <v/>
-      </c>
     </row>
     <row r="914">
       <c r="A914" t="str">
@@ -39756,18 +37872,6 @@
       <c r="M914" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N914" t="str">
-        <v/>
-      </c>
-      <c r="O914" t="str">
-        <v/>
-      </c>
-      <c r="P914" t="str">
-        <v/>
-      </c>
-      <c r="Q914" t="str">
-        <v/>
-      </c>
     </row>
     <row r="915">
       <c r="A915" t="str">
@@ -39809,18 +37913,6 @@
       <c r="M915" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N915" t="str">
-        <v/>
-      </c>
-      <c r="O915" t="str">
-        <v/>
-      </c>
-      <c r="P915" t="str">
-        <v/>
-      </c>
-      <c r="Q915" t="str">
-        <v/>
-      </c>
     </row>
     <row r="916">
       <c r="A916" t="str">
@@ -39862,18 +37954,6 @@
       <c r="M916" t="str">
         <v>【ダブルフック】 フロント：#4・リア：#4</v>
       </c>
-      <c r="N916" t="str">
-        <v/>
-      </c>
-      <c r="O916" t="str">
-        <v/>
-      </c>
-      <c r="P916" t="str">
-        <v/>
-      </c>
-      <c r="Q916" t="str">
-        <v/>
-      </c>
     </row>
     <row r="917">
       <c r="A917" t="str">
@@ -39915,18 +37995,6 @@
       <c r="M917" t="str">
         <v>【ダブルフック】 フロント：#8・リア：#8</v>
       </c>
-      <c r="N917" t="str">
-        <v/>
-      </c>
-      <c r="O917" t="str">
-        <v/>
-      </c>
-      <c r="P917" t="str">
-        <v/>
-      </c>
-      <c r="Q917" t="str">
-        <v/>
-      </c>
     </row>
     <row r="918">
       <c r="A918" t="str">
@@ -39968,18 +38036,6 @@
       <c r="M918" t="str">
         <v>【ダブルフック】 フロント：#8・リア：#8</v>
       </c>
-      <c r="N918" t="str">
-        <v/>
-      </c>
-      <c r="O918" t="str">
-        <v/>
-      </c>
-      <c r="P918" t="str">
-        <v/>
-      </c>
-      <c r="Q918" t="str">
-        <v/>
-      </c>
     </row>
     <row r="919">
       <c r="A919" t="str">
@@ -40021,18 +38077,6 @@
       <c r="M919" t="str">
         <v>【ダブルフック】 フロント：#8・リア：#8</v>
       </c>
-      <c r="N919" t="str">
-        <v/>
-      </c>
-      <c r="O919" t="str">
-        <v/>
-      </c>
-      <c r="P919" t="str">
-        <v/>
-      </c>
-      <c r="Q919" t="str">
-        <v/>
-      </c>
     </row>
     <row r="920">
       <c r="A920" t="str">
@@ -40074,18 +38118,6 @@
       <c r="M920" t="str">
         <v>【ダブルフック】 フロント：#8・リア：#8</v>
       </c>
-      <c r="N920" t="str">
-        <v/>
-      </c>
-      <c r="O920" t="str">
-        <v/>
-      </c>
-      <c r="P920" t="str">
-        <v/>
-      </c>
-      <c r="Q920" t="str">
-        <v/>
-      </c>
     </row>
     <row r="921">
       <c r="A921" t="str">
@@ -40127,18 +38159,6 @@
       <c r="M921" t="str">
         <v>【ダブルフック】 フロント：#8・リア：#8</v>
       </c>
-      <c r="N921" t="str">
-        <v/>
-      </c>
-      <c r="O921" t="str">
-        <v/>
-      </c>
-      <c r="P921" t="str">
-        <v/>
-      </c>
-      <c r="Q921" t="str">
-        <v/>
-      </c>
     </row>
     <row r="922">
       <c r="A922" t="str">
@@ -40180,18 +38200,6 @@
       <c r="M922" t="str">
         <v>【ダブルフック】 フロント：#8・リア：#8</v>
       </c>
-      <c r="N922" t="str">
-        <v/>
-      </c>
-      <c r="O922" t="str">
-        <v/>
-      </c>
-      <c r="P922" t="str">
-        <v/>
-      </c>
-      <c r="Q922" t="str">
-        <v/>
-      </c>
     </row>
     <row r="923">
       <c r="A923" t="str">
@@ -40233,18 +38241,6 @@
       <c r="M923" t="str">
         <v>【ダブルフック】 フロント：#8・リア：#8</v>
       </c>
-      <c r="N923" t="str">
-        <v/>
-      </c>
-      <c r="O923" t="str">
-        <v/>
-      </c>
-      <c r="P923" t="str">
-        <v/>
-      </c>
-      <c r="Q923" t="str">
-        <v/>
-      </c>
     </row>
     <row r="924">
       <c r="A924" t="str">
@@ -40286,18 +38282,6 @@
       <c r="M924" t="str">
         <v>【ダブルフック】 フロント：#8・リア：#8</v>
       </c>
-      <c r="N924" t="str">
-        <v/>
-      </c>
-      <c r="O924" t="str">
-        <v/>
-      </c>
-      <c r="P924" t="str">
-        <v/>
-      </c>
-      <c r="Q924" t="str">
-        <v/>
-      </c>
     </row>
     <row r="925">
       <c r="A925" t="str">
@@ -40339,18 +38323,6 @@
       <c r="M925" t="str">
         <v>【ダブルフック】 フロント：#8・リア：#8</v>
       </c>
-      <c r="N925" t="str">
-        <v/>
-      </c>
-      <c r="O925" t="str">
-        <v/>
-      </c>
-      <c r="P925" t="str">
-        <v/>
-      </c>
-      <c r="Q925" t="str">
-        <v/>
-      </c>
     </row>
     <row r="926">
       <c r="A926" t="str">
@@ -40392,18 +38364,6 @@
       <c r="M926" t="str">
         <v>【ダブルフック】 フロント：#8・リア：#8</v>
       </c>
-      <c r="N926" t="str">
-        <v/>
-      </c>
-      <c r="O926" t="str">
-        <v/>
-      </c>
-      <c r="P926" t="str">
-        <v/>
-      </c>
-      <c r="Q926" t="str">
-        <v/>
-      </c>
     </row>
     <row r="927">
       <c r="A927" t="str">
@@ -40445,18 +38405,6 @@
       <c r="M927" t="str">
         <v>【ダブルフック】 フロント：#8・リア：#8</v>
       </c>
-      <c r="N927" t="str">
-        <v/>
-      </c>
-      <c r="O927" t="str">
-        <v/>
-      </c>
-      <c r="P927" t="str">
-        <v/>
-      </c>
-      <c r="Q927" t="str">
-        <v/>
-      </c>
     </row>
     <row r="928">
       <c r="A928" t="str">
@@ -40498,18 +38446,6 @@
       <c r="M928" t="str">
         <v>【ダブルフック】 フロント：#8・リア：#8</v>
       </c>
-      <c r="N928" t="str">
-        <v/>
-      </c>
-      <c r="O928" t="str">
-        <v/>
-      </c>
-      <c r="P928" t="str">
-        <v/>
-      </c>
-      <c r="Q928" t="str">
-        <v/>
-      </c>
     </row>
     <row r="929">
       <c r="A929" t="str">
@@ -40551,18 +38487,6 @@
       <c r="M929" t="str">
         <v>【ダブルフック】 フロント：#8・リア：#8</v>
       </c>
-      <c r="N929" t="str">
-        <v/>
-      </c>
-      <c r="O929" t="str">
-        <v/>
-      </c>
-      <c r="P929" t="str">
-        <v/>
-      </c>
-      <c r="Q929" t="str">
-        <v/>
-      </c>
     </row>
     <row r="930">
       <c r="A930" t="str">
@@ -40604,18 +38528,6 @@
       <c r="M930" t="str">
         <v>【ダブルフック】 フロント：#8・リア：#8</v>
       </c>
-      <c r="N930" t="str">
-        <v/>
-      </c>
-      <c r="O930" t="str">
-        <v/>
-      </c>
-      <c r="P930" t="str">
-        <v/>
-      </c>
-      <c r="Q930" t="str">
-        <v/>
-      </c>
     </row>
     <row r="931">
       <c r="A931" t="str">
@@ -40657,18 +38569,6 @@
       <c r="M931" t="str">
         <v>【ダブルフック】 フロント：#8・リア：#8</v>
       </c>
-      <c r="N931" t="str">
-        <v/>
-      </c>
-      <c r="O931" t="str">
-        <v/>
-      </c>
-      <c r="P931" t="str">
-        <v/>
-      </c>
-      <c r="Q931" t="str">
-        <v/>
-      </c>
     </row>
     <row r="932">
       <c r="A932" t="str">
@@ -40710,18 +38610,6 @@
       <c r="M932" t="str">
         <v>【ダブルフック】 フロント：#8・リア：#8</v>
       </c>
-      <c r="N932" t="str">
-        <v/>
-      </c>
-      <c r="O932" t="str">
-        <v/>
-      </c>
-      <c r="P932" t="str">
-        <v/>
-      </c>
-      <c r="Q932" t="str">
-        <v/>
-      </c>
     </row>
     <row r="933">
       <c r="A933" t="str">
@@ -40763,18 +38651,6 @@
       <c r="M933" t="str">
         <v>【ダブルフック】 フロント：#8・リア：#8</v>
       </c>
-      <c r="N933" t="str">
-        <v/>
-      </c>
-      <c r="O933" t="str">
-        <v/>
-      </c>
-      <c r="P933" t="str">
-        <v/>
-      </c>
-      <c r="Q933" t="str">
-        <v/>
-      </c>
     </row>
     <row r="934">
       <c r="A934" t="str">
@@ -40816,18 +38692,6 @@
       <c r="M934" t="str">
         <v>【ダブルフック】 フロント：#8・リア：#8</v>
       </c>
-      <c r="N934" t="str">
-        <v/>
-      </c>
-      <c r="O934" t="str">
-        <v/>
-      </c>
-      <c r="P934" t="str">
-        <v/>
-      </c>
-      <c r="Q934" t="str">
-        <v/>
-      </c>
     </row>
     <row r="935">
       <c r="A935" t="str">
@@ -40869,18 +38733,6 @@
       <c r="M935" t="str">
         <v>【ダブルフック】 フロント：#8・リア：#8</v>
       </c>
-      <c r="N935" t="str">
-        <v/>
-      </c>
-      <c r="O935" t="str">
-        <v/>
-      </c>
-      <c r="P935" t="str">
-        <v/>
-      </c>
-      <c r="Q935" t="str">
-        <v/>
-      </c>
     </row>
     <row r="936">
       <c r="A936" t="str">
@@ -40922,18 +38774,6 @@
       <c r="M936" t="str">
         <v>【ダブルフック】 フロント：#8・リア：#8</v>
       </c>
-      <c r="N936" t="str">
-        <v/>
-      </c>
-      <c r="O936" t="str">
-        <v/>
-      </c>
-      <c r="P936" t="str">
-        <v/>
-      </c>
-      <c r="Q936" t="str">
-        <v/>
-      </c>
     </row>
     <row r="937">
       <c r="A937" t="str">
@@ -40975,18 +38815,6 @@
       <c r="M937" t="str">
         <v>【ダブルフック】 フロント：#8・リア：#8</v>
       </c>
-      <c r="N937" t="str">
-        <v/>
-      </c>
-      <c r="O937" t="str">
-        <v/>
-      </c>
-      <c r="P937" t="str">
-        <v/>
-      </c>
-      <c r="Q937" t="str">
-        <v/>
-      </c>
     </row>
     <row r="938">
       <c r="A938" t="str">
@@ -41028,18 +38856,6 @@
       <c r="M938" t="str">
         <v>【ダブルフック】 フロント：#8・リア：#8</v>
       </c>
-      <c r="N938" t="str">
-        <v/>
-      </c>
-      <c r="O938" t="str">
-        <v/>
-      </c>
-      <c r="P938" t="str">
-        <v/>
-      </c>
-      <c r="Q938" t="str">
-        <v/>
-      </c>
     </row>
     <row r="939">
       <c r="A939" t="str">
@@ -41081,18 +38897,6 @@
       <c r="M939" t="str">
         <v>#2</v>
       </c>
-      <c r="N939" t="str">
-        <v/>
-      </c>
-      <c r="O939" t="str">
-        <v/>
-      </c>
-      <c r="P939" t="str">
-        <v/>
-      </c>
-      <c r="Q939" t="str">
-        <v/>
-      </c>
     </row>
     <row r="940">
       <c r="A940" t="str">
@@ -41134,18 +38938,6 @@
       <c r="M940" t="str">
         <v>#2</v>
       </c>
-      <c r="N940" t="str">
-        <v/>
-      </c>
-      <c r="O940" t="str">
-        <v/>
-      </c>
-      <c r="P940" t="str">
-        <v/>
-      </c>
-      <c r="Q940" t="str">
-        <v/>
-      </c>
     </row>
     <row r="941">
       <c r="A941" t="str">
@@ -41187,18 +38979,6 @@
       <c r="M941" t="str">
         <v>#2</v>
       </c>
-      <c r="N941" t="str">
-        <v/>
-      </c>
-      <c r="O941" t="str">
-        <v/>
-      </c>
-      <c r="P941" t="str">
-        <v/>
-      </c>
-      <c r="Q941" t="str">
-        <v/>
-      </c>
     </row>
     <row r="942">
       <c r="A942" t="str">
@@ -41240,18 +39020,6 @@
       <c r="M942" t="str">
         <v>#2</v>
       </c>
-      <c r="N942" t="str">
-        <v/>
-      </c>
-      <c r="O942" t="str">
-        <v/>
-      </c>
-      <c r="P942" t="str">
-        <v/>
-      </c>
-      <c r="Q942" t="str">
-        <v/>
-      </c>
     </row>
     <row r="943">
       <c r="A943" t="str">
@@ -41293,18 +39061,6 @@
       <c r="M943" t="str">
         <v>#2</v>
       </c>
-      <c r="N943" t="str">
-        <v/>
-      </c>
-      <c r="O943" t="str">
-        <v/>
-      </c>
-      <c r="P943" t="str">
-        <v/>
-      </c>
-      <c r="Q943" t="str">
-        <v/>
-      </c>
     </row>
     <row r="944">
       <c r="A944" t="str">
@@ -41346,18 +39102,6 @@
       <c r="M944" t="str">
         <v>#2</v>
       </c>
-      <c r="N944" t="str">
-        <v/>
-      </c>
-      <c r="O944" t="str">
-        <v/>
-      </c>
-      <c r="P944" t="str">
-        <v/>
-      </c>
-      <c r="Q944" t="str">
-        <v/>
-      </c>
     </row>
     <row r="945">
       <c r="A945" t="str">
@@ -41399,18 +39143,6 @@
       <c r="M945" t="str">
         <v>#2</v>
       </c>
-      <c r="N945" t="str">
-        <v/>
-      </c>
-      <c r="O945" t="str">
-        <v/>
-      </c>
-      <c r="P945" t="str">
-        <v/>
-      </c>
-      <c r="Q945" t="str">
-        <v/>
-      </c>
     </row>
     <row r="946">
       <c r="A946" t="str">
@@ -41452,18 +39184,6 @@
       <c r="M946" t="str">
         <v>#2</v>
       </c>
-      <c r="N946" t="str">
-        <v/>
-      </c>
-      <c r="O946" t="str">
-        <v/>
-      </c>
-      <c r="P946" t="str">
-        <v/>
-      </c>
-      <c r="Q946" t="str">
-        <v/>
-      </c>
     </row>
     <row r="947">
       <c r="A947" t="str">
@@ -41505,18 +39225,6 @@
       <c r="M947" t="str">
         <v>#2</v>
       </c>
-      <c r="N947" t="str">
-        <v/>
-      </c>
-      <c r="O947" t="str">
-        <v/>
-      </c>
-      <c r="P947" t="str">
-        <v/>
-      </c>
-      <c r="Q947" t="str">
-        <v/>
-      </c>
     </row>
     <row r="948">
       <c r="A948" t="str">
@@ -41558,18 +39266,6 @@
       <c r="M948" t="str">
         <v>#2</v>
       </c>
-      <c r="N948" t="str">
-        <v/>
-      </c>
-      <c r="O948" t="str">
-        <v/>
-      </c>
-      <c r="P948" t="str">
-        <v/>
-      </c>
-      <c r="Q948" t="str">
-        <v/>
-      </c>
     </row>
     <row r="949">
       <c r="A949" t="str">
@@ -41611,18 +39307,6 @@
       <c r="M949" t="str">
         <v>#2</v>
       </c>
-      <c r="N949" t="str">
-        <v/>
-      </c>
-      <c r="O949" t="str">
-        <v/>
-      </c>
-      <c r="P949" t="str">
-        <v/>
-      </c>
-      <c r="Q949" t="str">
-        <v/>
-      </c>
     </row>
     <row r="950">
       <c r="A950" t="str">
@@ -41664,18 +39348,6 @@
       <c r="M950" t="str">
         <v>#2</v>
       </c>
-      <c r="N950" t="str">
-        <v/>
-      </c>
-      <c r="O950" t="str">
-        <v/>
-      </c>
-      <c r="P950" t="str">
-        <v/>
-      </c>
-      <c r="Q950" t="str">
-        <v/>
-      </c>
     </row>
     <row r="951">
       <c r="A951" t="str">
@@ -41717,18 +39389,6 @@
       <c r="M951" t="str">
         <v>#2</v>
       </c>
-      <c r="N951" t="str">
-        <v/>
-      </c>
-      <c r="O951" t="str">
-        <v/>
-      </c>
-      <c r="P951" t="str">
-        <v/>
-      </c>
-      <c r="Q951" t="str">
-        <v/>
-      </c>
     </row>
     <row r="952">
       <c r="A952" t="str">
@@ -41770,18 +39430,6 @@
       <c r="M952" t="str">
         <v>#2</v>
       </c>
-      <c r="N952" t="str">
-        <v/>
-      </c>
-      <c r="O952" t="str">
-        <v/>
-      </c>
-      <c r="P952" t="str">
-        <v/>
-      </c>
-      <c r="Q952" t="str">
-        <v/>
-      </c>
     </row>
     <row r="953">
       <c r="A953" t="str">
@@ -41823,18 +39471,6 @@
       <c r="M953" t="str">
         <v>#2</v>
       </c>
-      <c r="N953" t="str">
-        <v/>
-      </c>
-      <c r="O953" t="str">
-        <v/>
-      </c>
-      <c r="P953" t="str">
-        <v/>
-      </c>
-      <c r="Q953" t="str">
-        <v/>
-      </c>
     </row>
     <row r="954">
       <c r="A954" t="str">
@@ -41876,18 +39512,6 @@
       <c r="M954" t="str">
         <v>#2</v>
       </c>
-      <c r="N954" t="str">
-        <v/>
-      </c>
-      <c r="O954" t="str">
-        <v/>
-      </c>
-      <c r="P954" t="str">
-        <v/>
-      </c>
-      <c r="Q954" t="str">
-        <v/>
-      </c>
     </row>
     <row r="955">
       <c r="A955" t="str">
@@ -41929,18 +39553,6 @@
       <c r="M955" t="str">
         <v>#2</v>
       </c>
-      <c r="N955" t="str">
-        <v/>
-      </c>
-      <c r="O955" t="str">
-        <v/>
-      </c>
-      <c r="P955" t="str">
-        <v/>
-      </c>
-      <c r="Q955" t="str">
-        <v/>
-      </c>
     </row>
     <row r="956">
       <c r="A956" t="str">
@@ -41982,18 +39594,6 @@
       <c r="M956" t="str">
         <v>#2</v>
       </c>
-      <c r="N956" t="str">
-        <v/>
-      </c>
-      <c r="O956" t="str">
-        <v/>
-      </c>
-      <c r="P956" t="str">
-        <v/>
-      </c>
-      <c r="Q956" t="str">
-        <v/>
-      </c>
     </row>
     <row r="957">
       <c r="A957" t="str">
@@ -42035,18 +39635,6 @@
       <c r="M957" t="str">
         <v>#2</v>
       </c>
-      <c r="N957" t="str">
-        <v/>
-      </c>
-      <c r="O957" t="str">
-        <v/>
-      </c>
-      <c r="P957" t="str">
-        <v/>
-      </c>
-      <c r="Q957" t="str">
-        <v/>
-      </c>
     </row>
     <row r="958">
       <c r="A958" t="str">
@@ -42088,18 +39676,6 @@
       <c r="M958" t="str">
         <v>#2</v>
       </c>
-      <c r="N958" t="str">
-        <v/>
-      </c>
-      <c r="O958" t="str">
-        <v/>
-      </c>
-      <c r="P958" t="str">
-        <v/>
-      </c>
-      <c r="Q958" t="str">
-        <v/>
-      </c>
     </row>
     <row r="959">
       <c r="A959" t="str">
@@ -42141,18 +39717,6 @@
       <c r="M959" t="str">
         <v>#2</v>
       </c>
-      <c r="N959" t="str">
-        <v/>
-      </c>
-      <c r="O959" t="str">
-        <v/>
-      </c>
-      <c r="P959" t="str">
-        <v/>
-      </c>
-      <c r="Q959" t="str">
-        <v/>
-      </c>
     </row>
     <row r="960">
       <c r="A960" t="str">
@@ -42194,18 +39758,6 @@
       <c r="M960" t="str">
         <v>#2</v>
       </c>
-      <c r="N960" t="str">
-        <v/>
-      </c>
-      <c r="O960" t="str">
-        <v/>
-      </c>
-      <c r="P960" t="str">
-        <v/>
-      </c>
-      <c r="Q960" t="str">
-        <v/>
-      </c>
     </row>
     <row r="961">
       <c r="A961" t="str">
@@ -42247,18 +39799,6 @@
       <c r="M961" t="str">
         <v>#2</v>
       </c>
-      <c r="N961" t="str">
-        <v/>
-      </c>
-      <c r="O961" t="str">
-        <v/>
-      </c>
-      <c r="P961" t="str">
-        <v/>
-      </c>
-      <c r="Q961" t="str">
-        <v/>
-      </c>
     </row>
     <row r="962">
       <c r="A962" t="str">
@@ -42300,18 +39840,6 @@
       <c r="M962" t="str">
         <v>#2</v>
       </c>
-      <c r="N962" t="str">
-        <v/>
-      </c>
-      <c r="O962" t="str">
-        <v/>
-      </c>
-      <c r="P962" t="str">
-        <v/>
-      </c>
-      <c r="Q962" t="str">
-        <v/>
-      </c>
     </row>
     <row r="963">
       <c r="A963" t="str">
@@ -42353,18 +39881,6 @@
       <c r="M963" t="str">
         <v>#2</v>
       </c>
-      <c r="N963" t="str">
-        <v/>
-      </c>
-      <c r="O963" t="str">
-        <v/>
-      </c>
-      <c r="P963" t="str">
-        <v/>
-      </c>
-      <c r="Q963" t="str">
-        <v/>
-      </c>
     </row>
     <row r="964">
       <c r="A964" t="str">
@@ -42406,18 +39922,6 @@
       <c r="M964" t="str">
         <v>#2</v>
       </c>
-      <c r="N964" t="str">
-        <v/>
-      </c>
-      <c r="O964" t="str">
-        <v/>
-      </c>
-      <c r="P964" t="str">
-        <v/>
-      </c>
-      <c r="Q964" t="str">
-        <v/>
-      </c>
     </row>
     <row r="965">
       <c r="A965" t="str">
@@ -42459,18 +39963,6 @@
       <c r="M965" t="str">
         <v>#2</v>
       </c>
-      <c r="N965" t="str">
-        <v/>
-      </c>
-      <c r="O965" t="str">
-        <v/>
-      </c>
-      <c r="P965" t="str">
-        <v/>
-      </c>
-      <c r="Q965" t="str">
-        <v/>
-      </c>
     </row>
     <row r="966">
       <c r="A966" t="str">
@@ -42512,18 +40004,6 @@
       <c r="M966" t="str">
         <v>#2</v>
       </c>
-      <c r="N966" t="str">
-        <v/>
-      </c>
-      <c r="O966" t="str">
-        <v/>
-      </c>
-      <c r="P966" t="str">
-        <v/>
-      </c>
-      <c r="Q966" t="str">
-        <v/>
-      </c>
     </row>
     <row r="967">
       <c r="A967" t="str">
@@ -42565,18 +40045,6 @@
       <c r="M967" t="str">
         <v>#2</v>
       </c>
-      <c r="N967" t="str">
-        <v/>
-      </c>
-      <c r="O967" t="str">
-        <v/>
-      </c>
-      <c r="P967" t="str">
-        <v/>
-      </c>
-      <c r="Q967" t="str">
-        <v/>
-      </c>
     </row>
     <row r="968">
       <c r="A968" t="str">
@@ -42618,18 +40086,6 @@
       <c r="M968" t="str">
         <v>#2</v>
       </c>
-      <c r="N968" t="str">
-        <v/>
-      </c>
-      <c r="O968" t="str">
-        <v/>
-      </c>
-      <c r="P968" t="str">
-        <v/>
-      </c>
-      <c r="Q968" t="str">
-        <v/>
-      </c>
     </row>
     <row r="969">
       <c r="A969" t="str">
@@ -42671,18 +40127,6 @@
       <c r="M969" t="str">
         <v>#2</v>
       </c>
-      <c r="N969" t="str">
-        <v/>
-      </c>
-      <c r="O969" t="str">
-        <v/>
-      </c>
-      <c r="P969" t="str">
-        <v/>
-      </c>
-      <c r="Q969" t="str">
-        <v/>
-      </c>
     </row>
     <row r="970">
       <c r="A970" t="str">
@@ -42724,18 +40168,6 @@
       <c r="M970" t="str">
         <v>#2</v>
       </c>
-      <c r="N970" t="str">
-        <v/>
-      </c>
-      <c r="O970" t="str">
-        <v/>
-      </c>
-      <c r="P970" t="str">
-        <v/>
-      </c>
-      <c r="Q970" t="str">
-        <v/>
-      </c>
     </row>
     <row r="971">
       <c r="A971" t="str">
@@ -42777,18 +40209,6 @@
       <c r="M971" t="str">
         <v>#2</v>
       </c>
-      <c r="N971" t="str">
-        <v/>
-      </c>
-      <c r="O971" t="str">
-        <v/>
-      </c>
-      <c r="P971" t="str">
-        <v/>
-      </c>
-      <c r="Q971" t="str">
-        <v/>
-      </c>
     </row>
     <row r="972">
       <c r="A972" t="str">
@@ -42830,18 +40250,6 @@
       <c r="M972" t="str">
         <v>#2</v>
       </c>
-      <c r="N972" t="str">
-        <v/>
-      </c>
-      <c r="O972" t="str">
-        <v/>
-      </c>
-      <c r="P972" t="str">
-        <v/>
-      </c>
-      <c r="Q972" t="str">
-        <v/>
-      </c>
     </row>
     <row r="973">
       <c r="A973" t="str">
@@ -42883,18 +40291,6 @@
       <c r="M973" t="str">
         <v>#2</v>
       </c>
-      <c r="N973" t="str">
-        <v/>
-      </c>
-      <c r="O973" t="str">
-        <v/>
-      </c>
-      <c r="P973" t="str">
-        <v/>
-      </c>
-      <c r="Q973" t="str">
-        <v/>
-      </c>
     </row>
     <row r="974">
       <c r="A974" t="str">
@@ -42936,18 +40332,6 @@
       <c r="M974" t="str">
         <v>#2</v>
       </c>
-      <c r="N974" t="str">
-        <v/>
-      </c>
-      <c r="O974" t="str">
-        <v/>
-      </c>
-      <c r="P974" t="str">
-        <v/>
-      </c>
-      <c r="Q974" t="str">
-        <v/>
-      </c>
     </row>
     <row r="975">
       <c r="A975" t="str">
@@ -42989,18 +40373,6 @@
       <c r="M975" t="str">
         <v>#2</v>
       </c>
-      <c r="N975" t="str">
-        <v/>
-      </c>
-      <c r="O975" t="str">
-        <v/>
-      </c>
-      <c r="P975" t="str">
-        <v/>
-      </c>
-      <c r="Q975" t="str">
-        <v/>
-      </c>
     </row>
     <row r="976">
       <c r="A976" t="str">
@@ -43042,18 +40414,6 @@
       <c r="M976" t="str">
         <v>#2</v>
       </c>
-      <c r="N976" t="str">
-        <v/>
-      </c>
-      <c r="O976" t="str">
-        <v/>
-      </c>
-      <c r="P976" t="str">
-        <v/>
-      </c>
-      <c r="Q976" t="str">
-        <v/>
-      </c>
     </row>
     <row r="977">
       <c r="A977" t="str">
@@ -43095,18 +40455,6 @@
       <c r="M977" t="str">
         <v>#2</v>
       </c>
-      <c r="N977" t="str">
-        <v/>
-      </c>
-      <c r="O977" t="str">
-        <v/>
-      </c>
-      <c r="P977" t="str">
-        <v/>
-      </c>
-      <c r="Q977" t="str">
-        <v/>
-      </c>
     </row>
     <row r="978">
       <c r="A978" t="str">
@@ -43148,18 +40496,6 @@
       <c r="M978" t="str">
         <v>#2</v>
       </c>
-      <c r="N978" t="str">
-        <v/>
-      </c>
-      <c r="O978" t="str">
-        <v/>
-      </c>
-      <c r="P978" t="str">
-        <v/>
-      </c>
-      <c r="Q978" t="str">
-        <v/>
-      </c>
     </row>
     <row r="979">
       <c r="A979" t="str">
@@ -43201,18 +40537,6 @@
       <c r="M979" t="str">
         <v>#2</v>
       </c>
-      <c r="N979" t="str">
-        <v/>
-      </c>
-      <c r="O979" t="str">
-        <v/>
-      </c>
-      <c r="P979" t="str">
-        <v/>
-      </c>
-      <c r="Q979" t="str">
-        <v/>
-      </c>
     </row>
     <row r="980">
       <c r="A980" t="str">
@@ -43254,18 +40578,6 @@
       <c r="M980" t="str">
         <v>#2</v>
       </c>
-      <c r="N980" t="str">
-        <v/>
-      </c>
-      <c r="O980" t="str">
-        <v/>
-      </c>
-      <c r="P980" t="str">
-        <v/>
-      </c>
-      <c r="Q980" t="str">
-        <v/>
-      </c>
     </row>
     <row r="981">
       <c r="A981" t="str">
@@ -43307,18 +40619,6 @@
       <c r="M981" t="str">
         <v>#2</v>
       </c>
-      <c r="N981" t="str">
-        <v/>
-      </c>
-      <c r="O981" t="str">
-        <v/>
-      </c>
-      <c r="P981" t="str">
-        <v/>
-      </c>
-      <c r="Q981" t="str">
-        <v/>
-      </c>
     </row>
     <row r="982">
       <c r="A982" t="str">
@@ -43360,18 +40660,6 @@
       <c r="M982" t="str">
         <v>#2</v>
       </c>
-      <c r="N982" t="str">
-        <v/>
-      </c>
-      <c r="O982" t="str">
-        <v/>
-      </c>
-      <c r="P982" t="str">
-        <v/>
-      </c>
-      <c r="Q982" t="str">
-        <v/>
-      </c>
     </row>
     <row r="983">
       <c r="A983" t="str">
@@ -43413,18 +40701,6 @@
       <c r="M983" t="str">
         <v>#2</v>
       </c>
-      <c r="N983" t="str">
-        <v/>
-      </c>
-      <c r="O983" t="str">
-        <v/>
-      </c>
-      <c r="P983" t="str">
-        <v/>
-      </c>
-      <c r="Q983" t="str">
-        <v/>
-      </c>
     </row>
     <row r="984">
       <c r="A984" t="str">
@@ -43466,18 +40742,6 @@
       <c r="M984" t="str">
         <v>#2</v>
       </c>
-      <c r="N984" t="str">
-        <v/>
-      </c>
-      <c r="O984" t="str">
-        <v/>
-      </c>
-      <c r="P984" t="str">
-        <v/>
-      </c>
-      <c r="Q984" t="str">
-        <v/>
-      </c>
     </row>
     <row r="985">
       <c r="A985" t="str">
@@ -43519,18 +40783,6 @@
       <c r="M985" t="str">
         <v>#2</v>
       </c>
-      <c r="N985" t="str">
-        <v/>
-      </c>
-      <c r="O985" t="str">
-        <v/>
-      </c>
-      <c r="P985" t="str">
-        <v/>
-      </c>
-      <c r="Q985" t="str">
-        <v/>
-      </c>
     </row>
     <row r="986">
       <c r="A986" t="str">
@@ -43572,18 +40824,6 @@
       <c r="M986" t="str">
         <v>#2</v>
       </c>
-      <c r="N986" t="str">
-        <v/>
-      </c>
-      <c r="O986" t="str">
-        <v/>
-      </c>
-      <c r="P986" t="str">
-        <v/>
-      </c>
-      <c r="Q986" t="str">
-        <v/>
-      </c>
     </row>
     <row r="987">
       <c r="A987" t="str">
@@ -43625,18 +40865,6 @@
       <c r="M987" t="str">
         <v>#2</v>
       </c>
-      <c r="N987" t="str">
-        <v/>
-      </c>
-      <c r="O987" t="str">
-        <v/>
-      </c>
-      <c r="P987" t="str">
-        <v/>
-      </c>
-      <c r="Q987" t="str">
-        <v/>
-      </c>
     </row>
     <row r="988">
       <c r="A988" t="str">
@@ -43678,18 +40906,6 @@
       <c r="M988" t="str">
         <v>#2</v>
       </c>
-      <c r="N988" t="str">
-        <v/>
-      </c>
-      <c r="O988" t="str">
-        <v/>
-      </c>
-      <c r="P988" t="str">
-        <v/>
-      </c>
-      <c r="Q988" t="str">
-        <v/>
-      </c>
     </row>
     <row r="989">
       <c r="A989" t="str">
@@ -43731,18 +40947,6 @@
       <c r="M989" t="str">
         <v>【EGトレブルマジック】 フロント：#4・リア：#5</v>
       </c>
-      <c r="N989" t="str">
-        <v>－</v>
-      </c>
-      <c r="O989" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P989" t="str">
-        <v/>
-      </c>
-      <c r="Q989" t="str">
-        <v/>
-      </c>
     </row>
     <row r="990">
       <c r="A990" t="str">
@@ -43784,18 +40988,6 @@
       <c r="M990" t="str">
         <v>【EGトレブルマジック】 フロント：#4・リア：#5</v>
       </c>
-      <c r="N990" t="str">
-        <v>－</v>
-      </c>
-      <c r="O990" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P990" t="str">
-        <v/>
-      </c>
-      <c r="Q990" t="str">
-        <v/>
-      </c>
     </row>
     <row r="991">
       <c r="A991" t="str">
@@ -43837,18 +41029,6 @@
       <c r="M991" t="str">
         <v>【EGトレブルマジック】 フロント：#4・リア：#5</v>
       </c>
-      <c r="N991" t="str">
-        <v>－</v>
-      </c>
-      <c r="O991" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P991" t="str">
-        <v/>
-      </c>
-      <c r="Q991" t="str">
-        <v/>
-      </c>
     </row>
     <row r="992">
       <c r="A992" t="str">
@@ -43890,18 +41070,6 @@
       <c r="M992" t="str">
         <v>【EGトレブルマジック】 フロント：#4・リア：#5</v>
       </c>
-      <c r="N992" t="str">
-        <v>－</v>
-      </c>
-      <c r="O992" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P992" t="str">
-        <v/>
-      </c>
-      <c r="Q992" t="str">
-        <v/>
-      </c>
     </row>
     <row r="993">
       <c r="A993" t="str">
@@ -43943,18 +41111,6 @@
       <c r="M993" t="str">
         <v>【EGトレブルマジック】 フロント：#4・リア：#5</v>
       </c>
-      <c r="N993" t="str">
-        <v>－</v>
-      </c>
-      <c r="O993" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P993" t="str">
-        <v/>
-      </c>
-      <c r="Q993" t="str">
-        <v/>
-      </c>
     </row>
     <row r="994">
       <c r="A994" t="str">
@@ -43996,18 +41152,6 @@
       <c r="M994" t="str">
         <v>【EGトレブルマジック】 フロント：#4・リア：#5</v>
       </c>
-      <c r="N994" t="str">
-        <v>－</v>
-      </c>
-      <c r="O994" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P994" t="str">
-        <v/>
-      </c>
-      <c r="Q994" t="str">
-        <v/>
-      </c>
     </row>
     <row r="995">
       <c r="A995" t="str">
@@ -44049,18 +41193,6 @@
       <c r="M995" t="str">
         <v>【EGトレブルマジック】 フロント：#4・リア：#5</v>
       </c>
-      <c r="N995" t="str">
-        <v>－</v>
-      </c>
-      <c r="O995" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P995" t="str">
-        <v/>
-      </c>
-      <c r="Q995" t="str">
-        <v/>
-      </c>
     </row>
     <row r="996">
       <c r="A996" t="str">
@@ -44102,18 +41234,6 @@
       <c r="M996" t="str">
         <v>【EGトレブルマジック】 フロント：#4・リア：#5</v>
       </c>
-      <c r="N996" t="str">
-        <v>－</v>
-      </c>
-      <c r="O996" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P996" t="str">
-        <v/>
-      </c>
-      <c r="Q996" t="str">
-        <v/>
-      </c>
     </row>
     <row r="997">
       <c r="A997" t="str">
@@ -44155,18 +41275,6 @@
       <c r="M997" t="str">
         <v>【EGトレブルマジック】 フロント：#4・リア：#5</v>
       </c>
-      <c r="N997" t="str">
-        <v>－</v>
-      </c>
-      <c r="O997" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P997" t="str">
-        <v/>
-      </c>
-      <c r="Q997" t="str">
-        <v/>
-      </c>
     </row>
     <row r="998">
       <c r="A998" t="str">
@@ -44208,18 +41316,6 @@
       <c r="M998" t="str">
         <v>【EGトレブルマジック】 フロント：#4・リア：#5</v>
       </c>
-      <c r="N998" t="str">
-        <v>－</v>
-      </c>
-      <c r="O998" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P998" t="str">
-        <v/>
-      </c>
-      <c r="Q998" t="str">
-        <v/>
-      </c>
     </row>
     <row r="999">
       <c r="A999" t="str">
@@ -44261,18 +41357,6 @@
       <c r="M999" t="str">
         <v>【EGトレブルマジック】 フロント：#4・リア：#5</v>
       </c>
-      <c r="N999" t="str">
-        <v>－</v>
-      </c>
-      <c r="O999" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P999" t="str">
-        <v/>
-      </c>
-      <c r="Q999" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1000">
       <c r="A1000" t="str">
@@ -44314,18 +41398,6 @@
       <c r="M1000" t="str">
         <v>【EGトレブルマジック】 フロント：#4・リア：#5</v>
       </c>
-      <c r="N1000" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1000" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1000" t="str">
-        <v/>
-      </c>
-      <c r="Q1000" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1001">
       <c r="A1001" t="str">
@@ -44367,18 +41439,6 @@
       <c r="M1001" t="str">
         <v>【EGトレブルマジック】 フロント：#4・リア：#5</v>
       </c>
-      <c r="N1001" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1001" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1001" t="str">
-        <v/>
-      </c>
-      <c r="Q1001" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1002">
       <c r="A1002" t="str">
@@ -44420,18 +41480,6 @@
       <c r="M1002" t="str">
         <v/>
       </c>
-      <c r="N1002" t="str">
-        <v/>
-      </c>
-      <c r="O1002" t="str">
-        <v/>
-      </c>
-      <c r="P1002" t="str">
-        <v/>
-      </c>
-      <c r="Q1002" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1003">
       <c r="A1003" t="str">
@@ -44473,18 +41521,6 @@
       <c r="M1003" t="str">
         <v/>
       </c>
-      <c r="N1003" t="str">
-        <v/>
-      </c>
-      <c r="O1003" t="str">
-        <v/>
-      </c>
-      <c r="P1003" t="str">
-        <v/>
-      </c>
-      <c r="Q1003" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1004">
       <c r="A1004" t="str">
@@ -44526,18 +41562,6 @@
       <c r="M1004" t="str">
         <v/>
       </c>
-      <c r="N1004" t="str">
-        <v/>
-      </c>
-      <c r="O1004" t="str">
-        <v/>
-      </c>
-      <c r="P1004" t="str">
-        <v/>
-      </c>
-      <c r="Q1004" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1005">
       <c r="A1005" t="str">
@@ -44579,18 +41603,6 @@
       <c r="M1005" t="str">
         <v/>
       </c>
-      <c r="N1005" t="str">
-        <v/>
-      </c>
-      <c r="O1005" t="str">
-        <v/>
-      </c>
-      <c r="P1005" t="str">
-        <v/>
-      </c>
-      <c r="Q1005" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1006">
       <c r="A1006" t="str">
@@ -44632,18 +41644,6 @@
       <c r="M1006" t="str">
         <v/>
       </c>
-      <c r="N1006" t="str">
-        <v/>
-      </c>
-      <c r="O1006" t="str">
-        <v/>
-      </c>
-      <c r="P1006" t="str">
-        <v/>
-      </c>
-      <c r="Q1006" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1007">
       <c r="A1007" t="str">
@@ -44685,18 +41685,6 @@
       <c r="M1007" t="str">
         <v/>
       </c>
-      <c r="N1007" t="str">
-        <v/>
-      </c>
-      <c r="O1007" t="str">
-        <v/>
-      </c>
-      <c r="P1007" t="str">
-        <v/>
-      </c>
-      <c r="Q1007" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1008">
       <c r="A1008" t="str">
@@ -44738,18 +41726,6 @@
       <c r="M1008" t="str">
         <v/>
       </c>
-      <c r="N1008" t="str">
-        <v/>
-      </c>
-      <c r="O1008" t="str">
-        <v/>
-      </c>
-      <c r="P1008" t="str">
-        <v/>
-      </c>
-      <c r="Q1008" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1009">
       <c r="A1009" t="str">
@@ -44791,18 +41767,6 @@
       <c r="M1009" t="str">
         <v/>
       </c>
-      <c r="N1009" t="str">
-        <v/>
-      </c>
-      <c r="O1009" t="str">
-        <v/>
-      </c>
-      <c r="P1009" t="str">
-        <v/>
-      </c>
-      <c r="Q1009" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1010">
       <c r="A1010" t="str">
@@ -44844,18 +41808,6 @@
       <c r="M1010" t="str">
         <v/>
       </c>
-      <c r="N1010" t="str">
-        <v/>
-      </c>
-      <c r="O1010" t="str">
-        <v/>
-      </c>
-      <c r="P1010" t="str">
-        <v/>
-      </c>
-      <c r="Q1010" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1011">
       <c r="A1011" t="str">
@@ -44897,18 +41849,6 @@
       <c r="M1011" t="str">
         <v/>
       </c>
-      <c r="N1011" t="str">
-        <v/>
-      </c>
-      <c r="O1011" t="str">
-        <v/>
-      </c>
-      <c r="P1011" t="str">
-        <v/>
-      </c>
-      <c r="Q1011" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1012">
       <c r="A1012" t="str">
@@ -44950,18 +41890,6 @@
       <c r="M1012" t="str">
         <v/>
       </c>
-      <c r="N1012" t="str">
-        <v/>
-      </c>
-      <c r="O1012" t="str">
-        <v/>
-      </c>
-      <c r="P1012" t="str">
-        <v/>
-      </c>
-      <c r="Q1012" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1013">
       <c r="A1013" t="str">
@@ -45003,18 +41931,6 @@
       <c r="M1013" t="str">
         <v/>
       </c>
-      <c r="N1013" t="str">
-        <v/>
-      </c>
-      <c r="O1013" t="str">
-        <v/>
-      </c>
-      <c r="P1013" t="str">
-        <v/>
-      </c>
-      <c r="Q1013" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1014">
       <c r="A1014" t="str">
@@ -45056,18 +41972,6 @@
       <c r="M1014" t="str">
         <v/>
       </c>
-      <c r="N1014" t="str">
-        <v/>
-      </c>
-      <c r="O1014" t="str">
-        <v/>
-      </c>
-      <c r="P1014" t="str">
-        <v/>
-      </c>
-      <c r="Q1014" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1015">
       <c r="A1015" t="str">
@@ -45109,18 +42013,6 @@
       <c r="M1015" t="str">
         <v/>
       </c>
-      <c r="N1015" t="str">
-        <v/>
-      </c>
-      <c r="O1015" t="str">
-        <v/>
-      </c>
-      <c r="P1015" t="str">
-        <v/>
-      </c>
-      <c r="Q1015" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1016">
       <c r="A1016" t="str">
@@ -45162,18 +42054,6 @@
       <c r="M1016" t="str">
         <v/>
       </c>
-      <c r="N1016" t="str">
-        <v/>
-      </c>
-      <c r="O1016" t="str">
-        <v/>
-      </c>
-      <c r="P1016" t="str">
-        <v/>
-      </c>
-      <c r="Q1016" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1017">
       <c r="A1017" t="str">
@@ -45215,18 +42095,6 @@
       <c r="M1017" t="str">
         <v/>
       </c>
-      <c r="N1017" t="str">
-        <v/>
-      </c>
-      <c r="O1017" t="str">
-        <v/>
-      </c>
-      <c r="P1017" t="str">
-        <v/>
-      </c>
-      <c r="Q1017" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1018">
       <c r="A1018" t="str">
@@ -45268,18 +42136,6 @@
       <c r="M1018" t="str">
         <v/>
       </c>
-      <c r="N1018" t="str">
-        <v/>
-      </c>
-      <c r="O1018" t="str">
-        <v/>
-      </c>
-      <c r="P1018" t="str">
-        <v/>
-      </c>
-      <c r="Q1018" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1019">
       <c r="A1019" t="str">
@@ -45321,18 +42177,6 @@
       <c r="M1019" t="str">
         <v/>
       </c>
-      <c r="N1019" t="str">
-        <v/>
-      </c>
-      <c r="O1019" t="str">
-        <v/>
-      </c>
-      <c r="P1019" t="str">
-        <v/>
-      </c>
-      <c r="Q1019" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1020">
       <c r="A1020" t="str">
@@ -45374,18 +42218,6 @@
       <c r="M1020" t="str">
         <v/>
       </c>
-      <c r="N1020" t="str">
-        <v/>
-      </c>
-      <c r="O1020" t="str">
-        <v/>
-      </c>
-      <c r="P1020" t="str">
-        <v/>
-      </c>
-      <c r="Q1020" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1021">
       <c r="A1021" t="str">
@@ -45427,18 +42259,6 @@
       <c r="M1021" t="str">
         <v/>
       </c>
-      <c r="N1021" t="str">
-        <v/>
-      </c>
-      <c r="O1021" t="str">
-        <v/>
-      </c>
-      <c r="P1021" t="str">
-        <v/>
-      </c>
-      <c r="Q1021" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1022">
       <c r="A1022" t="str">
@@ -45480,18 +42300,6 @@
       <c r="M1022" t="str">
         <v/>
       </c>
-      <c r="N1022" t="str">
-        <v/>
-      </c>
-      <c r="O1022" t="str">
-        <v/>
-      </c>
-      <c r="P1022" t="str">
-        <v/>
-      </c>
-      <c r="Q1022" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1023">
       <c r="A1023" t="str">
@@ -45533,18 +42341,6 @@
       <c r="M1023" t="str">
         <v/>
       </c>
-      <c r="N1023" t="str">
-        <v/>
-      </c>
-      <c r="O1023" t="str">
-        <v/>
-      </c>
-      <c r="P1023" t="str">
-        <v/>
-      </c>
-      <c r="Q1023" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1024">
       <c r="A1024" t="str">
@@ -45586,18 +42382,6 @@
       <c r="M1024" t="str">
         <v/>
       </c>
-      <c r="N1024" t="str">
-        <v/>
-      </c>
-      <c r="O1024" t="str">
-        <v/>
-      </c>
-      <c r="P1024" t="str">
-        <v/>
-      </c>
-      <c r="Q1024" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1025">
       <c r="A1025" t="str">
@@ -45639,18 +42423,6 @@
       <c r="M1025" t="str">
         <v/>
       </c>
-      <c r="N1025" t="str">
-        <v/>
-      </c>
-      <c r="O1025" t="str">
-        <v/>
-      </c>
-      <c r="P1025" t="str">
-        <v/>
-      </c>
-      <c r="Q1025" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1026">
       <c r="A1026" t="str">
@@ -45692,18 +42464,6 @@
       <c r="M1026" t="str">
         <v/>
       </c>
-      <c r="N1026" t="str">
-        <v/>
-      </c>
-      <c r="O1026" t="str">
-        <v/>
-      </c>
-      <c r="P1026" t="str">
-        <v/>
-      </c>
-      <c r="Q1026" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1027">
       <c r="A1027" t="str">
@@ -45745,18 +42505,6 @@
       <c r="M1027" t="str">
         <v/>
       </c>
-      <c r="N1027" t="str">
-        <v/>
-      </c>
-      <c r="O1027" t="str">
-        <v/>
-      </c>
-      <c r="P1027" t="str">
-        <v/>
-      </c>
-      <c r="Q1027" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1028">
       <c r="A1028" t="str">
@@ -45798,18 +42546,6 @@
       <c r="M1028" t="str">
         <v/>
       </c>
-      <c r="N1028" t="str">
-        <v/>
-      </c>
-      <c r="O1028" t="str">
-        <v/>
-      </c>
-      <c r="P1028" t="str">
-        <v/>
-      </c>
-      <c r="Q1028" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1029">
       <c r="A1029" t="str">
@@ -45851,18 +42587,6 @@
       <c r="M1029" t="str">
         <v/>
       </c>
-      <c r="N1029" t="str">
-        <v/>
-      </c>
-      <c r="O1029" t="str">
-        <v/>
-      </c>
-      <c r="P1029" t="str">
-        <v/>
-      </c>
-      <c r="Q1029" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1030">
       <c r="A1030" t="str">
@@ -45904,18 +42628,6 @@
       <c r="M1030" t="str">
         <v/>
       </c>
-      <c r="N1030" t="str">
-        <v/>
-      </c>
-      <c r="O1030" t="str">
-        <v/>
-      </c>
-      <c r="P1030" t="str">
-        <v/>
-      </c>
-      <c r="Q1030" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1031">
       <c r="A1031" t="str">
@@ -45957,18 +42669,6 @@
       <c r="M1031" t="str">
         <v/>
       </c>
-      <c r="N1031" t="str">
-        <v/>
-      </c>
-      <c r="O1031" t="str">
-        <v/>
-      </c>
-      <c r="P1031" t="str">
-        <v/>
-      </c>
-      <c r="Q1031" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1032">
       <c r="A1032" t="str">
@@ -46010,18 +42710,6 @@
       <c r="M1032" t="str">
         <v/>
       </c>
-      <c r="N1032" t="str">
-        <v/>
-      </c>
-      <c r="O1032" t="str">
-        <v/>
-      </c>
-      <c r="P1032" t="str">
-        <v/>
-      </c>
-      <c r="Q1032" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1033">
       <c r="A1033" t="str">
@@ -46063,18 +42751,6 @@
       <c r="M1033" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1033" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1033" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1033" t="str">
-        <v/>
-      </c>
-      <c r="Q1033" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1034">
       <c r="A1034" t="str">
@@ -46116,18 +42792,6 @@
       <c r="M1034" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1034" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1034" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1034" t="str">
-        <v/>
-      </c>
-      <c r="Q1034" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1035">
       <c r="A1035" t="str">
@@ -46169,18 +42833,6 @@
       <c r="M1035" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1035" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1035" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1035" t="str">
-        <v/>
-      </c>
-      <c r="Q1035" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1036">
       <c r="A1036" t="str">
@@ -46222,18 +42874,6 @@
       <c r="M1036" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1036" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1036" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1036" t="str">
-        <v/>
-      </c>
-      <c r="Q1036" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1037">
       <c r="A1037" t="str">
@@ -46275,18 +42915,6 @@
       <c r="M1037" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1037" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1037" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1037" t="str">
-        <v/>
-      </c>
-      <c r="Q1037" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1038">
       <c r="A1038" t="str">
@@ -46328,18 +42956,6 @@
       <c r="M1038" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1038" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1038" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1038" t="str">
-        <v/>
-      </c>
-      <c r="Q1038" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1039">
       <c r="A1039" t="str">
@@ -46381,18 +42997,6 @@
       <c r="M1039" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1039" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1039" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1039" t="str">
-        <v/>
-      </c>
-      <c r="Q1039" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1040">
       <c r="A1040" t="str">
@@ -46434,18 +43038,6 @@
       <c r="M1040" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1040" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1040" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1040" t="str">
-        <v/>
-      </c>
-      <c r="Q1040" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1041">
       <c r="A1041" t="str">
@@ -46487,18 +43079,6 @@
       <c r="M1041" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1041" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1041" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1041" t="str">
-        <v/>
-      </c>
-      <c r="Q1041" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1042">
       <c r="A1042" t="str">
@@ -46540,18 +43120,6 @@
       <c r="M1042" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1042" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1042" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1042" t="str">
-        <v/>
-      </c>
-      <c r="Q1042" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1043">
       <c r="A1043" t="str">
@@ -46593,18 +43161,6 @@
       <c r="M1043" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1043" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1043" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1043" t="str">
-        <v/>
-      </c>
-      <c r="Q1043" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1044">
       <c r="A1044" t="str">
@@ -46646,18 +43202,6 @@
       <c r="M1044" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1044" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1044" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1044" t="str">
-        <v/>
-      </c>
-      <c r="Q1044" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1045">
       <c r="A1045" t="str">
@@ -46699,18 +43243,6 @@
       <c r="M1045" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1045" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1045" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1045" t="str">
-        <v/>
-      </c>
-      <c r="Q1045" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1046">
       <c r="A1046" t="str">
@@ -46752,18 +43284,6 @@
       <c r="M1046" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1046" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1046" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1046" t="str">
-        <v/>
-      </c>
-      <c r="Q1046" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1047">
       <c r="A1047" t="str">
@@ -46805,18 +43325,6 @@
       <c r="M1047" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1047" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1047" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1047" t="str">
-        <v/>
-      </c>
-      <c r="Q1047" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1048">
       <c r="A1048" t="str">
@@ -46858,18 +43366,6 @@
       <c r="M1048" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1048" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1048" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1048" t="str">
-        <v/>
-      </c>
-      <c r="Q1048" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1049">
       <c r="A1049" t="str">
@@ -46911,18 +43407,6 @@
       <c r="M1049" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1049" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1049" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1049" t="str">
-        <v/>
-      </c>
-      <c r="Q1049" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1050">
       <c r="A1050" t="str">
@@ -46964,18 +43448,6 @@
       <c r="M1050" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1050" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1050" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1050" t="str">
-        <v/>
-      </c>
-      <c r="Q1050" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1051">
       <c r="A1051" t="str">
@@ -47017,18 +43489,6 @@
       <c r="M1051" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1051" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1051" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1051" t="str">
-        <v/>
-      </c>
-      <c r="Q1051" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1052">
       <c r="A1052" t="str">
@@ -47070,18 +43530,6 @@
       <c r="M1052" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1052" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1052" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1052" t="str">
-        <v/>
-      </c>
-      <c r="Q1052" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1053">
       <c r="A1053" t="str">
@@ -47123,18 +43571,6 @@
       <c r="M1053" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1053" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1053" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1053" t="str">
-        <v/>
-      </c>
-      <c r="Q1053" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1054">
       <c r="A1054" t="str">
@@ -47176,18 +43612,6 @@
       <c r="M1054" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1054" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1054" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1054" t="str">
-        <v/>
-      </c>
-      <c r="Q1054" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1055">
       <c r="A1055" t="str">
@@ -47229,18 +43653,6 @@
       <c r="M1055" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1055" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1055" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1055" t="str">
-        <v/>
-      </c>
-      <c r="Q1055" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1056">
       <c r="A1056" t="str">
@@ -47282,18 +43694,6 @@
       <c r="M1056" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1056" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1056" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1056" t="str">
-        <v/>
-      </c>
-      <c r="Q1056" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1057">
       <c r="A1057" t="str">
@@ -47335,18 +43735,6 @@
       <c r="M1057" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1057" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1057" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1057" t="str">
-        <v/>
-      </c>
-      <c r="Q1057" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1058">
       <c r="A1058" t="str">
@@ -47388,18 +43776,6 @@
       <c r="M1058" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1058" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1058" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1058" t="str">
-        <v/>
-      </c>
-      <c r="Q1058" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1059">
       <c r="A1059" t="str">
@@ -47441,18 +43817,6 @@
       <c r="M1059" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1059" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1059" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1059" t="str">
-        <v/>
-      </c>
-      <c r="Q1059" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1060">
       <c r="A1060" t="str">
@@ -47494,18 +43858,6 @@
       <c r="M1060" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1060" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1060" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1060" t="str">
-        <v/>
-      </c>
-      <c r="Q1060" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1061">
       <c r="A1061" t="str">
@@ -47547,18 +43899,6 @@
       <c r="M1061" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1061" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1061" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1061" t="str">
-        <v/>
-      </c>
-      <c r="Q1061" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1062">
       <c r="A1062" t="str">
@@ -47600,18 +43940,6 @@
       <c r="M1062" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1062" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1062" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1062" t="str">
-        <v/>
-      </c>
-      <c r="Q1062" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1063">
       <c r="A1063" t="str">
@@ -47653,18 +43981,6 @@
       <c r="M1063" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1063" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1063" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1063" t="str">
-        <v/>
-      </c>
-      <c r="Q1063" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1064">
       <c r="A1064" t="str">
@@ -47706,18 +44022,6 @@
       <c r="M1064" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1064" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1064" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1064" t="str">
-        <v/>
-      </c>
-      <c r="Q1064" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1065">
       <c r="A1065" t="str">
@@ -47759,18 +44063,6 @@
       <c r="M1065" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1065" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1065" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1065" t="str">
-        <v/>
-      </c>
-      <c r="Q1065" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1066">
       <c r="A1066" t="str">
@@ -47812,18 +44104,6 @@
       <c r="M1066" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1066" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1066" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1066" t="str">
-        <v/>
-      </c>
-      <c r="Q1066" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1067">
       <c r="A1067" t="str">
@@ -47865,18 +44145,6 @@
       <c r="M1067" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1067" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1067" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1067" t="str">
-        <v/>
-      </c>
-      <c r="Q1067" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1068">
       <c r="A1068" t="str">
@@ -47918,18 +44186,6 @@
       <c r="M1068" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1068" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1068" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1068" t="str">
-        <v/>
-      </c>
-      <c r="Q1068" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1069">
       <c r="A1069" t="str">
@@ -47971,18 +44227,6 @@
       <c r="M1069" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1069" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1069" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1069" t="str">
-        <v/>
-      </c>
-      <c r="Q1069" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1070">
       <c r="A1070" t="str">
@@ -48024,18 +44268,6 @@
       <c r="M1070" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1070" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1070" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1070" t="str">
-        <v/>
-      </c>
-      <c r="Q1070" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1071">
       <c r="A1071" t="str">
@@ -48077,18 +44309,6 @@
       <c r="M1071" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1071" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1071" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1071" t="str">
-        <v/>
-      </c>
-      <c r="Q1071" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1072">
       <c r="A1072" t="str">
@@ -48130,18 +44350,6 @@
       <c r="M1072" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1072" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1072" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1072" t="str">
-        <v/>
-      </c>
-      <c r="Q1072" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1073">
       <c r="A1073" t="str">
@@ -48183,18 +44391,6 @@
       <c r="M1073" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1073" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1073" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1073" t="str">
-        <v/>
-      </c>
-      <c r="Q1073" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1074">
       <c r="A1074" t="str">
@@ -48236,18 +44432,6 @@
       <c r="M1074" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1074" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1074" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1074" t="str">
-        <v/>
-      </c>
-      <c r="Q1074" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1075">
       <c r="A1075" t="str">
@@ -48289,18 +44473,6 @@
       <c r="M1075" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1075" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1075" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1075" t="str">
-        <v/>
-      </c>
-      <c r="Q1075" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1076">
       <c r="A1076" t="str">
@@ -48342,18 +44514,6 @@
       <c r="M1076" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1076" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1076" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1076" t="str">
-        <v/>
-      </c>
-      <c r="Q1076" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1077">
       <c r="A1077" t="str">
@@ -48395,18 +44555,6 @@
       <c r="M1077" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1077" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1077" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1077" t="str">
-        <v/>
-      </c>
-      <c r="Q1077" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1078">
       <c r="A1078" t="str">
@@ -48448,18 +44596,6 @@
       <c r="M1078" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1078" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1078" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1078" t="str">
-        <v/>
-      </c>
-      <c r="Q1078" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1079">
       <c r="A1079" t="str">
@@ -48501,18 +44637,6 @@
       <c r="M1079" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1079" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1079" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1079" t="str">
-        <v/>
-      </c>
-      <c r="Q1079" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1080">
       <c r="A1080" t="str">
@@ -48554,18 +44678,6 @@
       <c r="M1080" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1080" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1080" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1080" t="str">
-        <v/>
-      </c>
-      <c r="Q1080" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1081">
       <c r="A1081" t="str">
@@ -48607,18 +44719,6 @@
       <c r="M1081" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1081" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1081" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1081" t="str">
-        <v/>
-      </c>
-      <c r="Q1081" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1082">
       <c r="A1082" t="str">
@@ -48660,18 +44760,6 @@
       <c r="M1082" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1082" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1082" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1082" t="str">
-        <v/>
-      </c>
-      <c r="Q1082" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1083">
       <c r="A1083" t="str">
@@ -48713,18 +44801,6 @@
       <c r="M1083" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1083" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1083" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1083" t="str">
-        <v/>
-      </c>
-      <c r="Q1083" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1084">
       <c r="A1084" t="str">
@@ -48766,18 +44842,6 @@
       <c r="M1084" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1084" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1084" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1084" t="str">
-        <v/>
-      </c>
-      <c r="Q1084" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1085">
       <c r="A1085" t="str">
@@ -48819,18 +44883,6 @@
       <c r="M1085" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1085" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1085" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1085" t="str">
-        <v/>
-      </c>
-      <c r="Q1085" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1086">
       <c r="A1086" t="str">
@@ -48872,18 +44924,6 @@
       <c r="M1086" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1086" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1086" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1086" t="str">
-        <v/>
-      </c>
-      <c r="Q1086" t="str">
-        <v/>
-      </c>
     </row>
     <row r="1087">
       <c r="A1087" t="str">
@@ -48925,22 +44965,10 @@
       <c r="M1087" t="str">
         <v>フロント：#4・リア：#6</v>
       </c>
-      <c r="N1087" t="str">
-        <v>－</v>
-      </c>
-      <c r="O1087" t="str">
-        <v>シンキング</v>
-      </c>
-      <c r="P1087" t="str">
-        <v/>
-      </c>
-      <c r="Q1087" t="str">
-        <v/>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q1087"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M1087"/>
   </ignoredErrors>
 </worksheet>
 </file>